--- a/backtest/resultaten/backtest.xlsx
+++ b/backtest/resultaten/backtest.xlsx
@@ -478,19 +478,19 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.06893078011176179</v>
+        <v>0.06765730383163304</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.01342288972166727</v>
+        <v>0.01318127216447307</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>-0.0453106895687847</v>
       </c>
       <c r="E2" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>10685.31</v>
+        <v>10672.58</v>
       </c>
     </row>
     <row r="3">
@@ -500,10 +500,10 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.8023580668955397</v>
+        <v>0.7966332910327338</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.1250587986043323</v>
+        <v>0.1243430927939526</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>-0.2159070282344387</v>
@@ -512,7 +512,7 @@
         <v>0.75</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>18023.5806689554</v>
+        <v>17966.33291032734</v>
       </c>
     </row>
     <row r="4">
@@ -522,19 +522,19 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.9517992389492855</v>
+        <v>0.9328518002062276</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.1431283133825358</v>
+        <v>0.1408999155644965</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>-0.2303250572697892</v>
+        <v>-0.230325229336082</v>
       </c>
       <c r="E4" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>19517.99238949285</v>
+        <v>19328.51800206228</v>
       </c>
     </row>
   </sheetData>
@@ -590,7 +590,7 @@
         <v>0.07653520965938676</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.1032400451411399</v>
+        <v>0.1032398940921537</v>
       </c>
     </row>
     <row r="3">
@@ -604,7 +604,7 @@
         <v>-0.135414019248523</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>-0.1307686249069812</v>
+        <v>-0.1307686513421884</v>
       </c>
     </row>
     <row r="4">
@@ -618,7 +618,7 @@
         <v>0.1989455715883754</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.2153106066474764</v>
+        <v>0.215310729417435</v>
       </c>
     </row>
     <row r="5">
@@ -632,7 +632,7 @@
         <v>0.2722609034779582</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.3283173244071134</v>
+        <v>0.3283176945842834</v>
       </c>
     </row>
     <row r="6">
@@ -646,7 +646,7 @@
         <v>0.0707564790521269</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.04279560166903007</v>
+        <v>0.04279538020587159</v>
       </c>
     </row>
     <row r="7">
@@ -654,13 +654,13 @@
         <v>2026</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.01220196087718461</v>
+        <v>0.01099606877279391</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.1856002615870618</v>
+        <v>0.1818344750404626</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.2090420819901981</v>
+        <v>0.1973050906392739</v>
       </c>
     </row>
   </sheetData>
@@ -782,16 +782,16 @@
         <v>0.6452684006640841</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.01044377848506683</v>
+        <v>0.01044367467660168</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>-0.05401617415841531</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-0.1303951526163767</v>
+        <v>-0.1303952576153423</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.1335971931188094</v>
+        <v>0.1335968056633563</v>
       </c>
     </row>
   </sheetData>
@@ -945,7 +945,7 @@
         <v>10164.24751123039</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>10195.49136994588</v>
+        <v>10195.49431121002</v>
       </c>
     </row>
     <row r="9">
@@ -961,7 +961,7 @@
         <v>10145.84607455603</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>10201.87051666557</v>
+        <v>10201.87271825138</v>
       </c>
     </row>
     <row r="10">
@@ -977,7 +977,7 @@
         <v>10171.06316627214</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>10217.31464549922</v>
+        <v>10217.31317402899</v>
       </c>
     </row>
     <row r="11">
@@ -993,7 +993,7 @@
         <v>10171.06316627214</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>10217.31464549922</v>
+        <v>10217.31317402899</v>
       </c>
     </row>
     <row r="12">
@@ -1009,7 +1009,7 @@
         <v>10171.06316627214</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>10217.31464549922</v>
+        <v>10217.31317402899</v>
       </c>
     </row>
     <row r="13">
@@ -1025,7 +1025,7 @@
         <v>10225.58424691432</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>10259.09072216851</v>
+        <v>10259.09145697134</v>
       </c>
     </row>
     <row r="14">
@@ -1041,7 +1041,7 @@
         <v>10303.27793074467</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>10293.42348091884</v>
+        <v>10293.42200772088</v>
       </c>
     </row>
     <row r="15">
@@ -1057,7 +1057,7 @@
         <v>10256.93480421422</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>10259.72296708184</v>
+        <v>10259.7222296275</v>
       </c>
     </row>
     <row r="16">
@@ -1089,7 +1089,7 @@
         <v>10324.40604540491</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>10303.89263554441</v>
+        <v>10303.89190347862</v>
       </c>
     </row>
     <row r="18">
@@ -1105,7 +1105,7 @@
         <v>10324.40604540491</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>10303.89263554441</v>
+        <v>10303.89190347862</v>
       </c>
     </row>
     <row r="19">
@@ -1121,7 +1121,7 @@
         <v>10324.40604540491</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>10303.89263554441</v>
+        <v>10303.89190347862</v>
       </c>
     </row>
     <row r="20">
@@ -1137,7 +1137,7 @@
         <v>10342.12529262132</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>10434.97490855287</v>
+        <v>10434.97416844704</v>
       </c>
     </row>
     <row r="21">
@@ -1153,7 +1153,7 @@
         <v>10379.60931550503</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>10438.41809326019</v>
+        <v>10438.41883062897</v>
       </c>
     </row>
     <row r="22">
@@ -1169,7 +1169,7 @@
         <v>10376.88263751915</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>10520.42054496654</v>
+        <v>10520.41906766302</v>
       </c>
     </row>
     <row r="23">
@@ -1185,7 +1185,7 @@
         <v>10483.88239012148</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>10536.95241116583</v>
+        <v>10536.95093848101</v>
       </c>
     </row>
     <row r="24">
@@ -1265,7 +1265,7 @@
         <v>10478.43007407267</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>10569.61199503704</v>
+        <v>10569.60978139122</v>
       </c>
     </row>
     <row r="29">
@@ -1275,13 +1275,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>9991.860000000001</v>
+        <v>9991.870000000001</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>10515.23190749844</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>10480.93383286551</v>
+        <v>10480.93530811628</v>
       </c>
     </row>
     <row r="30">
@@ -1297,7 +1297,7 @@
         <v>10527.49987858899</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>10584.37794700598</v>
+        <v>10584.37869167062</v>
       </c>
     </row>
     <row r="31">
@@ -1361,7 +1361,7 @@
         <v>10640.63309677513</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>10709.20322353948</v>
+        <v>10709.20023335137</v>
       </c>
     </row>
     <row r="35">
@@ -1377,7 +1377,7 @@
         <v>10729.91256223809</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>10822.68949284218</v>
+        <v>10822.69024533295</v>
       </c>
     </row>
     <row r="36">
@@ -1409,7 +1409,7 @@
         <v>10686.29507377057</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>10876.41010223518</v>
+        <v>10876.41161323814</v>
       </c>
     </row>
     <row r="38">
@@ -1489,7 +1489,7 @@
         <v>10641.31424631012</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>10916.96845401441</v>
+        <v>10916.96921482738</v>
       </c>
     </row>
     <row r="43">
@@ -1505,7 +1505,7 @@
         <v>10736.04602782189</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>10943.40718907272</v>
+        <v>10943.40642844792</v>
       </c>
     </row>
     <row r="44">
@@ -1521,7 +1521,7 @@
         <v>10763.30656814298</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>10984.38614415422</v>
+        <v>10984.38538068116</v>
       </c>
     </row>
     <row r="45">
@@ -1537,7 +1537,7 @@
         <v>10391.87624667264</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>10733.0251159795</v>
+        <v>10733.02435295974</v>
       </c>
     </row>
     <row r="46">
@@ -1553,7 +1553,7 @@
         <v>10391.87624667264</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>10733.0251159795</v>
+        <v>10733.02435295974</v>
       </c>
     </row>
     <row r="47">
@@ -1569,7 +1569,7 @@
         <v>10391.87624667264</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>10733.0251159795</v>
+        <v>10733.02435295974</v>
       </c>
     </row>
     <row r="48">
@@ -1601,7 +1601,7 @@
         <v>10403.46202830525</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>10574.2251247667</v>
+        <v>10574.22663948176</v>
       </c>
     </row>
     <row r="50">
@@ -1633,7 +1633,7 @@
         <v>10309.41243625142</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>10592.47292315105</v>
+        <v>10592.47518998919</v>
       </c>
     </row>
     <row r="52">
@@ -1649,7 +1649,7 @@
         <v>10278.74406840946</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>10512.66731545702</v>
+        <v>10512.6665589548</v>
       </c>
     </row>
     <row r="53">
@@ -1665,7 +1665,7 @@
         <v>10278.74406840946</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>10512.66731545702</v>
+        <v>10512.6665589548</v>
       </c>
     </row>
     <row r="54">
@@ -1681,7 +1681,7 @@
         <v>10278.74406840946</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>10512.66731545702</v>
+        <v>10512.6665589548</v>
       </c>
     </row>
     <row r="55">
@@ -1713,7 +1713,7 @@
         <v>10676.07159120795</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>10875.98153128967</v>
+        <v>10875.98077347882</v>
       </c>
     </row>
     <row r="57">
@@ -1729,7 +1729,7 @@
         <v>10590.88110280085</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>10914.62589443394</v>
+        <v>10914.62665292902</v>
       </c>
     </row>
     <row r="58">
@@ -1745,7 +1745,7 @@
         <v>10630.4096142125</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>10774.92449704714</v>
+        <v>10774.92298929436</v>
       </c>
     </row>
     <row r="59">
@@ -1761,7 +1761,7 @@
         <v>10566.34620054269</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>10926.69701126971</v>
+        <v>10926.6977686358</v>
       </c>
     </row>
     <row r="60">
@@ -1777,7 +1777,7 @@
         <v>10566.34620054269</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>10926.69701126971</v>
+        <v>10926.6977686358</v>
       </c>
     </row>
     <row r="61">
@@ -1793,7 +1793,7 @@
         <v>10566.34620054269</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>10926.69701126971</v>
+        <v>10926.6977686358</v>
       </c>
     </row>
     <row r="62">
@@ -1825,7 +1825,7 @@
         <v>10447.76170623071</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>10762.92492955103</v>
+        <v>10762.92720324028</v>
       </c>
     </row>
     <row r="64">
@@ -1841,7 +1841,7 @@
         <v>10464.11761445418</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>10954.5377959533</v>
+        <v>10954.53627691037</v>
       </c>
     </row>
     <row r="65">
@@ -1857,7 +1857,7 @@
         <v>10611.32702800315</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>10829.56787029142</v>
+        <v>10829.56559767979</v>
       </c>
     </row>
     <row r="66">
@@ -1873,7 +1873,7 @@
         <v>10521.36641300519</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>10673.29841623462</v>
+        <v>10673.29690695931</v>
       </c>
     </row>
     <row r="67">
@@ -1889,7 +1889,7 @@
         <v>10521.36641300519</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>10673.29841623462</v>
+        <v>10673.29690695931</v>
       </c>
     </row>
     <row r="68">
@@ -1905,7 +1905,7 @@
         <v>10521.36641300519</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>10673.29841623462</v>
+        <v>10673.29690695931</v>
       </c>
     </row>
     <row r="69">
@@ -1921,7 +1921,7 @@
         <v>10289.64766058412</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>10644.90180532798</v>
+        <v>10644.90028389015</v>
       </c>
     </row>
     <row r="70">
@@ -1937,7 +1937,7 @@
         <v>10462.75531538419</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>10801.29980634324</v>
+        <v>10801.29904791655</v>
       </c>
     </row>
     <row r="71">
@@ -1953,7 +1953,7 @@
         <v>10562.25722348683</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>10899.57650005006</v>
+        <v>10899.57801555202</v>
       </c>
     </row>
     <row r="72">
@@ -1969,7 +1969,7 @@
         <v>10687.65841276352</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>10927.41025027394</v>
+        <v>10927.41176025057</v>
       </c>
     </row>
     <row r="73">
@@ -1985,7 +1985,7 @@
         <v>10690.38405082644</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>10928.89605603913</v>
+        <v>10928.89756622108</v>
       </c>
     </row>
     <row r="74">
@@ -2001,7 +2001,7 @@
         <v>10690.38405082644</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>10928.89605603913</v>
+        <v>10928.89756622108</v>
       </c>
     </row>
     <row r="75">
@@ -2017,7 +2017,7 @@
         <v>10690.38405082644</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>10928.89605603913</v>
+        <v>10928.89756622108</v>
       </c>
     </row>
     <row r="76">
@@ -2033,7 +2033,7 @@
         <v>10753.08412550331</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>11086.57541210734</v>
+        <v>11086.57616740355</v>
       </c>
     </row>
     <row r="77">
@@ -2049,7 +2049,7 @@
         <v>10815.78420018018</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>11071.87024509542</v>
+        <v>11071.87100000676</v>
       </c>
     </row>
     <row r="78">
@@ -2065,7 +2065,7 @@
         <v>10757.17310255918</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>11100.98145607297</v>
+        <v>11100.98221200213</v>
       </c>
     </row>
     <row r="79">
@@ -2081,7 +2081,7 @@
         <v>10813.73971165224</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>11026.07802979234</v>
+        <v>11026.07652397252</v>
       </c>
     </row>
     <row r="80">
@@ -2097,7 +2097,7 @@
         <v>10765.35209659387</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>11032.4004514114</v>
+        <v>11032.39894092154</v>
       </c>
     </row>
     <row r="81">
@@ -2113,7 +2113,7 @@
         <v>10765.35209659387</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>11032.4004514114</v>
+        <v>11032.39894092154</v>
       </c>
     </row>
     <row r="82">
@@ -2129,7 +2129,7 @@
         <v>10765.35209659387</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>11032.4004514114</v>
+        <v>11032.39894092154</v>
       </c>
     </row>
     <row r="83">
@@ -2145,7 +2145,7 @@
         <v>10787.16032086615</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>11049.02595852277</v>
+        <v>11049.02370243606</v>
       </c>
     </row>
     <row r="84">
@@ -2161,7 +2161,7 @@
         <v>10835.54897584748</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>11114.91856496717</v>
+        <v>11114.9200785019</v>
       </c>
     </row>
     <row r="85">
@@ -2193,7 +2193,7 @@
         <v>10642.67758530306</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>10880.41468394951</v>
+        <v>10880.41695199362</v>
       </c>
     </row>
     <row r="87">
@@ -2209,7 +2209,7 @@
         <v>10560.21273495889</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>10853.34081719433</v>
+        <v>10853.34157432098</v>
       </c>
     </row>
     <row r="88">
@@ -2225,7 +2225,7 @@
         <v>10560.21273495889</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>10853.34081719433</v>
+        <v>10853.34157432098</v>
       </c>
     </row>
     <row r="89">
@@ -2241,7 +2241,7 @@
         <v>10560.21273495889</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>10853.34081719433</v>
+        <v>10853.34157432098</v>
       </c>
     </row>
     <row r="90">
@@ -2273,7 +2273,7 @@
         <v>10549.99029231922</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>10906.1921365096</v>
+        <v>10906.19062673822</v>
       </c>
     </row>
     <row r="92">
@@ -2289,7 +2289,7 @@
         <v>10605.19356241935</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>10900.98314766548</v>
+        <v>10900.98089019316</v>
       </c>
     </row>
     <row r="93">
@@ -2305,7 +2305,7 @@
         <v>10569.75402806357</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>10680.15205096395</v>
+        <v>10680.15279851097</v>
       </c>
     </row>
     <row r="94">
@@ -2321,7 +2321,7 @@
         <v>10426.63463149342</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>10670.09334735791</v>
+        <v>10670.09409389573</v>
       </c>
     </row>
     <row r="95">
@@ -2337,7 +2337,7 @@
         <v>10426.63463149342</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>10670.09334735791</v>
+        <v>10670.09409389573</v>
       </c>
     </row>
     <row r="96">
@@ -2353,7 +2353,7 @@
         <v>10426.63463149342</v>
       </c>
       <c r="D96" s="3" t="n">
-        <v>10670.09334735791</v>
+        <v>10670.09409389573</v>
       </c>
     </row>
     <row r="97">
@@ -2369,7 +2369,7 @@
         <v>10512.50626943551</v>
       </c>
       <c r="D97" s="3" t="n">
-        <v>10713.49163172767</v>
+        <v>10713.49238130187</v>
       </c>
     </row>
     <row r="98">
@@ -2385,7 +2385,7 @@
         <v>10395.9652237285</v>
       </c>
       <c r="D98" s="3" t="n">
-        <v>10523.88299775612</v>
+        <v>10523.88149859065</v>
       </c>
     </row>
     <row r="99">
@@ -2401,7 +2401,7 @@
         <v>10353.02992471894</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>10488.99805722316</v>
+        <v>10488.99881216016</v>
       </c>
     </row>
     <row r="100">
@@ -2417,7 +2417,7 @@
         <v>10437.53822366809</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>10360.32691774682</v>
+        <v>10360.33068785564</v>
       </c>
     </row>
     <row r="101">
@@ -2433,7 +2433,7 @@
         <v>9888.230120806809</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>10092.69466181504</v>
+        <v>10092.69692772944</v>
       </c>
     </row>
     <row r="102">
@@ -2449,7 +2449,7 @@
         <v>10090.6428044559</v>
       </c>
       <c r="D102" s="3" t="n">
-        <v>10084.81640688219</v>
+        <v>10084.81565026876</v>
       </c>
     </row>
     <row r="103">
@@ -2465,7 +2465,7 @@
         <v>10144.48377548604</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>10089.46973629251</v>
+        <v>10089.4689755736</v>
       </c>
     </row>
     <row r="104">
@@ -2481,7 +2481,7 @@
         <v>10010.90463209762</v>
       </c>
       <c r="D104" s="3" t="n">
-        <v>10429.56460230145</v>
+        <v>10429.56690421606</v>
       </c>
     </row>
     <row r="105">
@@ -2497,7 +2497,7 @@
         <v>10010.90463209762</v>
       </c>
       <c r="D105" s="3" t="n">
-        <v>10429.56460230145</v>
+        <v>10429.56690421606</v>
       </c>
     </row>
     <row r="106">
@@ -2513,7 +2513,7 @@
         <v>10010.90463209762</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>10429.56460230145</v>
+        <v>10429.56690421606</v>
       </c>
     </row>
     <row r="107">
@@ -2545,7 +2545,7 @@
         <v>10308.73024679348</v>
       </c>
       <c r="D108" s="3" t="n">
-        <v>10610.51494929126</v>
+        <v>10610.51342597168</v>
       </c>
     </row>
     <row r="109">
@@ -2577,7 +2577,7 @@
         <v>10148.57275254191</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>10396.67801955711</v>
+        <v>10396.67574879323</v>
       </c>
     </row>
     <row r="111">
@@ -2593,7 +2593,7 @@
         <v>10042.93633893252</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>10321.5099789412</v>
+        <v>10321.51297066913</v>
       </c>
     </row>
     <row r="112">
@@ -2609,7 +2609,7 @@
         <v>10042.93633893252</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>10321.5099789412</v>
+        <v>10321.51297066913</v>
       </c>
     </row>
     <row r="113">
@@ -2625,7 +2625,7 @@
         <v>10042.93633893252</v>
       </c>
       <c r="D113" s="3" t="n">
-        <v>10321.5099789412</v>
+        <v>10321.51297066913</v>
       </c>
     </row>
     <row r="114">
@@ -2641,7 +2641,7 @@
         <v>10102.91077554646</v>
       </c>
       <c r="D114" s="3" t="n">
-        <v>10270.97214948987</v>
+        <v>10270.97438948813</v>
       </c>
     </row>
     <row r="115">
@@ -2657,7 +2657,7 @@
         <v>10153.34287913277</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>10366.51240176291</v>
+        <v>10366.51314922443</v>
       </c>
     </row>
     <row r="116">
@@ -2689,7 +2689,7 @@
         <v>10230.35541342813</v>
       </c>
       <c r="D117" s="3" t="n">
-        <v>10348.65829641685</v>
+        <v>10348.65679868825</v>
       </c>
     </row>
     <row r="118">
@@ -2753,7 +2753,7 @@
         <v>10063.38226413481</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>10161.66487816736</v>
+        <v>10161.6641255825</v>
       </c>
     </row>
     <row r="122">
@@ -2769,7 +2769,7 @@
         <v>10146.52826401398</v>
       </c>
       <c r="D122" s="3" t="n">
-        <v>10379.16870597862</v>
+        <v>10379.17021896584</v>
       </c>
     </row>
     <row r="123">
@@ -2785,7 +2785,7 @@
         <v>10104.27307461645</v>
       </c>
       <c r="D123" s="3" t="n">
-        <v>10344.63444906773</v>
+        <v>10344.63218967082</v>
       </c>
     </row>
     <row r="124">
@@ -2817,7 +2817,7 @@
         <v>9942.071091836948</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>10049.53758211246</v>
+        <v>10049.53908709401</v>
       </c>
     </row>
     <row r="126">
@@ -2833,7 +2833,7 @@
         <v>9942.071091836948</v>
       </c>
       <c r="D126" s="3" t="n">
-        <v>10049.53758211246</v>
+        <v>10049.53908709401</v>
       </c>
     </row>
     <row r="127">
@@ -2849,7 +2849,7 @@
         <v>9942.071091836948</v>
       </c>
       <c r="D127" s="3" t="n">
-        <v>10049.53758211246</v>
+        <v>10049.53908709401</v>
       </c>
     </row>
     <row r="128">
@@ -2865,7 +2865,7 @@
         <v>9828.937873650817</v>
       </c>
       <c r="D128" s="3" t="n">
-        <v>10093.28694101826</v>
+        <v>10093.28845255154</v>
       </c>
     </row>
     <row r="129">
@@ -2881,7 +2881,7 @@
         <v>9853.472775908978</v>
       </c>
       <c r="D129" s="3" t="n">
-        <v>9991.637071292093</v>
+        <v>9991.638583834689</v>
       </c>
     </row>
     <row r="130">
@@ -2913,7 +2913,7 @@
         <v>9665.372551878376</v>
       </c>
       <c r="D131" s="3" t="n">
-        <v>9965.591279107621</v>
+        <v>9965.590522571178</v>
       </c>
     </row>
     <row r="132">
@@ -2977,7 +2977,7 @@
         <v>10024.53490225816</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>10272.6654043528</v>
+        <v>10272.66463938289</v>
       </c>
     </row>
     <row r="136">
@@ -2993,7 +2993,7 @@
         <v>9963.198166574235</v>
       </c>
       <c r="D136" s="3" t="n">
-        <v>10084.76206791691</v>
+        <v>10084.75978014076</v>
       </c>
     </row>
     <row r="137">
@@ -3009,7 +3009,7 @@
         <v>10072.92355723949</v>
       </c>
       <c r="D137" s="3" t="n">
-        <v>10346.99988285059</v>
+        <v>10347.00065113903</v>
       </c>
     </row>
     <row r="138">
@@ -3025,7 +3025,7 @@
         <v>10045.66197699545</v>
       </c>
       <c r="D138" s="3" t="n">
-        <v>10314.39896952677</v>
+        <v>10314.40127862613</v>
       </c>
     </row>
     <row r="139">
@@ -3041,7 +3041,7 @@
         <v>9954.338023004551</v>
       </c>
       <c r="D139" s="3" t="n">
-        <v>10272.66456079969</v>
+        <v>10272.66146934215</v>
       </c>
     </row>
     <row r="140">
@@ -3057,7 +3057,7 @@
         <v>9954.338023004551</v>
       </c>
       <c r="D140" s="3" t="n">
-        <v>10272.66456079969</v>
+        <v>10272.66146934215</v>
       </c>
     </row>
     <row r="141">
@@ -3073,7 +3073,7 @@
         <v>9954.338023004551</v>
       </c>
       <c r="D141" s="3" t="n">
-        <v>10272.66456079969</v>
+        <v>10272.66146934215</v>
       </c>
     </row>
     <row r="142">
@@ -3089,7 +3089,7 @@
         <v>9911.401684072031</v>
       </c>
       <c r="D142" s="3" t="n">
-        <v>10146.14728185074</v>
+        <v>10146.14806838311</v>
       </c>
     </row>
     <row r="143">
@@ -3105,7 +3105,7 @@
         <v>9692.633092199465</v>
       </c>
       <c r="D143" s="3" t="n">
-        <v>10077.76712744814</v>
+        <v>10077.76555304893</v>
       </c>
     </row>
     <row r="144">
@@ -3121,7 +3121,7 @@
         <v>9837.798017220501</v>
       </c>
       <c r="D144" s="3" t="n">
-        <v>10316.70332434726</v>
+        <v>10316.69940023847</v>
       </c>
     </row>
     <row r="145">
@@ -3137,7 +3137,7 @@
         <v>9773.052414092745</v>
       </c>
       <c r="D145" s="3" t="n">
-        <v>10107.26266638526</v>
+        <v>10107.2611216314</v>
       </c>
     </row>
     <row r="146">
@@ -3153,7 +3153,7 @@
         <v>9875.281000181258</v>
       </c>
       <c r="D146" s="3" t="n">
-        <v>10033.00543298561</v>
+        <v>10033.00465640913</v>
       </c>
     </row>
     <row r="147">
@@ -3169,7 +3169,7 @@
         <v>9875.281000181258</v>
       </c>
       <c r="D147" s="3" t="n">
-        <v>10033.00543298561</v>
+        <v>10033.00465640913</v>
       </c>
     </row>
     <row r="148">
@@ -3185,7 +3185,7 @@
         <v>9875.281000181258</v>
       </c>
       <c r="D148" s="3" t="n">
-        <v>10033.00543298561</v>
+        <v>10033.00465640913</v>
       </c>
     </row>
     <row r="149">
@@ -3201,7 +3201,7 @@
         <v>9766.918948508943</v>
       </c>
       <c r="D149" s="3" t="n">
-        <v>10034.27405603647</v>
+        <v>10034.27483842917</v>
       </c>
     </row>
     <row r="150">
@@ -3217,7 +3217,7 @@
         <v>9854.836114901918</v>
       </c>
       <c r="D150" s="3" t="n">
-        <v>10244.50543194832</v>
+        <v>10244.50621354558</v>
       </c>
     </row>
     <row r="151">
@@ -3233,7 +3233,7 @@
         <v>10052.4776320372</v>
       </c>
       <c r="D151" s="3" t="n">
-        <v>10446.68621129032</v>
+        <v>10446.68777075546</v>
       </c>
     </row>
     <row r="152">
@@ -3249,7 +3249,7 @@
         <v>10089.27946546296</v>
       </c>
       <c r="D152" s="3" t="n">
-        <v>10526.91547656324</v>
+        <v>10526.91470055118</v>
       </c>
     </row>
     <row r="153">
@@ -3265,7 +3265,7 @@
         <v>10245.34902258161</v>
       </c>
       <c r="D153" s="3" t="n">
-        <v>10567.84669113571</v>
+        <v>10567.84592054644</v>
       </c>
     </row>
     <row r="154">
@@ -3281,7 +3281,7 @@
         <v>10245.34902258161</v>
       </c>
       <c r="D154" s="3" t="n">
-        <v>10567.84669113571</v>
+        <v>10567.84592054644</v>
       </c>
     </row>
     <row r="155">
@@ -3297,7 +3297,7 @@
         <v>10245.34902258161</v>
       </c>
       <c r="D155" s="3" t="n">
-        <v>10567.84669113571</v>
+        <v>10567.84592054644</v>
       </c>
     </row>
     <row r="156">
@@ -3329,7 +3329,7 @@
         <v>10428.67912002136</v>
       </c>
       <c r="D157" s="3" t="n">
-        <v>10768.21893395548</v>
+        <v>10768.21971030105</v>
       </c>
     </row>
     <row r="158">
@@ -3345,7 +3345,7 @@
         <v>10406.18870629113</v>
       </c>
       <c r="D158" s="3" t="n">
-        <v>10617.48020665481</v>
+        <v>10617.48098211943</v>
       </c>
     </row>
     <row r="159">
@@ -3361,7 +3361,7 @@
         <v>10400.05524070733</v>
       </c>
       <c r="D159" s="3" t="n">
-        <v>10800.47384768598</v>
+        <v>10800.47540191674</v>
       </c>
     </row>
     <row r="160">
@@ -3377,7 +3377,7 @@
         <v>10456.62080987744</v>
       </c>
       <c r="D160" s="3" t="n">
-        <v>10849.99395518322</v>
+        <v>10849.99473206763</v>
       </c>
     </row>
     <row r="161">
@@ -3393,7 +3393,7 @@
         <v>10456.62080987744</v>
       </c>
       <c r="D161" s="3" t="n">
-        <v>10849.99395518322</v>
+        <v>10849.99473206763</v>
       </c>
     </row>
     <row r="162">
@@ -3409,7 +3409,7 @@
         <v>10456.62080987744</v>
       </c>
       <c r="D162" s="3" t="n">
-        <v>10849.99395518322</v>
+        <v>10849.99473206763</v>
       </c>
     </row>
     <row r="163">
@@ -3425,7 +3425,7 @@
         <v>10489.33470617029</v>
       </c>
       <c r="D163" s="3" t="n">
-        <v>10954.72001610652</v>
+        <v>10954.71923726344</v>
       </c>
     </row>
     <row r="164">
@@ -3441,7 +3441,7 @@
         <v>10565.6650510077</v>
       </c>
       <c r="D164" s="3" t="n">
-        <v>11078.18043680873</v>
+        <v>11078.18199280146</v>
       </c>
     </row>
     <row r="165">
@@ -3457,7 +3457,7 @@
         <v>10518.63973501931</v>
       </c>
       <c r="D165" s="3" t="n">
-        <v>10912.82429873266</v>
+        <v>10912.82352758741</v>
       </c>
     </row>
     <row r="166">
@@ -3473,7 +3473,7 @@
         <v>10509.09844191464</v>
       </c>
       <c r="D166" s="3" t="n">
-        <v>10677.16813065089</v>
+        <v>10677.16966322502</v>
       </c>
     </row>
     <row r="167">
@@ -3489,7 +3489,7 @@
         <v>10475.70443600974</v>
       </c>
       <c r="D167" s="3" t="n">
-        <v>10793.95706367353</v>
+        <v>10793.95629119398</v>
       </c>
     </row>
     <row r="168">
@@ -3505,7 +3505,7 @@
         <v>10475.70443600974</v>
       </c>
       <c r="D168" s="3" t="n">
-        <v>10793.95706367353</v>
+        <v>10793.95629119398</v>
       </c>
     </row>
     <row r="169">
@@ -3521,7 +3521,7 @@
         <v>10475.70443600974</v>
       </c>
       <c r="D169" s="3" t="n">
-        <v>10793.95706367353</v>
+        <v>10793.95629119398</v>
       </c>
     </row>
     <row r="170">
@@ -3585,7 +3585,7 @@
         <v>10393.23958566558</v>
       </c>
       <c r="D173" s="3" t="n">
-        <v>10865.93336269319</v>
+        <v>10865.93257787143</v>
       </c>
     </row>
     <row r="174">
@@ -3649,7 +3649,7 @@
         <v>10380.29046504003</v>
       </c>
       <c r="D177" s="3" t="n">
-        <v>10664.65381639644</v>
+        <v>10664.65224483706</v>
       </c>
     </row>
     <row r="178">
@@ -3665,7 +3665,7 @@
         <v>10435.49373514015</v>
       </c>
       <c r="D178" s="3" t="n">
-        <v>10631.96378435145</v>
+        <v>10631.96221178267</v>
       </c>
     </row>
     <row r="179">
@@ -3681,7 +3681,7 @@
         <v>10389.15060860971</v>
       </c>
       <c r="D179" s="3" t="n">
-        <v>10805.20657981553</v>
+        <v>10805.20578976778</v>
       </c>
     </row>
     <row r="180">
@@ -3697,7 +3697,7 @@
         <v>10451.85068328658</v>
       </c>
       <c r="D180" s="3" t="n">
-        <v>10601.69585241098</v>
+        <v>10601.69663735251</v>
       </c>
     </row>
     <row r="181">
@@ -3713,7 +3713,7 @@
         <v>10451.85068328658</v>
       </c>
       <c r="D181" s="3" t="n">
-        <v>10675.74523915444</v>
+        <v>10675.74602957853</v>
       </c>
     </row>
     <row r="182">
@@ -3729,7 +3729,7 @@
         <v>10451.85068328658</v>
       </c>
       <c r="D182" s="3" t="n">
-        <v>10675.74523915444</v>
+        <v>10675.74602957853</v>
       </c>
     </row>
     <row r="183">
@@ -3745,7 +3745,7 @@
         <v>10451.85068328658</v>
       </c>
       <c r="D183" s="3" t="n">
-        <v>10675.74523915444</v>
+        <v>10675.74602957853</v>
       </c>
     </row>
     <row r="184">
@@ -3761,7 +3761,7 @@
         <v>10451.85068328658</v>
       </c>
       <c r="D184" s="3" t="n">
-        <v>10685.79758470878</v>
+        <v>10685.79916639509</v>
       </c>
     </row>
     <row r="185">
@@ -3777,7 +3777,7 @@
         <v>10460.71082685626</v>
       </c>
       <c r="D185" s="3" t="n">
-        <v>10891.9982137281</v>
+        <v>10891.99980032399</v>
       </c>
     </row>
     <row r="186">
@@ -3793,7 +3793,7 @@
         <v>10479.11122360767</v>
       </c>
       <c r="D186" s="3" t="n">
-        <v>10871.13147146048</v>
+        <v>10871.13305619189</v>
       </c>
     </row>
     <row r="187">
@@ -3809,7 +3809,7 @@
         <v>10479.11122360767</v>
       </c>
       <c r="D187" s="3" t="n">
-        <v>10653.89422249123</v>
+        <v>10653.89343417122</v>
       </c>
     </row>
     <row r="188">
@@ -3825,7 +3825,7 @@
         <v>10231.71875242107</v>
       </c>
       <c r="D188" s="3" t="n">
-        <v>10375.61253741474</v>
+        <v>10375.61332680389</v>
       </c>
     </row>
     <row r="189">
@@ -3841,7 +3841,7 @@
         <v>10231.71875242107</v>
       </c>
       <c r="D189" s="3" t="n">
-        <v>10375.61253741474</v>
+        <v>10375.61332680389</v>
       </c>
     </row>
     <row r="190">
@@ -3857,7 +3857,7 @@
         <v>10231.71875242107</v>
       </c>
       <c r="D190" s="3" t="n">
-        <v>10375.61253741474</v>
+        <v>10375.61332680389</v>
       </c>
     </row>
     <row r="191">
@@ -3873,7 +3873,7 @@
         <v>10046.3441664534</v>
       </c>
       <c r="D191" s="3" t="n">
-        <v>10459.05986862629</v>
+        <v>10459.05907747522</v>
       </c>
     </row>
     <row r="192">
@@ -3889,7 +3889,7 @@
         <v>10060.65558614893</v>
       </c>
       <c r="D192" s="3" t="n">
-        <v>10247.94896150581</v>
+        <v>10247.94656660109</v>
       </c>
     </row>
     <row r="193">
@@ -3905,7 +3905,7 @@
         <v>10151.29839060484</v>
       </c>
       <c r="D193" s="3" t="n">
-        <v>10344.91960262702</v>
+        <v>10344.92201341503</v>
       </c>
     </row>
     <row r="194">
@@ -3921,7 +3921,7 @@
         <v>10206.50166070496</v>
       </c>
       <c r="D194" s="3" t="n">
-        <v>10695.18340834083</v>
+        <v>10695.18421867672</v>
       </c>
     </row>
     <row r="195">
@@ -3937,7 +3937,7 @@
         <v>10231.03656296312</v>
       </c>
       <c r="D195" s="3" t="n">
-        <v>10349.8364185476</v>
+        <v>10349.83397576225</v>
       </c>
     </row>
     <row r="196">
@@ -3953,7 +3953,7 @@
         <v>10231.03656296312</v>
       </c>
       <c r="D196" s="3" t="n">
-        <v>10349.8364185476</v>
+        <v>10349.83397576225</v>
       </c>
     </row>
     <row r="197">
@@ -3969,7 +3969,7 @@
         <v>10231.03656296312</v>
       </c>
       <c r="D197" s="3" t="n">
-        <v>10349.8364185476</v>
+        <v>10349.83397576225</v>
       </c>
     </row>
     <row r="198">
@@ -3985,7 +3985,7 @@
         <v>10010.90463209762</v>
       </c>
       <c r="D198" s="3" t="n">
-        <v>10380.74558708217</v>
+        <v>10380.74721069614</v>
       </c>
     </row>
     <row r="199">
@@ -4001,7 +4001,7 @@
         <v>10154.70621812571</v>
       </c>
       <c r="D199" s="3" t="n">
-        <v>10455.03213155423</v>
+        <v>10455.03050378326</v>
       </c>
     </row>
     <row r="200">
@@ -4017,7 +4017,7 @@
         <v>10022.49041373023</v>
       </c>
       <c r="D200" s="3" t="n">
-        <v>10753.49307903603</v>
+        <v>10753.49226665595</v>
       </c>
     </row>
     <row r="201">
@@ -4033,7 +4033,7 @@
         <v>10046.3441664534</v>
       </c>
       <c r="D201" s="3" t="n">
-        <v>10279.55836842275</v>
+        <v>10279.55917361814</v>
       </c>
     </row>
     <row r="202">
@@ -4129,7 +4129,7 @@
         <v>9711.715678408818</v>
       </c>
       <c r="D207" s="3" t="n">
-        <v>9839.311380297237</v>
+        <v>9839.312192335205</v>
       </c>
     </row>
     <row r="208">
@@ -4161,7 +4161,7 @@
         <v>9853.472775908978</v>
       </c>
       <c r="D209" s="3" t="n">
-        <v>10212.75582607642</v>
+        <v>10212.75417800034</v>
       </c>
     </row>
     <row r="210">
@@ -4177,7 +4177,7 @@
         <v>9853.472775908978</v>
       </c>
       <c r="D210" s="3" t="n">
-        <v>10212.75582607642</v>
+        <v>10212.75417800034</v>
       </c>
     </row>
     <row r="211">
@@ -4193,7 +4193,7 @@
         <v>9853.472775908978</v>
       </c>
       <c r="D211" s="3" t="n">
-        <v>10212.75582607642</v>
+        <v>10212.75417800034</v>
       </c>
     </row>
     <row r="212">
@@ -4209,7 +4209,7 @@
         <v>9824.166707137001</v>
       </c>
       <c r="D212" s="3" t="n">
-        <v>10150.72875228335</v>
+        <v>10150.73039702368</v>
       </c>
     </row>
     <row r="213">
@@ -4257,7 +4257,7 @@
         <v>9545.423678650495</v>
       </c>
       <c r="D215" s="3" t="n">
-        <v>9813.001639282211</v>
+        <v>9813.00082257426</v>
       </c>
     </row>
     <row r="216">
@@ -4273,7 +4273,7 @@
         <v>9514.755310808532</v>
       </c>
       <c r="D216" s="3" t="n">
-        <v>9718.685976585801</v>
+        <v>9718.68678509133</v>
       </c>
     </row>
     <row r="217">
@@ -4289,7 +4289,7 @@
         <v>9514.755310808532</v>
       </c>
       <c r="D217" s="3" t="n">
-        <v>9718.685976585801</v>
+        <v>9718.68678509133</v>
       </c>
     </row>
     <row r="218">
@@ -4305,7 +4305,7 @@
         <v>9514.755310808532</v>
       </c>
       <c r="D218" s="3" t="n">
-        <v>9718.685976585801</v>
+        <v>9718.68678509133</v>
       </c>
     </row>
     <row r="219">
@@ -4321,7 +4321,7 @@
         <v>9627.206339536717</v>
       </c>
       <c r="D219" s="3" t="n">
-        <v>9909.109934088126</v>
+        <v>9909.112361708632</v>
       </c>
     </row>
     <row r="220">
@@ -4337,7 +4337,7 @@
         <v>9403.666581150335</v>
       </c>
       <c r="D220" s="3" t="n">
-        <v>9730.155231691291</v>
+        <v>9730.154430986284</v>
       </c>
     </row>
     <row r="221">
@@ -4353,7 +4353,7 @@
         <v>9578.136535020394</v>
       </c>
       <c r="D221" s="3" t="n">
-        <v>9766.312726495222</v>
+        <v>9766.311929852929</v>
       </c>
     </row>
     <row r="222">
@@ -4369,7 +4369,7 @@
         <v>9720.575821978502</v>
       </c>
       <c r="D222" s="3" t="n">
-        <v>10007.98201316411</v>
+        <v>10007.97961207536</v>
       </c>
     </row>
     <row r="223">
@@ -4385,7 +4385,7 @@
         <v>9909.357195544097</v>
       </c>
       <c r="D223" s="3" t="n">
-        <v>10209.39966974313</v>
+        <v>10209.39887283575</v>
       </c>
     </row>
     <row r="224">
@@ -4401,7 +4401,7 @@
         <v>9909.357195544097</v>
       </c>
       <c r="D224" s="3" t="n">
-        <v>10209.39966974313</v>
+        <v>10209.39887283575</v>
       </c>
     </row>
     <row r="225">
@@ -4417,7 +4417,7 @@
         <v>9909.357195544097</v>
       </c>
       <c r="D225" s="3" t="n">
-        <v>10209.39966974313</v>
+        <v>10209.39887283575</v>
       </c>
     </row>
     <row r="226">
@@ -4433,7 +4433,7 @@
         <v>9970.012781693031</v>
       </c>
       <c r="D226" s="3" t="n">
-        <v>10210.82410030833</v>
+        <v>10210.82330328976</v>
       </c>
     </row>
     <row r="227">
@@ -4449,7 +4449,7 @@
         <v>9880.733316230067</v>
       </c>
       <c r="D227" s="3" t="n">
-        <v>10113.86742933933</v>
+        <v>10113.8690171499</v>
       </c>
     </row>
     <row r="228">
@@ -4465,7 +4465,7 @@
         <v>9870.510873590398</v>
       </c>
       <c r="D228" s="3" t="n">
-        <v>10068.9179386258</v>
+        <v>10068.9171418039</v>
       </c>
     </row>
     <row r="229">
@@ -4481,7 +4481,7 @@
         <v>9891.637948327685</v>
       </c>
       <c r="D229" s="3" t="n">
-        <v>10337.6520466411</v>
+        <v>10337.65124384056</v>
       </c>
     </row>
     <row r="230">
@@ -4545,7 +4545,7 @@
         <v>9948.885706955743</v>
       </c>
       <c r="D233" s="3" t="n">
-        <v>10130.60690407328</v>
+        <v>10130.60451181163</v>
       </c>
     </row>
     <row r="234">
@@ -4561,7 +4561,7 @@
         <v>9910.720534537037</v>
       </c>
       <c r="D234" s="3" t="n">
-        <v>10260.91140840647</v>
+        <v>10260.91220841011</v>
       </c>
     </row>
     <row r="235">
@@ -4593,7 +4593,7 @@
         <v>9835.753528692567</v>
       </c>
       <c r="D236" s="3" t="n">
-        <v>9883.713426747825</v>
+        <v>9883.715022837747</v>
       </c>
     </row>
     <row r="237">
@@ -4609,7 +4609,7 @@
         <v>9537.926874073753</v>
       </c>
       <c r="D237" s="3" t="n">
-        <v>9686.101774960729</v>
+        <v>9686.104191291262</v>
       </c>
     </row>
     <row r="238">
@@ -4625,7 +4625,7 @@
         <v>9537.926874073753</v>
       </c>
       <c r="D238" s="3" t="n">
-        <v>9686.101774960729</v>
+        <v>9686.104191291262</v>
       </c>
     </row>
     <row r="239">
@@ -4641,7 +4641,7 @@
         <v>9537.926874073753</v>
       </c>
       <c r="D239" s="3" t="n">
-        <v>9686.101774960729</v>
+        <v>9686.104191291262</v>
       </c>
     </row>
     <row r="240">
@@ -4657,7 +4657,7 @@
         <v>9306.89031111063</v>
       </c>
       <c r="D240" s="3" t="n">
-        <v>9433.124147304201</v>
+        <v>9433.126593399656</v>
       </c>
     </row>
     <row r="241">
@@ -4673,7 +4673,7 @@
         <v>9236.69343185702</v>
       </c>
       <c r="D241" s="3" t="n">
-        <v>9472.280213902814</v>
+        <v>9472.279392678734</v>
       </c>
     </row>
     <row r="242">
@@ -4689,7 +4689,7 @@
         <v>9306.209161575638</v>
       </c>
       <c r="D242" s="3" t="n">
-        <v>9583.904601506609</v>
+        <v>9583.906239951884</v>
       </c>
     </row>
     <row r="243">
@@ -4721,7 +4721,7 @@
         <v>9036.32523673586</v>
       </c>
       <c r="D244" s="3" t="n">
-        <v>9193.128344446372</v>
+        <v>9193.125911540021</v>
       </c>
     </row>
     <row r="245">
@@ -4737,7 +4737,7 @@
         <v>9036.32523673586</v>
       </c>
       <c r="D245" s="3" t="n">
-        <v>9193.128344446372</v>
+        <v>9193.125911540021</v>
       </c>
     </row>
     <row r="246">
@@ -4753,7 +4753,7 @@
         <v>9036.32523673586</v>
       </c>
       <c r="D246" s="3" t="n">
-        <v>9193.128344446372</v>
+        <v>9193.125911540021</v>
       </c>
     </row>
     <row r="247">
@@ -4769,7 +4769,7 @@
         <v>9081.306064196317</v>
       </c>
       <c r="D247" s="3" t="n">
-        <v>9241.705217688814</v>
+        <v>9241.702771926884</v>
       </c>
     </row>
     <row r="248">
@@ -4801,7 +4801,7 @@
         <v>9167.859891596352</v>
       </c>
       <c r="D249" s="3" t="n">
-        <v>9420.165240778908</v>
+        <v>9420.164428715298</v>
       </c>
     </row>
     <row r="250">
@@ -4833,7 +4833,7 @@
         <v>9404.348770608283</v>
       </c>
       <c r="D251" s="3" t="n">
-        <v>9826.62882230303</v>
+        <v>9826.627196242851</v>
       </c>
     </row>
     <row r="252">
@@ -4849,7 +4849,7 @@
         <v>9404.348770608283</v>
       </c>
       <c r="D252" s="3" t="n">
-        <v>9826.62882230303</v>
+        <v>9826.627196242851</v>
       </c>
     </row>
     <row r="253">
@@ -4865,7 +4865,7 @@
         <v>9404.348770608283</v>
       </c>
       <c r="D253" s="3" t="n">
-        <v>9826.62882230303</v>
+        <v>9826.627196242851</v>
       </c>
     </row>
     <row r="254">
@@ -4881,7 +4881,7 @@
         <v>9435.69828798524</v>
       </c>
       <c r="D254" s="3" t="n">
-        <v>9746.457088827809</v>
+        <v>9746.460326784303</v>
       </c>
     </row>
     <row r="255">
@@ -4913,7 +4913,7 @@
         <v>9347.782161515217</v>
       </c>
       <c r="D256" s="3" t="n">
-        <v>9578.141639772422</v>
+        <v>9578.140827007393</v>
       </c>
     </row>
     <row r="257">
@@ -4929,7 +4929,7 @@
         <v>9255.776018066374</v>
       </c>
       <c r="D257" s="3" t="n">
-        <v>9570.307993794679</v>
+        <v>9570.309631299133</v>
       </c>
     </row>
     <row r="258">
@@ -5009,7 +5009,7 @@
         <v>9324.610598249998</v>
       </c>
       <c r="D262" s="3" t="n">
-        <v>9702.244174505315</v>
+        <v>9702.244994309516</v>
       </c>
     </row>
     <row r="263">
@@ -5041,7 +5041,7 @@
         <v>9719.21248298556</v>
       </c>
       <c r="D264" s="3" t="n">
-        <v>10120.18654278726</v>
+        <v>10120.18570312255</v>
       </c>
     </row>
     <row r="265">
@@ -5057,7 +5057,7 @@
         <v>9786.683724176242</v>
       </c>
       <c r="D265" s="3" t="n">
-        <v>10128.34163878475</v>
+        <v>10128.33995671834</v>
       </c>
     </row>
     <row r="266">
@@ -5073,7 +5073,7 @@
         <v>9786.683724176242</v>
       </c>
       <c r="D266" s="3" t="n">
-        <v>10128.34163878475</v>
+        <v>10128.33995671834</v>
       </c>
     </row>
     <row r="267">
@@ -5089,7 +5089,7 @@
         <v>9786.683724176242</v>
       </c>
       <c r="D267" s="3" t="n">
-        <v>10128.34163878475</v>
+        <v>10128.33995671834</v>
       </c>
     </row>
     <row r="268">
@@ -5105,7 +5105,7 @@
         <v>9721.938121048488</v>
       </c>
       <c r="D268" s="3" t="n">
-        <v>10016.30454749977</v>
+        <v>10016.30538884087</v>
       </c>
     </row>
     <row r="269">
@@ -5137,7 +5137,7 @@
         <v>9595.85682215976</v>
       </c>
       <c r="D270" s="3" t="n">
-        <v>10006.45204512153</v>
+        <v>10006.45034013261</v>
       </c>
     </row>
     <row r="271">
@@ -5153,7 +5153,7 @@
         <v>9513.391971815592</v>
       </c>
       <c r="D271" s="3" t="n">
-        <v>9982.550030136919</v>
+        <v>9982.550882665611</v>
       </c>
     </row>
     <row r="272">
@@ -5169,7 +5169,7 @@
         <v>9687.180776150657</v>
       </c>
       <c r="D272" s="3" t="n">
-        <v>10180.412525734</v>
+        <v>10180.41423198876</v>
       </c>
     </row>
     <row r="273">
@@ -5185,7 +5185,7 @@
         <v>9687.180776150657</v>
       </c>
       <c r="D273" s="3" t="n">
-        <v>10180.412525734</v>
+        <v>10180.41423198876</v>
       </c>
     </row>
     <row r="274">
@@ -5201,7 +5201,7 @@
         <v>9687.180776150657</v>
       </c>
       <c r="D274" s="3" t="n">
-        <v>10180.412525734</v>
+        <v>10180.41423198876</v>
       </c>
     </row>
     <row r="275">
@@ -5217,7 +5217,7 @@
         <v>9727.390437097296</v>
       </c>
       <c r="D275" s="3" t="n">
-        <v>10025.70237157408</v>
+        <v>10025.7015244168</v>
       </c>
     </row>
     <row r="276">
@@ -5249,7 +5249,7 @@
         <v>9871.874212583338</v>
       </c>
       <c r="D277" s="3" t="n">
-        <v>10225.47143783109</v>
+        <v>10225.47060185281</v>
       </c>
     </row>
     <row r="278">
@@ -5265,7 +5265,7 @@
         <v>9895.045775848559</v>
       </c>
       <c r="D278" s="3" t="n">
-        <v>10378.8458701236</v>
+        <v>10378.84922997972</v>
       </c>
     </row>
     <row r="279">
@@ -5329,7 +5329,7 @@
         <v>9893.001287320625</v>
       </c>
       <c r="D282" s="3" t="n">
-        <v>10277.43228289544</v>
+        <v>10277.43395994959</v>
       </c>
     </row>
     <row r="283">
@@ -5345,7 +5345,7 @@
         <v>9877.325488709192</v>
       </c>
       <c r="D283" s="3" t="n">
-        <v>10131.28900689967</v>
+        <v>10131.28984339967</v>
       </c>
     </row>
     <row r="284">
@@ -5361,7 +5361,7 @@
         <v>9976.828436734779</v>
       </c>
       <c r="D284" s="3" t="n">
-        <v>10492.24652753875</v>
+        <v>10492.24568316133</v>
       </c>
     </row>
     <row r="285">
@@ -5377,7 +5377,7 @@
         <v>10108.36309159527</v>
       </c>
       <c r="D285" s="3" t="n">
-        <v>10540.87369993894</v>
+        <v>10540.87286215599</v>
       </c>
     </row>
     <row r="286">
@@ -5393,7 +5393,7 @@
         <v>10201.7315341141</v>
       </c>
       <c r="D286" s="3" t="n">
-        <v>10712.34548220701</v>
+        <v>10712.34296467538</v>
       </c>
     </row>
     <row r="287">
@@ -5409,7 +5409,7 @@
         <v>10201.7315341141</v>
       </c>
       <c r="D287" s="3" t="n">
-        <v>10712.34548220701</v>
+        <v>10712.34296467538</v>
       </c>
     </row>
     <row r="288">
@@ -5425,7 +5425,7 @@
         <v>10201.7315341141</v>
       </c>
       <c r="D288" s="3" t="n">
-        <v>10712.34548220701</v>
+        <v>10712.34296467538</v>
       </c>
     </row>
     <row r="289">
@@ -5441,7 +5441,7 @@
         <v>10220.13297078846</v>
       </c>
       <c r="D289" s="3" t="n">
-        <v>10663.96789147458</v>
+        <v>10663.96705360602</v>
       </c>
     </row>
     <row r="290">
@@ -5457,7 +5457,7 @@
         <v>10222.17745931639</v>
       </c>
       <c r="D290" s="3" t="n">
-        <v>10538.78434317001</v>
+        <v>10538.78601023415</v>
       </c>
     </row>
     <row r="291">
@@ -5473,7 +5473,7 @@
         <v>10322.36155687697</v>
       </c>
       <c r="D291" s="3" t="n">
-        <v>10815.18978867365</v>
+        <v>10815.19231528845</v>
       </c>
     </row>
     <row r="292">
@@ -5489,7 +5489,7 @@
         <v>10267.83943631184</v>
       </c>
       <c r="D292" s="3" t="n">
-        <v>10692.64010827148</v>
+        <v>10692.64094290687</v>
       </c>
     </row>
     <row r="293">
@@ -5505,7 +5505,7 @@
         <v>10267.83943631184</v>
       </c>
       <c r="D293" s="3" t="n">
-        <v>10692.64010827148</v>
+        <v>10692.64094290687</v>
       </c>
     </row>
     <row r="294">
@@ -5521,7 +5521,7 @@
         <v>10336.67297657251</v>
       </c>
       <c r="D294" s="3" t="n">
-        <v>10761.00143447714</v>
+        <v>10761.00227542478</v>
       </c>
     </row>
     <row r="295">
@@ -5553,7 +5553,7 @@
         <v>10318.27153989815</v>
       </c>
       <c r="D296" s="3" t="n">
-        <v>10903.4384426822</v>
+        <v>10903.43676692806</v>
       </c>
     </row>
     <row r="297">
@@ -5569,7 +5569,7 @@
         <v>10380.29046504003</v>
       </c>
       <c r="D297" s="3" t="n">
-        <v>10805.37980880486</v>
+        <v>10805.37814812139</v>
       </c>
     </row>
     <row r="298">
@@ -5585,7 +5585,7 @@
         <v>10480.47456260061</v>
       </c>
       <c r="D298" s="3" t="n">
-        <v>10971.32574834989</v>
+        <v>10971.32657740864</v>
       </c>
     </row>
     <row r="299">
@@ -5601,7 +5601,7 @@
         <v>10480.47456260061</v>
       </c>
       <c r="D299" s="3" t="n">
-        <v>10971.32574834989</v>
+        <v>10971.32657740864</v>
       </c>
     </row>
     <row r="300">
@@ -5617,7 +5617,7 @@
         <v>10480.47456260061</v>
       </c>
       <c r="D300" s="3" t="n">
-        <v>10971.32574834989</v>
+        <v>10971.32657740864</v>
       </c>
     </row>
     <row r="301">
@@ -5633,7 +5633,7 @@
         <v>10596.33341884966</v>
       </c>
       <c r="D301" s="3" t="n">
-        <v>11081.31825841036</v>
+        <v>11081.31909234448</v>
       </c>
     </row>
     <row r="302">
@@ -5649,7 +5649,7 @@
         <v>10648.12990135187</v>
       </c>
       <c r="D302" s="3" t="n">
-        <v>11206.198919646</v>
+        <v>11206.1955529129</v>
       </c>
     </row>
     <row r="303">
@@ -5665,7 +5665,7 @@
         <v>10562.93941294477</v>
       </c>
       <c r="D303" s="3" t="n">
-        <v>11117.15756282109</v>
+        <v>11117.1567218563</v>
       </c>
     </row>
     <row r="304">
@@ -5681,7 +5681,7 @@
         <v>10640.63309677513</v>
       </c>
       <c r="D304" s="3" t="n">
-        <v>11139.03610362596</v>
+        <v>11139.03190273664</v>
       </c>
     </row>
     <row r="305">
@@ -5745,7 +5745,7 @@
         <v>10514.55075796344</v>
       </c>
       <c r="D308" s="3" t="n">
-        <v>10915.96731875029</v>
+        <v>10915.96561412068</v>
       </c>
     </row>
     <row r="309">
@@ -5761,7 +5761,7 @@
         <v>10436.1759245981</v>
       </c>
       <c r="D309" s="3" t="n">
-        <v>10994.46835569087</v>
+        <v>10994.46577411306</v>
       </c>
     </row>
     <row r="310">
@@ -5777,7 +5777,7 @@
         <v>10476.38558554474</v>
       </c>
       <c r="D310" s="3" t="n">
-        <v>10999.29236586935</v>
+        <v>10999.29494033928</v>
       </c>
     </row>
     <row r="311">
@@ -5793,7 +5793,7 @@
         <v>10528.86321758194</v>
       </c>
       <c r="D311" s="3" t="n">
-        <v>11152.13191057703</v>
+        <v>11152.13019464004</v>
       </c>
     </row>
     <row r="312">
@@ -5809,7 +5809,7 @@
         <v>10378.92712604709</v>
       </c>
       <c r="D312" s="3" t="n">
-        <v>10772.27834284843</v>
+        <v>10772.27662728787</v>
       </c>
     </row>
     <row r="313">
@@ -5825,7 +5825,7 @@
         <v>10378.92712604709</v>
       </c>
       <c r="D313" s="3" t="n">
-        <v>10772.27834284843</v>
+        <v>10772.27662728787</v>
       </c>
     </row>
     <row r="314">
@@ -5841,7 +5841,7 @@
         <v>10378.92712604709</v>
       </c>
       <c r="D314" s="3" t="n">
-        <v>10772.27834284843</v>
+        <v>10772.27662728787</v>
       </c>
     </row>
     <row r="315">
@@ -5857,7 +5857,7 @@
         <v>10192.19024100942</v>
       </c>
       <c r="D315" s="3" t="n">
-        <v>10736.15682276554</v>
+        <v>10736.15596217122</v>
       </c>
     </row>
     <row r="316">
@@ -5905,7 +5905,7 @@
         <v>9936.61877578814</v>
       </c>
       <c r="D318" s="3" t="n">
-        <v>10464.87599343516</v>
+        <v>10464.87769741481</v>
       </c>
     </row>
     <row r="319">
@@ -5985,7 +5985,7 @@
         <v>9997.955511472066</v>
       </c>
       <c r="D323" s="3" t="n">
-        <v>10405.45324467825</v>
+        <v>10405.45238525578</v>
       </c>
     </row>
     <row r="324">
@@ -6001,7 +6001,7 @@
         <v>9957.064700990433</v>
       </c>
       <c r="D324" s="3" t="n">
-        <v>10650.47446822325</v>
+        <v>10650.47273995251</v>
       </c>
     </row>
     <row r="325">
@@ -6017,7 +6017,7 @@
         <v>10101.54743655352</v>
       </c>
       <c r="D325" s="3" t="n">
-        <v>10615.25397103936</v>
+        <v>10615.25311535458</v>
       </c>
     </row>
     <row r="326">
@@ -6033,7 +6033,7 @@
         <v>10178.55997084888</v>
       </c>
       <c r="D326" s="3" t="n">
-        <v>10762.60017463291</v>
+        <v>10762.5984660518</v>
       </c>
     </row>
     <row r="327">
@@ -6049,7 +6049,7 @@
         <v>10178.55997084888</v>
       </c>
       <c r="D327" s="3" t="n">
-        <v>10762.60017463291</v>
+        <v>10762.5984660518</v>
       </c>
     </row>
     <row r="328">
@@ -6065,7 +6065,7 @@
         <v>10178.55997084888</v>
       </c>
       <c r="D328" s="3" t="n">
-        <v>10762.60017463291</v>
+        <v>10762.5984660518</v>
       </c>
     </row>
     <row r="329">
@@ -6081,7 +6081,7 @@
         <v>10251.48248816542</v>
       </c>
       <c r="D329" s="3" t="n">
-        <v>10814.12260947892</v>
+        <v>10814.12345873171</v>
       </c>
     </row>
     <row r="330">
@@ -6097,7 +6097,7 @@
         <v>10069.51572971862</v>
       </c>
       <c r="D330" s="3" t="n">
-        <v>10284.51701574656</v>
+        <v>10284.51532699172</v>
       </c>
     </row>
     <row r="331">
@@ -6113,7 +6113,7 @@
         <v>9992.503195423258</v>
       </c>
       <c r="D331" s="3" t="n">
-        <v>10476.33578493405</v>
+        <v>10476.33492807753</v>
       </c>
     </row>
     <row r="332">
@@ -6129,7 +6129,7 @@
         <v>9936.61877578814</v>
       </c>
       <c r="D332" s="3" t="n">
-        <v>10355.3258606859</v>
+        <v>10355.32757405694</v>
       </c>
     </row>
     <row r="333">
@@ -6241,7 +6241,7 @@
         <v>9670.142678469238</v>
       </c>
       <c r="D339" s="3" t="n">
-        <v>10129.62806729861</v>
+        <v>10129.62893734416</v>
       </c>
     </row>
     <row r="340">
@@ -6257,7 +6257,7 @@
         <v>9554.964971755173</v>
       </c>
       <c r="D340" s="3" t="n">
-        <v>9948.942440637264</v>
+        <v>9948.943309724902</v>
       </c>
     </row>
     <row r="341">
@@ -6305,7 +6305,7 @@
         <v>9610.850431313245</v>
       </c>
       <c r="D343" s="3" t="n">
-        <v>10274.86422005655</v>
+        <v>10274.86332874776</v>
       </c>
     </row>
     <row r="344">
@@ -6321,7 +6321,7 @@
         <v>9379.813868350122</v>
       </c>
       <c r="D344" s="3" t="n">
-        <v>9944.192152387786</v>
+        <v>9944.193033415633</v>
       </c>
     </row>
     <row r="345">
@@ -6337,7 +6337,7 @@
         <v>9445.921770547864</v>
       </c>
       <c r="D345" s="3" t="n">
-        <v>9669.519806878927</v>
+        <v>9669.518066582585</v>
       </c>
     </row>
     <row r="346">
@@ -6353,7 +6353,7 @@
         <v>9445.921770547864</v>
       </c>
       <c r="D346" s="3" t="n">
-        <v>9669.519806878927</v>
+        <v>9669.518066582585</v>
       </c>
     </row>
     <row r="347">
@@ -6369,7 +6369,7 @@
         <v>9445.921770547864</v>
       </c>
       <c r="D347" s="3" t="n">
-        <v>9669.519806878927</v>
+        <v>9669.518066582585</v>
       </c>
     </row>
     <row r="348">
@@ -6385,7 +6385,7 @@
         <v>9428.883672866445</v>
       </c>
       <c r="D348" s="3" t="n">
-        <v>9962.171143015794</v>
+        <v>9962.172016439876</v>
       </c>
     </row>
     <row r="349">
@@ -6433,7 +6433,7 @@
         <v>9680.365121108907</v>
       </c>
       <c r="D351" s="3" t="n">
-        <v>10020.18767735824</v>
+        <v>10020.18854035601</v>
       </c>
     </row>
     <row r="352">
@@ -6449,7 +6449,7 @@
         <v>9490.901558085365</v>
       </c>
       <c r="D352" s="3" t="n">
-        <v>9862.037019199062</v>
+        <v>9862.037892948194</v>
       </c>
     </row>
     <row r="353">
@@ -6465,7 +6465,7 @@
         <v>9490.901558085365</v>
       </c>
       <c r="D353" s="3" t="n">
-        <v>9862.037019199062</v>
+        <v>9862.037892948194</v>
       </c>
     </row>
     <row r="354">
@@ -6481,7 +6481,7 @@
         <v>9490.901558085365</v>
       </c>
       <c r="D354" s="3" t="n">
-        <v>9862.037019199062</v>
+        <v>9862.037892948194</v>
       </c>
     </row>
     <row r="355">
@@ -6497,7 +6497,7 @@
         <v>9450.691897138724</v>
       </c>
       <c r="D355" s="3" t="n">
-        <v>9841.056333513774</v>
+        <v>9841.057212112524</v>
       </c>
     </row>
     <row r="356">
@@ -6529,7 +6529,7 @@
         <v>9354.596776634013</v>
       </c>
       <c r="D357" s="3" t="n">
-        <v>9781.489925464426</v>
+        <v>9781.491688974122</v>
       </c>
     </row>
     <row r="358">
@@ -6545,7 +6545,7 @@
         <v>9364.138069738689</v>
       </c>
       <c r="D358" s="3" t="n">
-        <v>10031.55065122028</v>
+        <v>10031.54888913051</v>
       </c>
     </row>
     <row r="359">
@@ -6561,7 +6561,7 @@
         <v>9396.169776573593</v>
       </c>
       <c r="D359" s="3" t="n">
-        <v>9759.35978818452</v>
+        <v>9759.358033929242</v>
       </c>
     </row>
     <row r="360">
@@ -6577,7 +6577,7 @@
         <v>9396.169776573593</v>
       </c>
       <c r="D360" s="3" t="n">
-        <v>9759.35978818452</v>
+        <v>9759.358033929242</v>
       </c>
     </row>
     <row r="361">
@@ -6593,7 +6593,7 @@
         <v>9396.169776573593</v>
       </c>
       <c r="D361" s="3" t="n">
-        <v>9759.35978818452</v>
+        <v>9759.358033929242</v>
       </c>
     </row>
     <row r="362">
@@ -6609,7 +6609,7 @@
         <v>9484.768092501563</v>
       </c>
       <c r="D362" s="3" t="n">
-        <v>10022.44291000311</v>
+        <v>10022.44378820837</v>
       </c>
     </row>
     <row r="363">
@@ -6641,7 +6641,7 @@
         <v>9542.015851129621</v>
       </c>
       <c r="D364" s="3" t="n">
-        <v>9941.258419244083</v>
+        <v>9941.26102060519</v>
       </c>
     </row>
     <row r="365">
@@ -6657,7 +6657,7 @@
         <v>9557.691649741055</v>
       </c>
       <c r="D365" s="3" t="n">
-        <v>9956.206964399957</v>
+        <v>9956.207840167641</v>
       </c>
     </row>
     <row r="366">
@@ -6673,7 +6673,7 @@
         <v>9516.799799336466</v>
       </c>
       <c r="D366" s="3" t="n">
-        <v>10185.20785895927</v>
+        <v>10185.20610964793</v>
       </c>
     </row>
     <row r="367">
@@ -6689,7 +6689,7 @@
         <v>9516.799799336466</v>
       </c>
       <c r="D367" s="3" t="n">
-        <v>10185.20785895927</v>
+        <v>10185.20610964793</v>
       </c>
     </row>
     <row r="368">
@@ -6705,7 +6705,7 @@
         <v>9516.799799336466</v>
       </c>
       <c r="D368" s="3" t="n">
-        <v>10185.20785895927</v>
+        <v>10185.20610964793</v>
       </c>
     </row>
     <row r="369">
@@ -6721,7 +6721,7 @@
         <v>9615.620557904105</v>
       </c>
       <c r="D369" s="3" t="n">
-        <v>10224.949805836</v>
+        <v>10224.95154074381</v>
       </c>
     </row>
     <row r="370">
@@ -6737,7 +6737,7 @@
         <v>9719.893632520554</v>
       </c>
       <c r="D370" s="3" t="n">
-        <v>10360.47003598447</v>
+        <v>10360.46917084846</v>
       </c>
     </row>
     <row r="371">
@@ -6753,7 +6753,7 @@
         <v>9738.976218729907</v>
       </c>
       <c r="D371" s="3" t="n">
-        <v>10202.71339826993</v>
+        <v>10202.71511513077</v>
       </c>
     </row>
     <row r="372">
@@ -6769,7 +6769,7 @@
         <v>9711.034528873824</v>
       </c>
       <c r="D372" s="3" t="n">
-        <v>10019.31133258263</v>
+        <v>10019.31048505759</v>
       </c>
     </row>
     <row r="373">
@@ -6785,7 +6785,7 @@
         <v>9788.728212704178</v>
       </c>
       <c r="D373" s="3" t="n">
-        <v>10385.41979564042</v>
+        <v>10385.42151179976</v>
       </c>
     </row>
     <row r="374">
@@ -6801,7 +6801,7 @@
         <v>9788.728212704178</v>
       </c>
       <c r="D374" s="3" t="n">
-        <v>10385.41979564042</v>
+        <v>10385.42151179976</v>
       </c>
     </row>
     <row r="375">
@@ -6817,7 +6817,7 @@
         <v>9788.728212704178</v>
       </c>
       <c r="D375" s="3" t="n">
-        <v>10385.41979564042</v>
+        <v>10385.42151179976</v>
       </c>
     </row>
     <row r="376">
@@ -6833,7 +6833,7 @@
         <v>9860.287391027774</v>
       </c>
       <c r="D376" s="3" t="n">
-        <v>10323.66220183298</v>
+        <v>10323.66134264989</v>
       </c>
     </row>
     <row r="377">
@@ -6849,7 +6849,7 @@
         <v>9877.325488709192</v>
       </c>
       <c r="D377" s="3" t="n">
-        <v>10349.90722013383</v>
+        <v>10349.90462467447</v>
       </c>
     </row>
     <row r="378">
@@ -6865,7 +6865,7 @@
         <v>9812.580925504391</v>
       </c>
       <c r="D378" s="3" t="n">
-        <v>10098.74105316414</v>
+        <v>10098.7427849415</v>
       </c>
     </row>
     <row r="379">
@@ -6881,7 +6881,7 @@
         <v>9707.62670135295</v>
       </c>
       <c r="D379" s="3" t="n">
-        <v>10059.42288413633</v>
+        <v>10059.4246271185</v>
       </c>
     </row>
     <row r="380">
@@ -6945,7 +6945,7 @@
         <v>9662.645873892496</v>
       </c>
       <c r="D383" s="3" t="n">
-        <v>10183.11995927905</v>
+        <v>10183.11909782945</v>
       </c>
     </row>
     <row r="384">
@@ -6961,7 +6961,7 @@
         <v>9754.652017341339</v>
       </c>
       <c r="D384" s="3" t="n">
-        <v>10146.27253693294</v>
+        <v>10146.27168320685</v>
       </c>
     </row>
     <row r="385">
@@ -7009,7 +7009,7 @@
         <v>9842.568143811361</v>
       </c>
       <c r="D387" s="3" t="n">
-        <v>10404.51527618192</v>
+        <v>10404.51359781042</v>
       </c>
     </row>
     <row r="388">
@@ -7025,7 +7025,7 @@
         <v>9842.568143811361</v>
       </c>
       <c r="D388" s="3" t="n">
-        <v>10404.51527618192</v>
+        <v>10404.51359781042</v>
       </c>
     </row>
     <row r="389">
@@ -7041,7 +7041,7 @@
         <v>9842.568143811361</v>
       </c>
       <c r="D389" s="3" t="n">
-        <v>10404.51527618192</v>
+        <v>10404.51359781042</v>
       </c>
     </row>
     <row r="390">
@@ -7073,7 +7073,7 @@
         <v>9931.847609274324</v>
       </c>
       <c r="D391" s="3" t="n">
-        <v>10275.89701105396</v>
+        <v>10275.89535334694</v>
       </c>
     </row>
     <row r="392">
@@ -7105,7 +7105,7 @@
         <v>9754.652017341339</v>
       </c>
       <c r="D393" s="3" t="n">
-        <v>10092.23563655831</v>
+        <v>10092.23481374338</v>
       </c>
     </row>
     <row r="394">
@@ -7121,7 +7121,7 @@
         <v>9825.530046129943</v>
       </c>
       <c r="D394" s="3" t="n">
-        <v>10170.62180807231</v>
+        <v>10170.62263353013</v>
       </c>
     </row>
     <row r="395">
@@ -7137,7 +7137,7 @@
         <v>9825.530046129943</v>
       </c>
       <c r="D395" s="3" t="n">
-        <v>10170.62180807231</v>
+        <v>10170.62263353013</v>
       </c>
     </row>
     <row r="396">
@@ -7153,7 +7153,7 @@
         <v>9825.530046129943</v>
       </c>
       <c r="D396" s="3" t="n">
-        <v>10170.62180807231</v>
+        <v>10170.62263353013</v>
       </c>
     </row>
     <row r="397">
@@ -7185,7 +7185,7 @@
         <v>9927.077482683462</v>
       </c>
       <c r="D398" s="3" t="n">
-        <v>10386.32111243607</v>
+        <v>10386.32194724258</v>
       </c>
     </row>
     <row r="399">
@@ -7201,7 +7201,7 @@
         <v>9964.561505567175</v>
       </c>
       <c r="D399" s="3" t="n">
-        <v>10385.4855510186</v>
+        <v>10385.48721004265</v>
       </c>
     </row>
     <row r="400">
@@ -7217,7 +7217,7 @@
         <v>9980.917413790647</v>
       </c>
       <c r="D400" s="3" t="n">
-        <v>10280.64857687737</v>
+        <v>10280.65021915428</v>
       </c>
     </row>
     <row r="401">
@@ -7233,7 +7233,7 @@
         <v>9967.287143630103</v>
       </c>
       <c r="D401" s="3" t="n">
-        <v>10286.37928619299</v>
+        <v>10286.37764263306</v>
       </c>
     </row>
     <row r="402">
@@ -7249,7 +7249,7 @@
         <v>9967.287143630103</v>
       </c>
       <c r="D402" s="3" t="n">
-        <v>10286.37928619299</v>
+        <v>10286.37764263306</v>
       </c>
     </row>
     <row r="403">
@@ -7265,7 +7265,7 @@
         <v>9967.287143630103</v>
       </c>
       <c r="D403" s="3" t="n">
-        <v>10286.37928619299</v>
+        <v>10286.37764263306</v>
       </c>
     </row>
     <row r="404">
@@ -7281,7 +7281,7 @@
         <v>9891.637948327685</v>
       </c>
       <c r="D404" s="3" t="n">
-        <v>10161.85353905892</v>
+        <v>10161.85271406286</v>
       </c>
     </row>
     <row r="405">
@@ -7297,7 +7297,7 @@
         <v>9833.026850706685</v>
       </c>
       <c r="D405" s="3" t="n">
-        <v>10165.95775267847</v>
+        <v>10165.96023292665</v>
       </c>
     </row>
     <row r="406">
@@ -7329,7 +7329,7 @@
         <v>9994.547683951192</v>
       </c>
       <c r="D407" s="3" t="n">
-        <v>10398.25595472334</v>
+        <v>10398.25759556349</v>
       </c>
     </row>
     <row r="408">
@@ -7409,7 +7409,7 @@
         <v>9726.709287562304</v>
       </c>
       <c r="D412" s="3" t="n">
-        <v>9983.856747195488</v>
+        <v>9983.857562021814</v>
       </c>
     </row>
     <row r="413">
@@ -7425,7 +7425,7 @@
         <v>9674.231655525105</v>
       </c>
       <c r="D413" s="3" t="n">
-        <v>9993.448176448212</v>
+        <v>9993.446542450522</v>
       </c>
     </row>
     <row r="414">
@@ -7505,7 +7505,7 @@
         <v>9701.493235769149</v>
       </c>
       <c r="D418" s="3" t="n">
-        <v>10089.34199138731</v>
+        <v>10089.34280425491</v>
       </c>
     </row>
     <row r="419">
@@ -7521,7 +7521,7 @@
         <v>9841.204804818421</v>
       </c>
       <c r="D419" s="3" t="n">
-        <v>10146.89202887309</v>
+        <v>10146.89121751079</v>
       </c>
     </row>
     <row r="420">
@@ -7553,7 +7553,7 @@
         <v>9482.042454438635</v>
       </c>
       <c r="D421" s="3" t="n">
-        <v>9711.389013377973</v>
+        <v>9711.389814510603</v>
       </c>
     </row>
     <row r="422">
@@ -7617,7 +7617,7 @@
         <v>9368.909236252504</v>
       </c>
       <c r="D425" s="3" t="n">
-        <v>9597.442619871545</v>
+        <v>9597.441811827935</v>
       </c>
     </row>
     <row r="426">
@@ -7633,7 +7633,7 @@
         <v>9333.469701896725</v>
       </c>
       <c r="D426" s="3" t="n">
-        <v>9583.820376128759</v>
+        <v>9583.821181922882</v>
       </c>
     </row>
     <row r="427">
@@ -7649,7 +7649,7 @@
         <v>9505.89516723885</v>
       </c>
       <c r="D427" s="3" t="n">
-        <v>9715.763422297092</v>
+        <v>9715.765836856828</v>
       </c>
     </row>
     <row r="428">
@@ -7665,7 +7665,7 @@
         <v>9358.004604154887</v>
       </c>
       <c r="D428" s="3" t="n">
-        <v>9592.423267421689</v>
+        <v>9592.425685830451</v>
       </c>
     </row>
     <row r="429">
@@ -7681,7 +7681,7 @@
         <v>9380.495017885114</v>
       </c>
       <c r="D429" s="3" t="n">
-        <v>9653.746162121659</v>
+        <v>9653.744548822846</v>
       </c>
     </row>
     <row r="430">
@@ -7697,7 +7697,7 @@
         <v>9380.495017885114</v>
       </c>
       <c r="D430" s="3" t="n">
-        <v>9653.746162121659</v>
+        <v>9653.744548822846</v>
       </c>
     </row>
     <row r="431">
@@ -7713,7 +7713,7 @@
         <v>9380.495017885114</v>
       </c>
       <c r="D431" s="3" t="n">
-        <v>9653.746162121659</v>
+        <v>9653.744548822846</v>
       </c>
     </row>
     <row r="432">
@@ -7729,7 +7729,7 @@
         <v>9380.495017885114</v>
       </c>
       <c r="D432" s="3" t="n">
-        <v>9595.400608959033</v>
+        <v>9595.399005410718</v>
       </c>
     </row>
     <row r="433">
@@ -7745,7 +7745,7 @@
         <v>9381.858356878056</v>
       </c>
       <c r="D433" s="3" t="n">
-        <v>9582.336137303335</v>
+        <v>9582.335333450737</v>
       </c>
     </row>
     <row r="434">
@@ -7777,7 +7777,7 @@
         <v>9399.577604094467</v>
       </c>
       <c r="D435" s="3" t="n">
-        <v>9643.532147492964</v>
+        <v>9643.531342810682</v>
       </c>
     </row>
     <row r="436">
@@ -7793,7 +7793,7 @@
         <v>9307.572500568578</v>
       </c>
       <c r="D436" s="3" t="n">
-        <v>9589.708614957173</v>
+        <v>9589.70701034824</v>
       </c>
     </row>
     <row r="437">
@@ -7809,7 +7809,7 @@
         <v>9307.572500568578</v>
       </c>
       <c r="D437" s="3" t="n">
-        <v>9589.708614957173</v>
+        <v>9589.70701034824</v>
       </c>
     </row>
     <row r="438">
@@ -7825,7 +7825,7 @@
         <v>9307.572500568578</v>
       </c>
       <c r="D438" s="3" t="n">
-        <v>9589.708614957173</v>
+        <v>9589.70701034824</v>
       </c>
     </row>
     <row r="439">
@@ -7841,7 +7841,7 @@
         <v>9522.252115385276</v>
       </c>
       <c r="D439" s="3" t="n">
-        <v>9545.850311287244</v>
+        <v>9545.848714016951</v>
       </c>
     </row>
     <row r="440">
@@ -7857,7 +7857,7 @@
         <v>9427.520333873505</v>
       </c>
       <c r="D440" s="3" t="n">
-        <v>9534.167936708529</v>
+        <v>9534.170339798651</v>
       </c>
     </row>
     <row r="441">
@@ -7889,7 +7889,7 @@
         <v>9458.188701715468</v>
       </c>
       <c r="D442" s="3" t="n">
-        <v>9562.009916032503</v>
+        <v>9562.01233528824</v>
       </c>
     </row>
     <row r="443">
@@ -7905,7 +7905,7 @@
         <v>9548.831506171371</v>
       </c>
       <c r="D443" s="3" t="n">
-        <v>9859.50936580752</v>
+        <v>9859.510991542733</v>
       </c>
     </row>
     <row r="444">
@@ -7921,7 +7921,7 @@
         <v>9548.831506171371</v>
       </c>
       <c r="D444" s="3" t="n">
-        <v>9859.50936580752</v>
+        <v>9859.510991542733</v>
       </c>
     </row>
     <row r="445">
@@ -7937,7 +7937,7 @@
         <v>9548.831506171371</v>
       </c>
       <c r="D445" s="3" t="n">
-        <v>9859.50936580752</v>
+        <v>9859.510991542733</v>
       </c>
     </row>
     <row r="446">
@@ -7953,7 +7953,7 @@
         <v>9605.398115264436</v>
       </c>
       <c r="D446" s="3" t="n">
-        <v>9729.913142166473</v>
+        <v>9729.91233952849</v>
       </c>
     </row>
     <row r="447">
@@ -7969,7 +7969,7 @@
         <v>9503.850678710916</v>
       </c>
       <c r="D447" s="3" t="n">
-        <v>9727.981004397037</v>
+        <v>9727.98180128734</v>
       </c>
     </row>
     <row r="448">
@@ -7985,7 +7985,7 @@
         <v>9588.360017583018</v>
       </c>
       <c r="D448" s="3" t="n">
-        <v>9845.734755779507</v>
+        <v>9845.733959316822</v>
       </c>
     </row>
     <row r="449">
@@ -8001,7 +8001,7 @@
         <v>9615.620557904105</v>
       </c>
       <c r="D449" s="3" t="n">
-        <v>9856.748321877492</v>
+        <v>9856.7491163387</v>
       </c>
     </row>
     <row r="450">
@@ -8017,7 +8017,7 @@
         <v>9646.971115204016</v>
       </c>
       <c r="D450" s="3" t="n">
-        <v>9809.124675509973</v>
+        <v>9809.125463077331</v>
       </c>
     </row>
     <row r="451">
@@ -8033,7 +8033,7 @@
         <v>9646.971115204016</v>
       </c>
       <c r="D451" s="3" t="n">
-        <v>9809.124675509973</v>
+        <v>9809.125463077331</v>
       </c>
     </row>
     <row r="452">
@@ -8049,7 +8049,7 @@
         <v>9646.971115204016</v>
       </c>
       <c r="D452" s="3" t="n">
-        <v>9809.124675509973</v>
+        <v>9809.125463077331</v>
       </c>
     </row>
     <row r="453">
@@ -8065,7 +8065,7 @@
         <v>9696.040919720339</v>
       </c>
       <c r="D453" s="3" t="n">
-        <v>9841.402801086891</v>
+        <v>9841.403591245837</v>
       </c>
     </row>
     <row r="454">
@@ -8081,7 +8081,7 @@
         <v>9723.301460041428</v>
       </c>
       <c r="D454" s="3" t="n">
-        <v>9818.378449594384</v>
+        <v>9818.377659837433</v>
       </c>
     </row>
     <row r="455">
@@ -8097,7 +8097,7 @@
         <v>9668.098189941304</v>
       </c>
       <c r="D455" s="3" t="n">
-        <v>9696.333105396681</v>
+        <v>9696.332312945475</v>
       </c>
     </row>
     <row r="456">
@@ -8193,7 +8193,7 @@
         <v>9716.486844922634</v>
       </c>
       <c r="D461" s="3" t="n">
-        <v>9838.239417438763</v>
+        <v>9838.240203988296</v>
       </c>
     </row>
     <row r="462">
@@ -8209,7 +8209,7 @@
         <v>9639.474310627274</v>
       </c>
       <c r="D462" s="3" t="n">
-        <v>9829.406942749967</v>
+        <v>9829.404586103621</v>
       </c>
     </row>
     <row r="463">
@@ -8225,7 +8225,7 @@
         <v>9754.652017341339</v>
       </c>
       <c r="D463" s="3" t="n">
-        <v>9906.59777581603</v>
+        <v>9906.596209593768</v>
       </c>
     </row>
     <row r="464">
@@ -8241,7 +8241,7 @@
         <v>9844.612632339295</v>
       </c>
       <c r="D464" s="3" t="n">
-        <v>9954.521463186975</v>
+        <v>9954.522248282507</v>
       </c>
     </row>
     <row r="465">
@@ -8257,7 +8257,7 @@
         <v>9844.612632339295</v>
       </c>
       <c r="D465" s="3" t="n">
-        <v>9954.521463186975</v>
+        <v>9954.522248282507</v>
       </c>
     </row>
     <row r="466">
@@ -8273,7 +8273,7 @@
         <v>9844.612632339295</v>
       </c>
       <c r="D466" s="3" t="n">
-        <v>9954.521463186975</v>
+        <v>9954.522248282507</v>
       </c>
     </row>
     <row r="467">
@@ -8321,7 +8321,7 @@
         <v>9779.1869195995</v>
       </c>
       <c r="D469" s="3" t="n">
-        <v>10111.2307160404</v>
+        <v>10111.23229107243</v>
       </c>
     </row>
     <row r="470">
@@ -8337,7 +8337,7 @@
         <v>10010.22348256262</v>
       </c>
       <c r="D470" s="3" t="n">
-        <v>10116.923527173</v>
+        <v>10116.92430382648</v>
       </c>
     </row>
     <row r="471">
@@ -8353,7 +8353,7 @@
         <v>10062.01892514187</v>
       </c>
       <c r="D471" s="3" t="n">
-        <v>10108.26810416605</v>
+        <v>10108.26653551464</v>
       </c>
     </row>
     <row r="472">
@@ -8369,7 +8369,7 @@
         <v>10062.01892514187</v>
       </c>
       <c r="D472" s="3" t="n">
-        <v>10108.26810416605</v>
+        <v>10108.26653551464</v>
       </c>
     </row>
     <row r="473">
@@ -8385,7 +8385,7 @@
         <v>10062.01892514187</v>
       </c>
       <c r="D473" s="3" t="n">
-        <v>10108.26810416605</v>
+        <v>10108.26653551464</v>
       </c>
     </row>
     <row r="474">
@@ -8401,7 +8401,7 @@
         <v>10010.22348256262</v>
       </c>
       <c r="D474" s="3" t="n">
-        <v>10152.87271131546</v>
+        <v>10152.87350394631</v>
       </c>
     </row>
     <row r="475">
@@ -8417,7 +8417,7 @@
         <v>10032.0317068349</v>
       </c>
       <c r="D475" s="3" t="n">
-        <v>10343.26397494951</v>
+        <v>10343.26238080966</v>
       </c>
     </row>
     <row r="476">
@@ -8449,7 +8449,7 @@
         <v>10033.39504582785</v>
       </c>
       <c r="D477" s="3" t="n">
-        <v>10155.62218775547</v>
+        <v>10155.62138957361</v>
       </c>
     </row>
     <row r="478">
@@ -8465,7 +8465,7 @@
         <v>9982.280752783588</v>
       </c>
       <c r="D478" s="3" t="n">
-        <v>10154.23296635731</v>
+        <v>10154.2337625719</v>
       </c>
     </row>
     <row r="479">
@@ -8481,7 +8481,7 @@
         <v>9982.280752783588</v>
       </c>
       <c r="D479" s="3" t="n">
-        <v>10154.23296635731</v>
+        <v>10154.2337625719</v>
       </c>
     </row>
     <row r="480">
@@ -8497,7 +8497,7 @@
         <v>9982.280752783588</v>
       </c>
       <c r="D480" s="3" t="n">
-        <v>10154.23296635731</v>
+        <v>10154.2337625719</v>
       </c>
     </row>
     <row r="481">
@@ -8513,7 +8513,7 @@
         <v>10051.7964825022</v>
       </c>
       <c r="D481" s="3" t="n">
-        <v>10335.56645086846</v>
+        <v>10335.56564983842</v>
       </c>
     </row>
     <row r="482">
@@ -8529,7 +8529,7 @@
         <v>10006.81565504175</v>
       </c>
       <c r="D482" s="3" t="n">
-        <v>10280.06948608111</v>
+        <v>10280.06868898551</v>
       </c>
     </row>
     <row r="483">
@@ -8545,7 +8545,7 @@
         <v>10094.05063197678</v>
       </c>
       <c r="D483" s="3" t="n">
-        <v>10308.36186475268</v>
+        <v>10308.36106805058</v>
       </c>
     </row>
     <row r="484">
@@ -8577,7 +8577,7 @@
         <v>9963.198166574235</v>
       </c>
       <c r="D485" s="3" t="n">
-        <v>10207.54888366231</v>
+        <v>10207.54808173419</v>
       </c>
     </row>
     <row r="486">
@@ -8593,7 +8593,7 @@
         <v>9963.198166574235</v>
       </c>
       <c r="D486" s="3" t="n">
-        <v>10207.54888366231</v>
+        <v>10207.54808173419</v>
       </c>
     </row>
     <row r="487">
@@ -8609,7 +8609,7 @@
         <v>9963.198166574235</v>
       </c>
       <c r="D487" s="3" t="n">
-        <v>10207.54888366231</v>
+        <v>10207.54808173419</v>
       </c>
     </row>
     <row r="488">
@@ -8625,7 +8625,7 @@
         <v>9982.961902318581</v>
       </c>
       <c r="D488" s="3" t="n">
-        <v>10189.69459456603</v>
+        <v>10189.69379404059</v>
       </c>
     </row>
     <row r="489">
@@ -8673,7 +8673,7 @@
         <v>9875.963189639206</v>
       </c>
       <c r="D491" s="3" t="n">
-        <v>10098.89433071827</v>
+        <v>10098.89352425699</v>
       </c>
     </row>
     <row r="492">
@@ -8689,7 +8689,7 @@
         <v>9827.574534657877</v>
       </c>
       <c r="D492" s="3" t="n">
-        <v>9998.325529408852</v>
+        <v>9998.324722357405</v>
       </c>
     </row>
     <row r="493">
@@ -8705,7 +8705,7 @@
         <v>9827.574534657877</v>
       </c>
       <c r="D493" s="3" t="n">
-        <v>9998.325529408852</v>
+        <v>9998.324722357405</v>
       </c>
     </row>
     <row r="494">
@@ -8721,7 +8721,7 @@
         <v>9827.574534657877</v>
       </c>
       <c r="D494" s="3" t="n">
-        <v>9998.325529408852</v>
+        <v>9998.324722357405</v>
       </c>
     </row>
     <row r="495">
@@ -8737,7 +8737,7 @@
         <v>9882.096655223007</v>
       </c>
       <c r="D495" s="3" t="n">
-        <v>10073.52541144754</v>
+        <v>10073.52460108602</v>
       </c>
     </row>
     <row r="496">
@@ -8769,7 +8769,7 @@
         <v>9743.747385243722</v>
       </c>
       <c r="D497" s="3" t="n">
-        <v>9976.479399983667</v>
+        <v>9976.477782716014</v>
       </c>
     </row>
     <row r="498">
@@ -8785,7 +8785,7 @@
         <v>9792.135000302098</v>
       </c>
       <c r="D498" s="3" t="n">
-        <v>9967.716683549261</v>
+        <v>9967.715881860657</v>
       </c>
     </row>
     <row r="499">
@@ -8849,7 +8849,7 @@
         <v>9992.503195423258</v>
       </c>
       <c r="D502" s="3" t="n">
-        <v>10175.35770440214</v>
+        <v>10175.35689948894</v>
       </c>
     </row>
     <row r="503">
@@ -8865,7 +8865,7 @@
         <v>9933.892097802258</v>
       </c>
       <c r="D503" s="3" t="n">
-        <v>9961.143641836456</v>
+        <v>9961.142041367353</v>
       </c>
     </row>
     <row r="504">
@@ -8881,7 +8881,7 @@
         <v>9920.94401709966</v>
       </c>
       <c r="D504" s="3" t="n">
-        <v>10107.50269415985</v>
+        <v>10107.50350482928</v>
       </c>
     </row>
     <row r="505">
@@ -8961,7 +8961,7 @@
         <v>9479.997965910701</v>
       </c>
       <c r="D509" s="3" t="n">
-        <v>9642.472553044836</v>
+        <v>9642.473353630123</v>
       </c>
     </row>
     <row r="510">
@@ -8977,7 +8977,7 @@
         <v>9620.391724417921</v>
       </c>
       <c r="D510" s="3" t="n">
-        <v>9764.061852638286</v>
+        <v>9764.060257643139</v>
       </c>
     </row>
     <row r="511">
@@ -8993,7 +8993,7 @@
         <v>9534.519046552879</v>
       </c>
       <c r="D511" s="3" t="n">
-        <v>9700.599807860801</v>
+        <v>9700.599010559967</v>
       </c>
     </row>
     <row r="512">
@@ -9009,7 +9009,7 @@
         <v>9665.372551878376</v>
       </c>
       <c r="D512" s="3" t="n">
-        <v>10005.38443565489</v>
+        <v>10005.38524382683</v>
       </c>
     </row>
     <row r="513">
@@ -9089,7 +9089,7 @@
         <v>9669.461528934244</v>
       </c>
       <c r="D517" s="3" t="n">
-        <v>9986.432194446388</v>
+        <v>9986.432992380143</v>
       </c>
     </row>
     <row r="518">
@@ -9105,7 +9105,7 @@
         <v>9685.136287622723</v>
       </c>
       <c r="D518" s="3" t="n">
-        <v>9766.008095001785</v>
+        <v>9766.007301147891</v>
       </c>
     </row>
     <row r="519">
@@ -9137,7 +9137,7 @@
         <v>9582.226551999216</v>
       </c>
       <c r="D520" s="3" t="n">
-        <v>9801.339226678987</v>
+        <v>9801.338437281242</v>
       </c>
     </row>
     <row r="521">
@@ -9153,7 +9153,7 @@
         <v>9582.226551999216</v>
       </c>
       <c r="D521" s="3" t="n">
-        <v>9801.339226678987</v>
+        <v>9801.338437281242</v>
       </c>
     </row>
     <row r="522">
@@ -9169,7 +9169,7 @@
         <v>9582.226551999216</v>
       </c>
       <c r="D522" s="3" t="n">
-        <v>9801.339226678987</v>
+        <v>9801.338437281242</v>
       </c>
     </row>
     <row r="523">
@@ -9201,7 +9201,7 @@
         <v>9608.805942785311</v>
       </c>
       <c r="D524" s="3" t="n">
-        <v>9822.995076040979</v>
+        <v>9822.996658924856</v>
       </c>
     </row>
     <row r="525">
@@ -9217,7 +9217,7 @@
         <v>9704.900023367069</v>
       </c>
       <c r="D525" s="3" t="n">
-        <v>9935.93805573574</v>
+        <v>9935.938844808448</v>
       </c>
     </row>
     <row r="526">
@@ -9233,7 +9233,7 @@
         <v>9755.333166876333</v>
       </c>
       <c r="D526" s="3" t="n">
-        <v>9990.324768461023</v>
+        <v>9990.323979687677</v>
       </c>
     </row>
     <row r="527">
@@ -9249,7 +9249,7 @@
         <v>9863.695218548648</v>
       </c>
       <c r="D527" s="3" t="n">
-        <v>10074.44817112594</v>
+        <v>10074.44660240611</v>
       </c>
     </row>
     <row r="528">
@@ -9265,7 +9265,7 @@
         <v>9863.695218548648</v>
       </c>
       <c r="D528" s="3" t="n">
-        <v>10074.44817112594</v>
+        <v>10074.44660240611</v>
       </c>
     </row>
     <row r="529">
@@ -9281,7 +9281,7 @@
         <v>9863.695218548648</v>
       </c>
       <c r="D529" s="3" t="n">
-        <v>10074.44817112594</v>
+        <v>10074.44660240611</v>
       </c>
     </row>
     <row r="530">
@@ -9313,7 +9313,7 @@
         <v>9831.663511713745</v>
       </c>
       <c r="D531" s="3" t="n">
-        <v>10049.71032583293</v>
+        <v>10049.7111096454</v>
       </c>
     </row>
     <row r="532">
@@ -9345,7 +9345,7 @@
         <v>9818.033241553199</v>
       </c>
       <c r="D533" s="3" t="n">
-        <v>10070.73403233673</v>
+        <v>10070.73324788274</v>
       </c>
     </row>
     <row r="534">
@@ -9361,7 +9361,7 @@
         <v>9818.033241553199</v>
       </c>
       <c r="D534" s="3" t="n">
-        <v>10055.25162118754</v>
+        <v>10055.25083793954</v>
       </c>
     </row>
     <row r="535">
@@ -9377,7 +9377,7 @@
         <v>9818.033241553199</v>
       </c>
       <c r="D535" s="3" t="n">
-        <v>10055.25162118754</v>
+        <v>10055.25083793954</v>
       </c>
     </row>
     <row r="536">
@@ -9393,7 +9393,7 @@
         <v>9818.033241553199</v>
       </c>
       <c r="D536" s="3" t="n">
-        <v>10055.25162118754</v>
+        <v>10055.25083793954</v>
       </c>
     </row>
     <row r="537">
@@ -9409,7 +9409,7 @@
         <v>9818.033241553199</v>
       </c>
       <c r="D537" s="3" t="n">
-        <v>10071.61498882665</v>
+        <v>10071.6165562634</v>
       </c>
     </row>
     <row r="538">
@@ -9425,7 +9425,7 @@
         <v>9885.504482743883</v>
       </c>
       <c r="D538" s="3" t="n">
-        <v>10115.33333292972</v>
+        <v>10115.33175911224</v>
       </c>
     </row>
     <row r="539">
@@ -9457,7 +9457,7 @@
         <v>9827.574534657877</v>
       </c>
       <c r="D540" s="3" t="n">
-        <v>10086.75181584722</v>
+        <v>10086.75103827858</v>
       </c>
     </row>
     <row r="541">
@@ -9569,7 +9569,7 @@
         <v>9916.172850585846</v>
       </c>
       <c r="D547" s="3" t="n">
-        <v>10091.73159118555</v>
+        <v>10091.73237214126</v>
       </c>
     </row>
     <row r="548">
@@ -9585,7 +9585,7 @@
         <v>9912.765023064971</v>
       </c>
       <c r="D548" s="3" t="n">
-        <v>10082.31667884565</v>
+        <v>10082.31745846706</v>
       </c>
     </row>
     <row r="549">
@@ -9601,7 +9601,7 @@
         <v>9912.765023064971</v>
       </c>
       <c r="D549" s="3" t="n">
-        <v>10082.31667884565</v>
+        <v>10082.31745846706</v>
       </c>
     </row>
     <row r="550">
@@ -9617,7 +9617,7 @@
         <v>9912.765023064971</v>
       </c>
       <c r="D550" s="3" t="n">
-        <v>10082.31667884565</v>
+        <v>10082.31745846706</v>
       </c>
     </row>
     <row r="551">
@@ -9633,7 +9633,7 @@
         <v>9868.466385062464</v>
       </c>
       <c r="D551" s="3" t="n">
-        <v>10073.23740325511</v>
+        <v>10073.23662514754</v>
       </c>
     </row>
     <row r="552">
@@ -9649,7 +9649,7 @@
         <v>9850.746097923096</v>
       </c>
       <c r="D552" s="3" t="n">
-        <v>9853.074703147226</v>
+        <v>9853.073929769589</v>
       </c>
     </row>
     <row r="553">
@@ -9665,7 +9665,7 @@
         <v>9752.607528813405</v>
       </c>
       <c r="D553" s="3" t="n">
-        <v>9883.82507811098</v>
+        <v>9883.82585720211</v>
       </c>
     </row>
     <row r="554">
@@ -9697,7 +9697,7 @@
         <v>9889.593459799751</v>
       </c>
       <c r="D555" s="3" t="n">
-        <v>10117.18567555512</v>
+        <v>10117.18722615925</v>
       </c>
     </row>
     <row r="556">
@@ -9713,7 +9713,7 @@
         <v>9889.593459799751</v>
       </c>
       <c r="D556" s="3" t="n">
-        <v>10117.18567555512</v>
+        <v>10117.18722615925</v>
       </c>
     </row>
     <row r="557">
@@ -9729,7 +9729,7 @@
         <v>9889.593459799751</v>
       </c>
       <c r="D557" s="3" t="n">
-        <v>10117.18567555512</v>
+        <v>10117.18722615925</v>
       </c>
     </row>
     <row r="558">
@@ -9745,7 +9745,7 @@
         <v>9889.593459799751</v>
       </c>
       <c r="D558" s="3" t="n">
-        <v>10126.37205198042</v>
+        <v>10126.37360556115</v>
       </c>
     </row>
     <row r="559">
@@ -9755,13 +9755,13 @@
         </is>
       </c>
       <c r="B559" s="3" t="n">
-        <v>9807.91</v>
+        <v>9807.9</v>
       </c>
       <c r="C559" s="3" t="n">
         <v>9793.498339295038</v>
       </c>
       <c r="D559" s="3" t="n">
-        <v>10050.59444878076</v>
+        <v>10050.59600826319</v>
       </c>
     </row>
     <row r="560">
@@ -9793,7 +9793,7 @@
         <v>9744.428534778715</v>
       </c>
       <c r="D561" s="3" t="n">
-        <v>9821.654851403126</v>
+        <v>9821.654078684069</v>
       </c>
     </row>
     <row r="562">
@@ -9809,7 +9809,7 @@
         <v>9867.784195604516</v>
       </c>
       <c r="D562" s="3" t="n">
-        <v>10045.22272590722</v>
+        <v>10045.22194996364</v>
       </c>
     </row>
     <row r="563">
@@ -9825,7 +9825,7 @@
         <v>9867.784195604516</v>
       </c>
       <c r="D563" s="3" t="n">
-        <v>10045.22272590722</v>
+        <v>10045.22194996364</v>
       </c>
     </row>
     <row r="564">
@@ -9841,7 +9841,7 @@
         <v>9867.784195604516</v>
       </c>
       <c r="D564" s="3" t="n">
-        <v>10045.22272590722</v>
+        <v>10045.22194996364</v>
       </c>
     </row>
     <row r="565">
@@ -9857,7 +9857,7 @@
         <v>9899.134752904427</v>
       </c>
       <c r="D565" s="3" t="n">
-        <v>10051.77620891979</v>
+        <v>10051.77698516272</v>
       </c>
     </row>
     <row r="566">
@@ -9873,7 +9873,7 @@
         <v>9933.892097802258</v>
       </c>
       <c r="D566" s="3" t="n">
-        <v>10028.20562938626</v>
+        <v>10028.20485155242</v>
       </c>
     </row>
     <row r="567">
@@ -9905,7 +9905,7 @@
         <v>9948.20455742075</v>
       </c>
       <c r="D568" s="3" t="n">
-        <v>10068.55126213455</v>
+        <v>10068.5520408237</v>
       </c>
     </row>
     <row r="569">
@@ -9969,7 +9969,7 @@
         <v>10012.26797109056</v>
       </c>
       <c r="D572" s="3" t="n">
-        <v>10212.1837926529</v>
+        <v>10212.1822164235</v>
       </c>
     </row>
     <row r="573">
@@ -9985,7 +9985,7 @@
         <v>9995.229873409138</v>
       </c>
       <c r="D573" s="3" t="n">
-        <v>10124.34436589058</v>
+        <v>10124.34279270598</v>
       </c>
     </row>
     <row r="574">
@@ -10001,7 +10001,7 @@
         <v>10022.49041373023</v>
       </c>
       <c r="D574" s="3" t="n">
-        <v>10254.81782859483</v>
+        <v>10254.8186157687</v>
       </c>
     </row>
     <row r="575">
@@ -10017,7 +10017,7 @@
         <v>10165.61085022333</v>
       </c>
       <c r="D575" s="3" t="n">
-        <v>10379.70541802696</v>
+        <v>10379.70462886877</v>
       </c>
     </row>
     <row r="576">
@@ -10033,7 +10033,7 @@
         <v>10160.15853417452</v>
       </c>
       <c r="D576" s="3" t="n">
-        <v>10425.15151979321</v>
+        <v>10425.15231356165</v>
       </c>
     </row>
     <row r="577">
@@ -10049,7 +10049,7 @@
         <v>10160.15853417452</v>
       </c>
       <c r="D577" s="3" t="n">
-        <v>10425.15151979321</v>
+        <v>10425.15231356165</v>
       </c>
     </row>
     <row r="578">
@@ -10065,7 +10065,7 @@
         <v>10160.15853417452</v>
       </c>
       <c r="D578" s="3" t="n">
-        <v>10425.15151979321</v>
+        <v>10425.15231356165</v>
       </c>
     </row>
     <row r="579">
@@ -10081,7 +10081,7 @@
         <v>10196.27921806529</v>
       </c>
       <c r="D579" s="3" t="n">
-        <v>10383.76003605474</v>
+        <v>10383.75687487169</v>
       </c>
     </row>
     <row r="580">
@@ -10097,7 +10097,7 @@
         <v>10175.833292863</v>
       </c>
       <c r="D580" s="3" t="n">
-        <v>10278.33406508345</v>
+        <v>10278.33643853666</v>
       </c>
     </row>
     <row r="581">
@@ -10113,7 +10113,7 @@
         <v>10017.03809768142</v>
       </c>
       <c r="D581" s="3" t="n">
-        <v>10243.03190978417</v>
+        <v>10243.03032140926</v>
       </c>
     </row>
     <row r="582">
@@ -10129,7 +10129,7 @@
         <v>10062.70007467687</v>
       </c>
       <c r="D582" s="3" t="n">
-        <v>10343.64243814309</v>
+        <v>10343.64084793776</v>
       </c>
     </row>
     <row r="583">
@@ -10145,7 +10145,7 @@
         <v>10207.18385016291</v>
       </c>
       <c r="D583" s="3" t="n">
-        <v>10509.72210524014</v>
+        <v>10509.72051015954</v>
       </c>
     </row>
     <row r="584">
@@ -10161,7 +10161,7 @@
         <v>10207.18385016291</v>
       </c>
       <c r="D584" s="3" t="n">
-        <v>10509.72210524014</v>
+        <v>10509.72051015954</v>
       </c>
     </row>
     <row r="585">
@@ -10177,7 +10177,7 @@
         <v>10207.18385016291</v>
       </c>
       <c r="D585" s="3" t="n">
-        <v>10509.72210524014</v>
+        <v>10509.72051015954</v>
       </c>
     </row>
     <row r="586">
@@ -10193,7 +10193,7 @@
         <v>10237.17106846988</v>
       </c>
       <c r="D586" s="3" t="n">
-        <v>10511.0750851065</v>
+        <v>10511.07348982055</v>
       </c>
     </row>
     <row r="587">
@@ -10225,7 +10225,7 @@
         <v>10134.26029292342</v>
       </c>
       <c r="D588" s="3" t="n">
-        <v>10447.01335653218</v>
+        <v>10447.01574722858</v>
       </c>
     </row>
     <row r="589">
@@ -10241,7 +10241,7 @@
         <v>10132.89695393048</v>
       </c>
       <c r="D589" s="3" t="n">
-        <v>10583.62515560765</v>
+        <v>10583.62595532907</v>
       </c>
     </row>
     <row r="590">
@@ -10305,7 +10305,7 @@
         <v>10400.05524070733</v>
       </c>
       <c r="D593" s="3" t="n">
-        <v>10712.6649680545</v>
+        <v>10712.66416858972</v>
       </c>
     </row>
     <row r="594">
@@ -10321,7 +10321,7 @@
         <v>10413.68551086787</v>
       </c>
       <c r="D594" s="3" t="n">
-        <v>10722.78340002362</v>
+        <v>10722.78260154241</v>
       </c>
     </row>
     <row r="595">
@@ -10353,7 +10353,7 @@
         <v>10342.12529262132</v>
       </c>
       <c r="D596" s="3" t="n">
-        <v>10754.71633698744</v>
+        <v>10754.71553818122</v>
       </c>
     </row>
     <row r="597">
@@ -10417,7 +10417,7 @@
         <v>10421.86346497961</v>
       </c>
       <c r="D600" s="3" t="n">
-        <v>10827.7507281113</v>
+        <v>10827.74993253819</v>
       </c>
     </row>
     <row r="601">
@@ -10433,7 +10433,7 @@
         <v>10517.95858548432</v>
       </c>
       <c r="D601" s="3" t="n">
-        <v>10886.94950609106</v>
+        <v>10886.94871140749</v>
       </c>
     </row>
     <row r="602">
@@ -10465,7 +10465,7 @@
         <v>10482.51905112854</v>
       </c>
       <c r="D603" s="3" t="n">
-        <v>10953.57212660594</v>
+        <v>10953.57133778984</v>
       </c>
     </row>
     <row r="604">
@@ -10481,7 +10481,7 @@
         <v>10525.45539006106</v>
       </c>
       <c r="D604" s="3" t="n">
-        <v>10813.63797091919</v>
+        <v>10813.63875231973</v>
       </c>
     </row>
     <row r="605">
@@ -10497,7 +10497,7 @@
         <v>10525.45539006106</v>
       </c>
       <c r="D605" s="3" t="n">
-        <v>10813.63797091919</v>
+        <v>10813.63875231973</v>
       </c>
     </row>
     <row r="606">
@@ -10513,7 +10513,7 @@
         <v>10525.45539006106</v>
       </c>
       <c r="D606" s="3" t="n">
-        <v>10813.63797091919</v>
+        <v>10813.63875231973</v>
       </c>
     </row>
     <row r="607">
@@ -10529,7 +10529,7 @@
         <v>10460.02863739831</v>
       </c>
       <c r="D607" s="3" t="n">
-        <v>10817.42554901957</v>
+        <v>10817.4263306938</v>
       </c>
     </row>
     <row r="608">
@@ -10561,7 +10561,7 @@
         <v>10360.52672929568</v>
       </c>
       <c r="D609" s="3" t="n">
-        <v>10727.48672465336</v>
+        <v>10727.48594142247</v>
       </c>
     </row>
     <row r="610">
@@ -10577,7 +10577,7 @@
         <v>10333.26514905164</v>
       </c>
       <c r="D610" s="3" t="n">
-        <v>10695.43193640336</v>
+        <v>10695.43271448519</v>
       </c>
     </row>
     <row r="611">
@@ -10689,7 +10689,7 @@
         <v>10431.40475808428</v>
       </c>
       <c r="D617" s="3" t="n">
-        <v>10810.1562007476</v>
+        <v>10810.15541719167</v>
       </c>
     </row>
     <row r="618">
@@ -10753,7 +10753,7 @@
         <v>10549.99029231922</v>
       </c>
       <c r="D621" s="3" t="n">
-        <v>10958.67512494864</v>
+        <v>10958.67355663943</v>
       </c>
     </row>
     <row r="622">
@@ -10769,7 +10769,7 @@
         <v>10561.57607395183</v>
       </c>
       <c r="D622" s="3" t="n">
-        <v>10953.05726886763</v>
+        <v>10953.0557013624</v>
       </c>
     </row>
     <row r="623">
@@ -10801,7 +10801,7 @@
         <v>10379.60931550503</v>
       </c>
       <c r="D624" s="3" t="n">
-        <v>10907.61186229394</v>
+        <v>10907.61343795894</v>
       </c>
     </row>
     <row r="625">
@@ -10817,7 +10817,7 @@
         <v>10379.60931550503</v>
       </c>
       <c r="D625" s="3" t="n">
-        <v>10846.05564298305</v>
+        <v>10846.05485761389</v>
       </c>
     </row>
     <row r="626">
@@ -10833,7 +10833,7 @@
         <v>10379.60931550503</v>
       </c>
       <c r="D626" s="3" t="n">
-        <v>10846.05564298305</v>
+        <v>10846.05485761389</v>
       </c>
     </row>
     <row r="627">
@@ -10849,7 +10849,7 @@
         <v>10379.60931550503</v>
       </c>
       <c r="D627" s="3" t="n">
-        <v>10846.05564298305</v>
+        <v>10846.05485761389</v>
       </c>
     </row>
     <row r="628">
@@ -10865,7 +10865,7 @@
         <v>10335.99182703752</v>
       </c>
       <c r="D628" s="3" t="n">
-        <v>10795.11331423594</v>
+        <v>10795.1148736499</v>
       </c>
     </row>
     <row r="629">
@@ -10897,7 +10897,7 @@
         <v>10427.99693056341</v>
       </c>
       <c r="D630" s="3" t="n">
-        <v>10907.18395422574</v>
+        <v>10907.18550736172</v>
       </c>
     </row>
     <row r="631">
@@ -10913,7 +10913,7 @@
         <v>10427.99693056341</v>
       </c>
       <c r="D631" s="3" t="n">
-        <v>10865.03836733484</v>
+        <v>10865.03759985892</v>
       </c>
     </row>
     <row r="632">
@@ -10977,7 +10977,7 @@
         <v>10415.7299993958</v>
       </c>
       <c r="D635" s="3" t="n">
-        <v>10815.21991401969</v>
+        <v>10815.22219938383</v>
       </c>
     </row>
     <row r="636">
@@ -10993,7 +10993,7 @@
         <v>10471.61441903092</v>
       </c>
       <c r="D636" s="3" t="n">
-        <v>10886.04503767906</v>
+        <v>10886.04351543716</v>
       </c>
     </row>
     <row r="637">
@@ -11009,7 +11009,7 @@
         <v>10564.30171201476</v>
       </c>
       <c r="D637" s="3" t="n">
-        <v>10918.70901608468</v>
+        <v>10918.71130121785</v>
       </c>
     </row>
     <row r="638">
@@ -11025,7 +11025,7 @@
         <v>10573.16185558444</v>
       </c>
       <c r="D638" s="3" t="n">
-        <v>10869.16912352367</v>
+        <v>10869.1675968854</v>
       </c>
     </row>
     <row r="639">
@@ -11041,7 +11041,7 @@
         <v>10587.47431520294</v>
       </c>
       <c r="D639" s="3" t="n">
-        <v>10935.66639534867</v>
+        <v>10935.66485937047</v>
       </c>
     </row>
     <row r="640">
@@ -11057,7 +11057,7 @@
         <v>10587.47431520294</v>
       </c>
       <c r="D640" s="3" t="n">
-        <v>10935.66639534867</v>
+        <v>10935.66485937047</v>
       </c>
     </row>
     <row r="641">
@@ -11073,7 +11073,7 @@
         <v>10587.47431520294</v>
       </c>
       <c r="D641" s="3" t="n">
-        <v>10935.66639534867</v>
+        <v>10935.66485937047</v>
       </c>
     </row>
     <row r="642">
@@ -11089,7 +11089,7 @@
         <v>10626.32063715663</v>
       </c>
       <c r="D642" s="3" t="n">
-        <v>10996.142645536</v>
+        <v>10996.14187673427</v>
       </c>
     </row>
     <row r="643">
@@ -11105,7 +11105,7 @@
         <v>10680.84275772177</v>
       </c>
       <c r="D643" s="3" t="n">
-        <v>11088.11139376732</v>
+        <v>11088.10984752522</v>
       </c>
     </row>
     <row r="644">
@@ -11121,7 +11121,7 @@
         <v>10643.35873483805</v>
       </c>
       <c r="D644" s="3" t="n">
-        <v>11102.57275775998</v>
+        <v>11102.57353177051</v>
       </c>
     </row>
     <row r="645">
@@ -11201,7 +11201,7 @@
         <v>10766.71439566385</v>
       </c>
       <c r="D649" s="3" t="n">
-        <v>11184.65592072023</v>
+        <v>11184.65747241926</v>
       </c>
     </row>
     <row r="650">
@@ -11217,7 +11217,7 @@
         <v>10761.26207961505</v>
       </c>
       <c r="D650" s="3" t="n">
-        <v>11179.70050749105</v>
+        <v>11179.69972975983</v>
       </c>
     </row>
     <row r="651">
@@ -11233,7 +11233,7 @@
         <v>10645.40322336599</v>
       </c>
       <c r="D651" s="3" t="n">
-        <v>11013.87609934423</v>
+        <v>11013.87532234002</v>
       </c>
     </row>
     <row r="652">
@@ -11265,7 +11265,7 @@
         <v>10576.56968310532</v>
       </c>
       <c r="D653" s="3" t="n">
-        <v>10988.84227187893</v>
+        <v>10988.84149088045</v>
       </c>
     </row>
     <row r="654">
@@ -11281,7 +11281,7 @@
         <v>10576.56968310532</v>
       </c>
       <c r="D654" s="3" t="n">
-        <v>10988.84227187893</v>
+        <v>10988.84149088045</v>
       </c>
     </row>
     <row r="655">
@@ -11297,7 +11297,7 @@
         <v>10576.56968310532</v>
       </c>
       <c r="D655" s="3" t="n">
-        <v>10988.84227187893</v>
+        <v>10988.84149088045</v>
       </c>
     </row>
     <row r="656">
@@ -11313,7 +11313,7 @@
         <v>10547.26361433334</v>
       </c>
       <c r="D656" s="3" t="n">
-        <v>11033.28716072613</v>
+        <v>11033.28482861035</v>
       </c>
     </row>
     <row r="657">
@@ -11329,7 +11329,7 @@
         <v>10525.45539006106</v>
       </c>
       <c r="D657" s="3" t="n">
-        <v>10984.82378359273</v>
+        <v>10984.823006255</v>
       </c>
     </row>
     <row r="658">
@@ -11361,7 +11361,7 @@
         <v>10568.39172899358</v>
       </c>
       <c r="D659" s="3" t="n">
-        <v>10940.64550720654</v>
+        <v>10940.64628634903</v>
       </c>
     </row>
     <row r="660">
@@ -11377,7 +11377,7 @@
         <v>10498.87599927497</v>
       </c>
       <c r="D660" s="3" t="n">
-        <v>10930.30503877197</v>
+        <v>10930.30425991173</v>
       </c>
     </row>
     <row r="661">
@@ -11393,7 +11393,7 @@
         <v>10498.87599927497</v>
       </c>
       <c r="D661" s="3" t="n">
-        <v>10930.30503877197</v>
+        <v>10930.30425991173</v>
       </c>
     </row>
     <row r="662">
@@ -11409,7 +11409,7 @@
         <v>10498.87599927497</v>
       </c>
       <c r="D662" s="3" t="n">
-        <v>10930.30503877197</v>
+        <v>10930.30425991173</v>
       </c>
     </row>
     <row r="663">
@@ -11425,7 +11425,7 @@
         <v>10564.98390147271</v>
       </c>
       <c r="D663" s="3" t="n">
-        <v>11028.05612259594</v>
+        <v>11028.05534108424</v>
       </c>
     </row>
     <row r="664">
@@ -11441,7 +11441,7 @@
         <v>10492.74253369116</v>
       </c>
       <c r="D664" s="3" t="n">
-        <v>10934.06618751481</v>
+        <v>10934.0669714984</v>
       </c>
     </row>
     <row r="665">
@@ -11457,7 +11457,7 @@
         <v>10474.3410970168</v>
       </c>
       <c r="D665" s="3" t="n">
-        <v>10859.51471764316</v>
+        <v>10859.5131488549</v>
       </c>
     </row>
     <row r="666">
@@ -11537,7 +11537,7 @@
         <v>10328.49502246078</v>
       </c>
       <c r="D670" s="3" t="n">
-        <v>10880.62126696849</v>
+        <v>10880.62048051311</v>
       </c>
     </row>
     <row r="671">
@@ -11569,7 +11569,7 @@
         <v>10495.46817175409</v>
       </c>
       <c r="D672" s="3" t="n">
-        <v>11001.24280321859</v>
+        <v>11001.24122611661</v>
       </c>
     </row>
     <row r="673">
@@ -11585,7 +11585,7 @@
         <v>10454.5763213495</v>
       </c>
       <c r="D673" s="3" t="n">
-        <v>10829.71339472645</v>
+        <v>10829.71103323049</v>
       </c>
     </row>
     <row r="674">
@@ -11601,7 +11601,7 @@
         <v>10456.62080987744</v>
       </c>
       <c r="D674" s="3" t="n">
-        <v>10973.37038680226</v>
+        <v>10973.36959477873</v>
       </c>
     </row>
     <row r="675">
@@ -11617,7 +11617,7 @@
         <v>10456.62080987744</v>
       </c>
       <c r="D675" s="3" t="n">
-        <v>10973.37038680226</v>
+        <v>10973.36959477873</v>
       </c>
     </row>
     <row r="676">
@@ -11633,7 +11633,7 @@
         <v>10456.62080987744</v>
       </c>
       <c r="D676" s="3" t="n">
-        <v>10973.37038680226</v>
+        <v>10973.36959477873</v>
       </c>
     </row>
     <row r="677">
@@ -11649,7 +11649,7 @@
         <v>10539.08566022161</v>
       </c>
       <c r="D677" s="3" t="n">
-        <v>11044.74499127437</v>
+        <v>11044.74578342627</v>
       </c>
     </row>
     <row r="678">
@@ -11665,7 +11665,7 @@
         <v>10627.00178669163</v>
       </c>
       <c r="D678" s="3" t="n">
-        <v>11175.23833044425</v>
+        <v>11175.2375403537</v>
       </c>
     </row>
     <row r="679">
@@ -11681,7 +11681,7 @@
         <v>10620.86832110783</v>
       </c>
       <c r="D679" s="3" t="n">
-        <v>11176.19743200692</v>
+        <v>11176.19664508963</v>
       </c>
     </row>
     <row r="680">
@@ -11697,7 +11697,7 @@
         <v>10704.69651044493</v>
       </c>
       <c r="D680" s="3" t="n">
-        <v>11095.19101484763</v>
+        <v>11095.19023248923</v>
       </c>
     </row>
     <row r="681">
@@ -11713,7 +11713,7 @@
         <v>10752.40297596832</v>
       </c>
       <c r="D681" s="3" t="n">
-        <v>11206.54512588268</v>
+        <v>11206.54433714349</v>
       </c>
     </row>
     <row r="682">
@@ -11729,7 +11729,7 @@
         <v>10752.40297596832</v>
       </c>
       <c r="D682" s="3" t="n">
-        <v>11206.54512588268</v>
+        <v>11206.54433714349</v>
       </c>
     </row>
     <row r="683">
@@ -11745,7 +11745,7 @@
         <v>10752.40297596832</v>
       </c>
       <c r="D683" s="3" t="n">
-        <v>11206.54512588268</v>
+        <v>11206.54433714349</v>
       </c>
     </row>
     <row r="684">
@@ -11761,7 +11761,7 @@
         <v>10757.85529201712</v>
       </c>
       <c r="D684" s="3" t="n">
-        <v>11277.51390680408</v>
+        <v>11277.51311306997</v>
       </c>
     </row>
     <row r="685">
@@ -11777,7 +11777,7 @@
         <v>10796.70161397082</v>
       </c>
       <c r="D685" s="3" t="n">
-        <v>11209.41299196679</v>
+        <v>11209.41378433249</v>
       </c>
     </row>
     <row r="686">
@@ -11793,7 +11793,7 @@
         <v>10709.4666370358</v>
       </c>
       <c r="D686" s="3" t="n">
-        <v>11204.96848447675</v>
+        <v>11204.96928188879</v>
       </c>
     </row>
     <row r="687">
@@ -11889,7 +11889,7 @@
         <v>10723.09690719634</v>
       </c>
       <c r="D692" s="3" t="n">
-        <v>11173.96848733349</v>
+        <v>11173.9676917176</v>
       </c>
     </row>
     <row r="693">
@@ -11905,7 +11905,7 @@
         <v>10719.00793014047</v>
       </c>
       <c r="D693" s="3" t="n">
-        <v>11183.98768085603</v>
+        <v>11183.98847625804</v>
       </c>
     </row>
     <row r="694">
@@ -11921,7 +11921,7 @@
         <v>10857.35720011976</v>
       </c>
       <c r="D694" s="3" t="n">
-        <v>11300.43663361001</v>
+        <v>11300.4358367967</v>
       </c>
     </row>
     <row r="695">
@@ -11937,7 +11937,7 @@
         <v>10807.60624606844</v>
       </c>
       <c r="D695" s="3" t="n">
-        <v>11266.1504616489</v>
+        <v>11266.14965756541</v>
       </c>
     </row>
     <row r="696">
@@ -11953,7 +11953,7 @@
         <v>10807.60624606844</v>
       </c>
       <c r="D696" s="3" t="n">
-        <v>11266.1504616489</v>
+        <v>11266.14965756541</v>
       </c>
     </row>
     <row r="697">
@@ -11969,7 +11969,7 @@
         <v>10807.60624606844</v>
       </c>
       <c r="D697" s="3" t="n">
-        <v>11266.1504616489</v>
+        <v>11266.14965756541</v>
       </c>
     </row>
     <row r="698">
@@ -11985,7 +11985,7 @@
         <v>10755.81080348919</v>
       </c>
       <c r="D698" s="3" t="n">
-        <v>11239.90240742457</v>
+        <v>11239.90160568463</v>
       </c>
     </row>
     <row r="699">
@@ -12001,7 +12001,7 @@
         <v>10706.74099897287</v>
       </c>
       <c r="D699" s="3" t="n">
-        <v>11190.98401537824</v>
+        <v>11190.98241555917</v>
       </c>
     </row>
     <row r="700">
@@ -12017,7 +12017,7 @@
         <v>10737.40936681483</v>
       </c>
       <c r="D700" s="3" t="n">
-        <v>11099.12698740564</v>
+        <v>11099.12858881566</v>
       </c>
     </row>
     <row r="701">
@@ -12033,7 +12033,7 @@
         <v>10566.34620054269</v>
       </c>
       <c r="D701" s="3" t="n">
-        <v>10945.41081493148</v>
+        <v>10945.41161781753</v>
       </c>
     </row>
     <row r="702">
@@ -12049,7 +12049,7 @@
         <v>10562.25722348683</v>
       </c>
       <c r="D702" s="3" t="n">
-        <v>10912.0737244863</v>
+        <v>10912.07532897557</v>
       </c>
     </row>
     <row r="703">
@@ -12065,7 +12065,7 @@
         <v>10562.25722348683</v>
       </c>
       <c r="D703" s="3" t="n">
-        <v>10912.0737244863</v>
+        <v>10912.07532897557</v>
       </c>
     </row>
     <row r="704">
@@ -12081,7 +12081,7 @@
         <v>10562.25722348683</v>
       </c>
       <c r="D704" s="3" t="n">
-        <v>10912.0737244863</v>
+        <v>10912.07532897557</v>
       </c>
     </row>
     <row r="705">
@@ -12097,7 +12097,7 @@
         <v>10556.80490743802</v>
       </c>
       <c r="D705" s="3" t="n">
-        <v>10971.39574382016</v>
+        <v>10971.39735027664</v>
       </c>
     </row>
     <row r="706">
@@ -12113,7 +12113,7 @@
         <v>10472.29660848887</v>
       </c>
       <c r="D706" s="3" t="n">
-        <v>10868.23030028578</v>
+        <v>10868.22949274674</v>
       </c>
     </row>
     <row r="707">
@@ -12129,7 +12129,7 @@
         <v>10500.9204878029</v>
       </c>
       <c r="D707" s="3" t="n">
-        <v>10895.36898109246</v>
+        <v>10895.3705995576</v>
       </c>
     </row>
     <row r="708">
@@ -12145,7 +12145,7 @@
         <v>10517.27743594933</v>
       </c>
       <c r="D708" s="3" t="n">
-        <v>11025.47993910837</v>
+        <v>11025.48156746081</v>
       </c>
     </row>
     <row r="709">
@@ -12161,7 +12161,7 @@
         <v>10534.99668316574</v>
       </c>
       <c r="D709" s="3" t="n">
-        <v>10939.21716014544</v>
+        <v>10939.21877968811</v>
       </c>
     </row>
     <row r="710">
@@ -12177,7 +12177,7 @@
         <v>10534.99668316574</v>
       </c>
       <c r="D710" s="3" t="n">
-        <v>10939.21716014544</v>
+        <v>10939.21877968811</v>
       </c>
     </row>
     <row r="711">
@@ -12193,7 +12193,7 @@
         <v>10534.99668316574</v>
       </c>
       <c r="D711" s="3" t="n">
-        <v>10939.21716014544</v>
+        <v>10939.21877968811</v>
       </c>
     </row>
     <row r="712">
@@ -12225,7 +12225,7 @@
         <v>10393.23958566558</v>
       </c>
       <c r="D713" s="3" t="n">
-        <v>10872.58894603813</v>
+        <v>10872.58976212174</v>
       </c>
     </row>
     <row r="714">
@@ -12257,7 +12257,7 @@
         <v>10354.39222378892</v>
       </c>
       <c r="D715" s="3" t="n">
-        <v>10920.21584474579</v>
+        <v>10920.21503070638</v>
       </c>
     </row>
     <row r="716">
@@ -12273,7 +12273,7 @@
         <v>10419.13782691668</v>
       </c>
       <c r="D716" s="3" t="n">
-        <v>11008.4202620256</v>
+        <v>11008.42107301152</v>
       </c>
     </row>
     <row r="717">
@@ -12289,7 +12289,7 @@
         <v>10489.33470617029</v>
       </c>
       <c r="D717" s="3" t="n">
-        <v>11057.04737178364</v>
+        <v>11057.04818117012</v>
       </c>
     </row>
     <row r="718">
@@ -12305,7 +12305,7 @@
         <v>10636.54411971926</v>
       </c>
       <c r="D718" s="3" t="n">
-        <v>11102.61738650196</v>
+        <v>11102.61900353014</v>
       </c>
     </row>
     <row r="719">
@@ -12337,7 +12337,7 @@
         <v>10675.39044167296</v>
       </c>
       <c r="D720" s="3" t="n">
-        <v>11032.77915590177</v>
+        <v>11032.77835084317</v>
       </c>
     </row>
     <row r="721">
@@ -12353,7 +12353,7 @@
         <v>10609.28253947522</v>
       </c>
       <c r="D721" s="3" t="n">
-        <v>11069.03100606491</v>
+        <v>11069.0326295593</v>
       </c>
     </row>
     <row r="722">
@@ -12369,7 +12369,7 @@
         <v>10609.28253947522</v>
       </c>
       <c r="D722" s="3" t="n">
-        <v>11069.03100606491</v>
+        <v>11069.0326295593</v>
       </c>
     </row>
     <row r="723">
@@ -12385,7 +12385,7 @@
         <v>10609.28253947522</v>
       </c>
       <c r="D723" s="3" t="n">
-        <v>11069.03100606491</v>
+        <v>11069.0326295593</v>
       </c>
     </row>
     <row r="724">
@@ -12401,7 +12401,7 @@
         <v>10659.03349352653</v>
       </c>
       <c r="D724" s="3" t="n">
-        <v>11201.63880996485</v>
+        <v>11201.63962288376</v>
       </c>
     </row>
     <row r="725">
@@ -12433,7 +12433,7 @@
         <v>10573.84300511944</v>
       </c>
       <c r="D726" s="3" t="n">
-        <v>10998.03103186049</v>
+        <v>10998.03184081934</v>
       </c>
     </row>
     <row r="727">
@@ -12465,7 +12465,7 @@
         <v>10271.24726383272</v>
       </c>
       <c r="D728" s="3" t="n">
-        <v>10753.78087338932</v>
+        <v>10753.77925752448</v>
       </c>
     </row>
     <row r="729">
@@ -12481,7 +12481,7 @@
         <v>10271.24726383272</v>
       </c>
       <c r="D729" s="3" t="n">
-        <v>10753.78087338932</v>
+        <v>10753.77925752448</v>
       </c>
     </row>
     <row r="730">
@@ -12497,7 +12497,7 @@
         <v>10271.24726383272</v>
       </c>
       <c r="D730" s="3" t="n">
-        <v>10753.78087338932</v>
+        <v>10753.77925752448</v>
       </c>
     </row>
     <row r="731">
@@ -12529,7 +12529,7 @@
         <v>10288.96651104913</v>
       </c>
       <c r="D732" s="3" t="n">
-        <v>10731.57302461928</v>
+        <v>10731.57382623945</v>
       </c>
     </row>
     <row r="733">
@@ -12545,7 +12545,7 @@
         <v>10244.66787304662</v>
       </c>
       <c r="D733" s="3" t="n">
-        <v>10651.92719580285</v>
+        <v>10651.9263885461</v>
       </c>
     </row>
     <row r="734">
@@ -12577,7 +12577,7 @@
         <v>10072.92355723949</v>
       </c>
       <c r="D735" s="3" t="n">
-        <v>10507.30651011449</v>
+        <v>10507.30570049713</v>
       </c>
     </row>
     <row r="736">
@@ -12593,7 +12593,7 @@
         <v>10072.92355723949</v>
       </c>
       <c r="D736" s="3" t="n">
-        <v>10507.30651011449</v>
+        <v>10507.30570049713</v>
       </c>
     </row>
     <row r="737">
@@ -12609,7 +12609,7 @@
         <v>10072.92355723949</v>
       </c>
       <c r="D737" s="3" t="n">
-        <v>10507.30651011449</v>
+        <v>10507.30570049713</v>
       </c>
     </row>
     <row r="738">
@@ -12657,7 +12657,7 @@
         <v>10288.96651104913</v>
       </c>
       <c r="D740" s="3" t="n">
-        <v>10798.85059278402</v>
+        <v>10798.85220977795</v>
       </c>
     </row>
     <row r="741">
@@ -12673,7 +12673,7 @@
         <v>10439.58271219602</v>
       </c>
       <c r="D741" s="3" t="n">
-        <v>10997.53698950627</v>
+        <v>10997.53779739593</v>
       </c>
     </row>
     <row r="742">
@@ -12689,7 +12689,7 @@
         <v>10492.06034423322</v>
       </c>
       <c r="D742" s="3" t="n">
-        <v>11064.38714768101</v>
+        <v>11064.386342229</v>
       </c>
     </row>
     <row r="743">
@@ -12705,7 +12705,7 @@
         <v>10492.06034423322</v>
       </c>
       <c r="D743" s="3" t="n">
-        <v>11064.38714768101</v>
+        <v>11064.386342229</v>
       </c>
     </row>
     <row r="744">
@@ -12721,7 +12721,7 @@
         <v>10492.06034423322</v>
       </c>
       <c r="D744" s="3" t="n">
-        <v>11064.38714768101</v>
+        <v>11064.386342229</v>
       </c>
     </row>
     <row r="745">
@@ -12737,7 +12737,7 @@
         <v>10464.11761445418</v>
       </c>
       <c r="D745" s="3" t="n">
-        <v>10973.01692353301</v>
+        <v>10973.01931443468</v>
       </c>
     </row>
     <row r="746">
@@ -12785,7 +12785,7 @@
         <v>10535.67783270073</v>
       </c>
       <c r="D748" s="3" t="n">
-        <v>10948.58985360055</v>
+        <v>10948.58825643301</v>
       </c>
     </row>
     <row r="749">
@@ -12801,7 +12801,7 @@
         <v>10510.46178090758</v>
       </c>
       <c r="D749" s="3" t="n">
-        <v>11164.09996683539</v>
+        <v>11164.10076862666</v>
       </c>
     </row>
     <row r="750">
@@ -12817,7 +12817,7 @@
         <v>10510.46178090758</v>
       </c>
       <c r="D750" s="3" t="n">
-        <v>11164.09996683539</v>
+        <v>11164.10076862666</v>
       </c>
     </row>
     <row r="751">
@@ -12833,7 +12833,7 @@
         <v>10510.46178090758</v>
       </c>
       <c r="D751" s="3" t="n">
-        <v>11164.09996683539</v>
+        <v>11164.10076862666</v>
       </c>
     </row>
     <row r="752">
@@ -12849,7 +12849,7 @@
         <v>10584.06648768206</v>
       </c>
       <c r="D752" s="3" t="n">
-        <v>11129.89898779952</v>
+        <v>11129.90138809278</v>
       </c>
     </row>
     <row r="753">
@@ -12865,7 +12865,7 @@
         <v>10653.58221740068</v>
       </c>
       <c r="D753" s="3" t="n">
-        <v>11333.45614382784</v>
+        <v>11333.45774227847</v>
       </c>
     </row>
     <row r="754">
@@ -12881,7 +12881,7 @@
         <v>10691.74738981938</v>
       </c>
       <c r="D754" s="3" t="n">
-        <v>11173.18844363126</v>
+        <v>11173.18687111383</v>
       </c>
     </row>
     <row r="755">
@@ -12897,7 +12897,7 @@
         <v>10630.4096142125</v>
       </c>
       <c r="D755" s="3" t="n">
-        <v>11211.31429326535</v>
+        <v>11211.31508124321</v>
       </c>
     </row>
     <row r="756">
@@ -12977,7 +12977,7 @@
         <v>10682.8872462497</v>
       </c>
       <c r="D760" s="3" t="n">
-        <v>11192.79929886354</v>
+        <v>11192.80008026408</v>
       </c>
     </row>
     <row r="761">
@@ -12993,7 +12993,7 @@
         <v>10772.16671171266</v>
       </c>
       <c r="D761" s="3" t="n">
-        <v>11264.54500197638</v>
+        <v>11264.54656874603</v>
       </c>
     </row>
     <row r="762">
@@ -13009,7 +13009,7 @@
         <v>10766.71439566385</v>
       </c>
       <c r="D762" s="3" t="n">
-        <v>11292.83235491116</v>
+        <v>11292.83392561526</v>
       </c>
     </row>
     <row r="763">
@@ -13025,7 +13025,7 @@
         <v>10746.26847046156</v>
       </c>
       <c r="D763" s="3" t="n">
-        <v>11283.78211606429</v>
+        <v>11283.78290030443</v>
       </c>
     </row>
     <row r="764">
@@ -13041,7 +13041,7 @@
         <v>10746.26847046156</v>
       </c>
       <c r="D764" s="3" t="n">
-        <v>11283.78211606429</v>
+        <v>11283.78290030443</v>
       </c>
     </row>
     <row r="765">
@@ -13057,7 +13057,7 @@
         <v>10746.26847046156</v>
       </c>
       <c r="D765" s="3" t="n">
-        <v>11283.78211606429</v>
+        <v>11283.78290030443</v>
       </c>
     </row>
     <row r="766">
@@ -13073,7 +13073,7 @@
         <v>10727.18588425221</v>
       </c>
       <c r="D766" s="3" t="n">
-        <v>11228.32926505818</v>
+        <v>11228.33004685217</v>
       </c>
     </row>
     <row r="767">
@@ -13089,7 +13089,7 @@
         <v>10706.74099897287</v>
       </c>
       <c r="D767" s="3" t="n">
-        <v>11221.002055026</v>
+        <v>11221.00127451502</v>
       </c>
     </row>
     <row r="768">
@@ -13121,7 +13121,7 @@
         <v>10763.98875760093</v>
       </c>
       <c r="D769" s="3" t="n">
-        <v>11241.5925989222</v>
+        <v>11241.59415777171</v>
       </c>
     </row>
     <row r="770">
@@ -13137,7 +13137,7 @@
         <v>10883.93659090585</v>
       </c>
       <c r="D770" s="3" t="n">
-        <v>11392.85248879504</v>
+        <v>11392.85170352851</v>
       </c>
     </row>
     <row r="771">
@@ -13153,7 +13153,7 @@
         <v>10883.93659090585</v>
       </c>
       <c r="D771" s="3" t="n">
-        <v>11392.85248879504</v>
+        <v>11392.85170352851</v>
       </c>
     </row>
     <row r="772">
@@ -13169,7 +13169,7 @@
         <v>10883.93659090585</v>
       </c>
       <c r="D772" s="3" t="n">
-        <v>11392.85248879504</v>
+        <v>11392.85170352851</v>
       </c>
     </row>
     <row r="773">
@@ -13185,7 +13185,7 @@
         <v>10871.66965973825</v>
       </c>
       <c r="D773" s="3" t="n">
-        <v>11337.11857535065</v>
+        <v>11337.12093199699</v>
       </c>
     </row>
     <row r="774">
@@ -13217,7 +13217,7 @@
         <v>10942.54768852685</v>
       </c>
       <c r="D775" s="3" t="n">
-        <v>11388.03650389986</v>
+        <v>11388.0357114743</v>
       </c>
     </row>
     <row r="776">
@@ -13233,7 +13233,7 @@
         <v>10955.4968091524</v>
       </c>
       <c r="D776" s="3" t="n">
-        <v>11503.66375434837</v>
+        <v>11503.66454875821</v>
       </c>
     </row>
     <row r="777">
@@ -13249,7 +13249,7 @@
         <v>11023.64919987808</v>
       </c>
       <c r="D777" s="3" t="n">
-        <v>11525.87983689422</v>
+        <v>11525.87904435749</v>
       </c>
     </row>
     <row r="778">
@@ -13265,7 +13265,7 @@
         <v>11023.64919987808</v>
       </c>
       <c r="D778" s="3" t="n">
-        <v>11525.87983689422</v>
+        <v>11525.87904435749</v>
       </c>
     </row>
     <row r="779">
@@ -13281,7 +13281,7 @@
         <v>11023.64919987808</v>
       </c>
       <c r="D779" s="3" t="n">
-        <v>11525.87983689422</v>
+        <v>11525.87904435749</v>
       </c>
     </row>
     <row r="780">
@@ -13297,7 +13297,7 @@
         <v>11062.49656175473</v>
       </c>
       <c r="D780" s="3" t="n">
-        <v>11599.05626811137</v>
+        <v>11599.05706258964</v>
       </c>
     </row>
     <row r="781">
@@ -13345,7 +13345,7 @@
         <v>11095.89056765962</v>
       </c>
       <c r="D783" s="3" t="n">
-        <v>11719.60157054189</v>
+        <v>11719.60078484764</v>
       </c>
     </row>
     <row r="784">
@@ -13361,7 +13361,7 @@
         <v>11173.58425148998</v>
       </c>
       <c r="D784" s="3" t="n">
-        <v>11585.92590521448</v>
+        <v>11585.92357117426</v>
       </c>
     </row>
     <row r="785">
@@ -13377,7 +13377,7 @@
         <v>11173.58425148998</v>
       </c>
       <c r="D785" s="3" t="n">
-        <v>11585.92590521448</v>
+        <v>11585.92357117426</v>
       </c>
     </row>
     <row r="786">
@@ -13393,7 +13393,7 @@
         <v>11173.58425148998</v>
       </c>
       <c r="D786" s="3" t="n">
-        <v>11585.92590521448</v>
+        <v>11585.92357117426</v>
       </c>
     </row>
     <row r="787">
@@ -13409,7 +13409,7 @@
         <v>11178.35541800379</v>
       </c>
       <c r="D787" s="3" t="n">
-        <v>11756.25707513947</v>
+        <v>11756.2562901039</v>
       </c>
     </row>
     <row r="788">
@@ -13425,7 +13425,7 @@
         <v>11189.9411996364</v>
       </c>
       <c r="D788" s="3" t="n">
-        <v>11796.81589467018</v>
+        <v>11796.81667765304</v>
       </c>
     </row>
     <row r="789">
@@ -13537,7 +13537,7 @@
         <v>11182.44439505966</v>
       </c>
       <c r="D795" s="3" t="n">
-        <v>11713.54192593627</v>
+        <v>11713.54270206803</v>
       </c>
     </row>
     <row r="796">
@@ -13569,7 +13569,7 @@
         <v>11184.48888358759</v>
       </c>
       <c r="D797" s="3" t="n">
-        <v>11645.74900904363</v>
+        <v>11645.74977899997</v>
       </c>
     </row>
     <row r="798">
@@ -13585,7 +13585,7 @@
         <v>11159.27283179444</v>
       </c>
       <c r="D798" s="3" t="n">
-        <v>11654.47459441613</v>
+        <v>11654.47382164581</v>
       </c>
     </row>
     <row r="799">
@@ -13601,7 +13601,7 @@
         <v>11159.27283179444</v>
       </c>
       <c r="D799" s="3" t="n">
-        <v>11654.47459441613</v>
+        <v>11654.47382164581</v>
       </c>
     </row>
     <row r="800">
@@ -13617,7 +13617,7 @@
         <v>11159.27283179444</v>
       </c>
       <c r="D800" s="3" t="n">
-        <v>11654.47459441613</v>
+        <v>11654.47382164581</v>
       </c>
     </row>
     <row r="801">
@@ -13633,7 +13633,7 @@
         <v>11159.27283179444</v>
       </c>
       <c r="D801" s="3" t="n">
-        <v>11667.50345271051</v>
+        <v>11667.50267907628</v>
       </c>
     </row>
     <row r="802">
@@ -13649,7 +13649,7 @@
         <v>11206.29710785987</v>
       </c>
       <c r="D802" s="3" t="n">
-        <v>11620.16637025563</v>
+        <v>11620.16559542394</v>
       </c>
     </row>
     <row r="803">
@@ -13681,7 +13681,7 @@
         <v>11147.68705016183</v>
       </c>
       <c r="D804" s="3" t="n">
-        <v>11604.81397170129</v>
+        <v>11604.81240630017</v>
       </c>
     </row>
     <row r="805">
@@ -13697,7 +13697,7 @@
         <v>11126.55893550159</v>
       </c>
       <c r="D805" s="3" t="n">
-        <v>11599.88210834974</v>
+        <v>11599.88054575406</v>
       </c>
     </row>
     <row r="806">
@@ -13713,7 +13713,7 @@
         <v>11126.55893550159</v>
       </c>
       <c r="D806" s="3" t="n">
-        <v>11599.88210834974</v>
+        <v>11599.88054575406</v>
       </c>
     </row>
     <row r="807">
@@ -13729,7 +13729,7 @@
         <v>11126.55893550159</v>
       </c>
       <c r="D807" s="3" t="n">
-        <v>11599.88210834974</v>
+        <v>11599.88054575406</v>
       </c>
     </row>
     <row r="808">
@@ -13745,7 +13745,7 @@
         <v>11149.73153868976</v>
       </c>
       <c r="D808" s="3" t="n">
-        <v>11771.01910264879</v>
+        <v>11771.01753931753</v>
       </c>
     </row>
     <row r="809">
@@ -13777,7 +13777,7 @@
         <v>11232.19534911097</v>
       </c>
       <c r="D810" s="3" t="n">
-        <v>11830.2374969708</v>
+        <v>11830.23593223675</v>
       </c>
     </row>
     <row r="811">
@@ -13809,7 +13809,7 @@
         <v>11270.36052152968</v>
       </c>
       <c r="D812" s="3" t="n">
-        <v>11780.17475109353</v>
+        <v>11780.17630881402</v>
       </c>
     </row>
     <row r="813">
@@ -13825,7 +13825,7 @@
         <v>11270.36052152968</v>
       </c>
       <c r="D813" s="3" t="n">
-        <v>11780.17475109353</v>
+        <v>11780.17630881402</v>
       </c>
     </row>
     <row r="814">
@@ -13841,7 +13841,7 @@
         <v>11270.36052152968</v>
       </c>
       <c r="D814" s="3" t="n">
-        <v>11780.17475109353</v>
+        <v>11780.17630881402</v>
       </c>
     </row>
     <row r="815">
@@ -13857,7 +13857,7 @@
         <v>11278.53951556437</v>
       </c>
       <c r="D815" s="3" t="n">
-        <v>11818.85514217604</v>
+        <v>11818.85670501133</v>
       </c>
     </row>
     <row r="816">
@@ -13873,7 +13873,7 @@
         <v>11305.80005588546</v>
       </c>
       <c r="D816" s="3" t="n">
-        <v>11775.46536460613</v>
+        <v>11775.46614602378</v>
       </c>
     </row>
     <row r="817">
@@ -13889,7 +13889,7 @@
         <v>11231.51419957598</v>
       </c>
       <c r="D817" s="3" t="n">
-        <v>11782.04316328003</v>
+        <v>11782.04159083118</v>
       </c>
     </row>
     <row r="818">
@@ -13905,7 +13905,7 @@
         <v>11276.49502703644</v>
       </c>
       <c r="D818" s="3" t="n">
-        <v>11879.19051687507</v>
+        <v>11879.18973115518</v>
       </c>
     </row>
     <row r="819">
@@ -13969,7 +13969,7 @@
         <v>11442.10483733681</v>
       </c>
       <c r="D822" s="3" t="n">
-        <v>12045.49057011694</v>
+        <v>12045.49135536636</v>
       </c>
     </row>
     <row r="823">
@@ -14001,7 +14001,7 @@
         <v>11518.43518217422</v>
       </c>
       <c r="D824" s="3" t="n">
-        <v>12132.15983859003</v>
+        <v>12132.16141406682</v>
       </c>
     </row>
     <row r="825">
@@ -14017,7 +14017,7 @@
         <v>11566.82383715555</v>
       </c>
       <c r="D825" s="3" t="n">
-        <v>12171.39217818024</v>
+        <v>12171.39375020154</v>
       </c>
     </row>
     <row r="826">
@@ -14033,7 +14033,7 @@
         <v>11581.81744630904</v>
       </c>
       <c r="D826" s="3" t="n">
-        <v>12194.81897505663</v>
+        <v>12194.81976358189</v>
       </c>
     </row>
     <row r="827">
@@ -14049,7 +14049,7 @@
         <v>11581.81744630904</v>
       </c>
       <c r="D827" s="3" t="n">
-        <v>12194.81897505663</v>
+        <v>12194.81976358189</v>
       </c>
     </row>
     <row r="828">
@@ -14065,7 +14065,7 @@
         <v>11581.81744630904</v>
       </c>
       <c r="D828" s="3" t="n">
-        <v>12194.81897505663</v>
+        <v>12194.81976358189</v>
       </c>
     </row>
     <row r="829">
@@ -14081,7 +14081,7 @@
         <v>11626.79827376949</v>
       </c>
       <c r="D829" s="3" t="n">
-        <v>12295.39493163776</v>
+        <v>12295.39256529222</v>
       </c>
     </row>
     <row r="830">
@@ -14097,7 +14097,7 @@
         <v>11660.19227967438</v>
       </c>
       <c r="D830" s="3" t="n">
-        <v>12296.14331358161</v>
+        <v>12296.14252414113</v>
       </c>
     </row>
     <row r="831">
@@ -14129,7 +14129,7 @@
         <v>11544.33342342533</v>
       </c>
       <c r="D832" s="3" t="n">
-        <v>12288.46126455213</v>
+        <v>12288.46205622496</v>
       </c>
     </row>
     <row r="833">
@@ -14145,7 +14145,7 @@
         <v>11726.30018187213</v>
       </c>
       <c r="D833" s="3" t="n">
-        <v>12337.06134508499</v>
+        <v>12337.06213160883</v>
       </c>
     </row>
     <row r="834">
@@ -14161,7 +14161,7 @@
         <v>11726.30018187213</v>
       </c>
       <c r="D834" s="3" t="n">
-        <v>12337.06134508499</v>
+        <v>12337.06213160883</v>
       </c>
     </row>
     <row r="835">
@@ -14177,7 +14177,7 @@
         <v>11726.30018187213</v>
       </c>
       <c r="D835" s="3" t="n">
-        <v>12337.06134508499</v>
+        <v>12337.06213160883</v>
       </c>
     </row>
     <row r="836">
@@ -14193,7 +14193,7 @@
         <v>11746.06495753943</v>
       </c>
       <c r="D836" s="3" t="n">
-        <v>12400.01430704833</v>
+        <v>12400.01351362204</v>
       </c>
     </row>
     <row r="837">
@@ -14209,7 +14209,7 @@
         <v>11772.64434832552</v>
       </c>
       <c r="D837" s="3" t="n">
-        <v>12480.25538480747</v>
+        <v>12480.25458855869</v>
       </c>
     </row>
     <row r="838">
@@ -14241,7 +14241,7 @@
         <v>11829.89210695358</v>
       </c>
       <c r="D839" s="3" t="n">
-        <v>12550.27958275834</v>
+        <v>12550.27878901563</v>
       </c>
     </row>
     <row r="840">
@@ -14257,7 +14257,7 @@
         <v>11849.65584269793</v>
       </c>
       <c r="D840" s="3" t="n">
-        <v>12621.04416037839</v>
+        <v>12621.04495400995</v>
       </c>
     </row>
     <row r="841">
@@ -14273,7 +14273,7 @@
         <v>11849.65584269793</v>
       </c>
       <c r="D841" s="3" t="n">
-        <v>12621.04416037839</v>
+        <v>12621.04495400995</v>
       </c>
     </row>
     <row r="842">
@@ -14289,7 +14289,7 @@
         <v>11849.65584269793</v>
       </c>
       <c r="D842" s="3" t="n">
-        <v>12621.04416037839</v>
+        <v>12621.04495400995</v>
       </c>
     </row>
     <row r="843">
@@ -14305,7 +14305,7 @@
         <v>11947.11430219558</v>
       </c>
       <c r="D843" s="3" t="n">
-        <v>12591.03176799597</v>
+        <v>12591.03256008796</v>
       </c>
     </row>
     <row r="844">
@@ -14321,7 +14321,7 @@
         <v>11831.25544594652</v>
       </c>
       <c r="D844" s="3" t="n">
-        <v>12447.51652424408</v>
+        <v>12447.51573024479</v>
       </c>
     </row>
     <row r="845">
@@ -14337,7 +14337,7 @@
         <v>11848.29354362794</v>
       </c>
       <c r="D845" s="3" t="n">
-        <v>12634.91766381713</v>
+        <v>12634.91846251211</v>
       </c>
     </row>
     <row r="846">
@@ -14353,7 +14353,7 @@
         <v>11904.85911279805</v>
       </c>
       <c r="D846" s="3" t="n">
-        <v>12694.57531185248</v>
+        <v>12694.57451488526</v>
       </c>
     </row>
     <row r="847">
@@ -14433,7 +14433,7 @@
         <v>11814.8984978001</v>
       </c>
       <c r="D851" s="3" t="n">
-        <v>12511.39565445421</v>
+        <v>12511.39486068576</v>
       </c>
     </row>
     <row r="852">
@@ -14449,7 +14449,7 @@
         <v>11801.94937717454</v>
       </c>
       <c r="D852" s="3" t="n">
-        <v>12479.00875528825</v>
+        <v>12479.00717329399</v>
       </c>
     </row>
     <row r="853">
@@ -14465,7 +14465,7 @@
         <v>12001.63642276071</v>
       </c>
       <c r="D853" s="3" t="n">
-        <v>12728.72722280212</v>
+        <v>12728.72959420268</v>
       </c>
     </row>
     <row r="854">
@@ -14529,7 +14529,7 @@
         <v>12002.9987218307</v>
       </c>
       <c r="D857" s="3" t="n">
-        <v>12691.26763679148</v>
+        <v>12691.26684629894</v>
       </c>
     </row>
     <row r="858">
@@ -14545,7 +14545,7 @@
         <v>11985.27947461428</v>
       </c>
       <c r="D858" s="3" t="n">
-        <v>12678.66268153161</v>
+        <v>12678.66189328859</v>
       </c>
     </row>
     <row r="859">
@@ -14577,7 +14577,7 @@
         <v>12019.35566997712</v>
       </c>
       <c r="D860" s="3" t="n">
-        <v>12721.62659811942</v>
+        <v>12721.62580899542</v>
       </c>
     </row>
     <row r="861">
@@ -14593,7 +14593,7 @@
         <v>12103.86500884922</v>
       </c>
       <c r="D861" s="3" t="n">
-        <v>12881.28434368128</v>
+        <v>12881.2835520854</v>
       </c>
     </row>
     <row r="862">
@@ -14609,7 +14609,7 @@
         <v>12103.86500884922</v>
       </c>
       <c r="D862" s="3" t="n">
-        <v>12881.28434368128</v>
+        <v>12881.2835520854</v>
       </c>
     </row>
     <row r="863">
@@ -14625,7 +14625,7 @@
         <v>12103.86500884922</v>
       </c>
       <c r="D863" s="3" t="n">
-        <v>12881.28434368128</v>
+        <v>12881.2835520854</v>
       </c>
     </row>
     <row r="864">
@@ -14641,7 +14641,7 @@
         <v>12102.50166985628</v>
       </c>
       <c r="D864" s="3" t="n">
-        <v>12822.70263458922</v>
+        <v>12822.70184574745</v>
       </c>
     </row>
     <row r="865">
@@ -14673,7 +14673,7 @@
         <v>12058.88418138877</v>
       </c>
       <c r="D866" s="3" t="n">
-        <v>12743.24298129753</v>
+        <v>12743.24376917276</v>
       </c>
     </row>
     <row r="867">
@@ -14689,7 +14689,7 @@
         <v>12112.72411249595</v>
       </c>
       <c r="D867" s="3" t="n">
-        <v>12818.3249884288</v>
+        <v>12818.32341897344</v>
       </c>
     </row>
     <row r="868">
@@ -14769,7 +14769,7 @@
         <v>12141.34799180998</v>
       </c>
       <c r="D872" s="3" t="n">
-        <v>12829.93115637688</v>
+        <v>12829.92959148892</v>
       </c>
     </row>
     <row r="873">
@@ -14785,7 +14785,7 @@
         <v>12141.34799180998</v>
       </c>
       <c r="D873" s="3" t="n">
-        <v>12814.01980940503</v>
+        <v>12814.02137480615</v>
       </c>
     </row>
     <row r="874">
@@ -14801,7 +14801,7 @@
         <v>12148.84479638673</v>
       </c>
       <c r="D874" s="3" t="n">
-        <v>12756.54551102544</v>
+        <v>12756.54629175877</v>
       </c>
     </row>
     <row r="875">
@@ -14881,7 +14881,7 @@
         <v>12201.32242842392</v>
       </c>
       <c r="D879" s="3" t="n">
-        <v>12910.95528781637</v>
+        <v>12910.95450124123</v>
       </c>
     </row>
     <row r="880">
@@ -14897,7 +14897,7 @@
         <v>12229.26515820296</v>
       </c>
       <c r="D880" s="3" t="n">
-        <v>13043.1255946528</v>
+        <v>13043.12638199779</v>
       </c>
     </row>
     <row r="881">
@@ -14913,7 +14913,7 @@
         <v>12406.46075013594</v>
       </c>
       <c r="D881" s="3" t="n">
-        <v>12997.80465118463</v>
+        <v>12997.80386915981</v>
       </c>
     </row>
     <row r="882">
@@ -14929,7 +14929,7 @@
         <v>12400.32728455214</v>
       </c>
       <c r="D882" s="3" t="n">
-        <v>13062.55483125622</v>
+        <v>13062.55246901595</v>
       </c>
     </row>
     <row r="883">
@@ -14945,7 +14945,7 @@
         <v>12400.32728455214</v>
       </c>
       <c r="D883" s="3" t="n">
-        <v>13062.55483125622</v>
+        <v>13062.55246901595</v>
       </c>
     </row>
     <row r="884">
@@ -14961,7 +14961,7 @@
         <v>12400.32728455214</v>
       </c>
       <c r="D884" s="3" t="n">
-        <v>13062.55483125622</v>
+        <v>13062.55246901595</v>
       </c>
     </row>
     <row r="885">
@@ -15009,7 +15009,7 @@
         <v>12385.33367539866</v>
       </c>
       <c r="D887" s="3" t="n">
-        <v>13147.9947287729</v>
+        <v>13147.99551836732</v>
       </c>
     </row>
     <row r="888">
@@ -15025,7 +15025,7 @@
         <v>12464.39069822195</v>
       </c>
       <c r="D888" s="3" t="n">
-        <v>13168.54963955153</v>
+        <v>13168.55043053156</v>
       </c>
     </row>
     <row r="889">
@@ -15041,7 +15041,7 @@
         <v>12464.39069822195</v>
       </c>
       <c r="D889" s="3" t="n">
-        <v>13191.61880783227</v>
+        <v>13191.61960019797</v>
       </c>
     </row>
     <row r="890">
@@ -15057,7 +15057,7 @@
         <v>12464.39069822195</v>
       </c>
       <c r="D890" s="3" t="n">
-        <v>13191.61880783227</v>
+        <v>13191.61960019797</v>
       </c>
     </row>
     <row r="891">
@@ -15073,7 +15073,7 @@
         <v>12464.39069822195</v>
       </c>
       <c r="D891" s="3" t="n">
-        <v>13191.61880783227</v>
+        <v>13191.61960019797</v>
       </c>
     </row>
     <row r="892">
@@ -15089,7 +15089,7 @@
         <v>12464.39069822195</v>
       </c>
       <c r="D892" s="3" t="n">
-        <v>13170.79722736024</v>
+        <v>13170.799604842</v>
       </c>
     </row>
     <row r="893">
@@ -15105,7 +15105,7 @@
         <v>12360.7987731405</v>
       </c>
       <c r="D893" s="3" t="n">
-        <v>13154.71503411915</v>
+        <v>13154.71423752825</v>
       </c>
     </row>
     <row r="894">
@@ -15121,7 +15121,7 @@
         <v>12371.70340523811</v>
       </c>
       <c r="D894" s="3" t="n">
-        <v>13130.84497033557</v>
+        <v>13130.84258751657</v>
       </c>
     </row>
     <row r="895">
@@ -15137,7 +15137,7 @@
         <v>12382.60803733573</v>
       </c>
       <c r="D895" s="3" t="n">
-        <v>12887.04251251171</v>
+        <v>12887.0433016699</v>
       </c>
     </row>
     <row r="896">
@@ -15153,7 +15153,7 @@
         <v>12294.69087094275</v>
       </c>
       <c r="D896" s="3" t="n">
-        <v>13023.22404853831</v>
+        <v>13023.2256270429</v>
       </c>
     </row>
     <row r="897">
@@ -15169,7 +15169,7 @@
         <v>12294.69087094275</v>
       </c>
       <c r="D897" s="3" t="n">
-        <v>13023.22404853831</v>
+        <v>13023.2256270429</v>
       </c>
     </row>
     <row r="898">
@@ -15185,7 +15185,7 @@
         <v>12294.69087094275</v>
       </c>
       <c r="D898" s="3" t="n">
-        <v>13023.22404853831</v>
+        <v>13023.2256270429</v>
       </c>
     </row>
     <row r="899">
@@ -15201,7 +15201,7 @@
         <v>12319.22577320091</v>
       </c>
       <c r="D899" s="3" t="n">
-        <v>13038.4172811513</v>
+        <v>13038.41807088261</v>
       </c>
     </row>
     <row r="900">
@@ -15233,7 +15233,7 @@
         <v>12304.91435350538</v>
       </c>
       <c r="D901" s="3" t="n">
-        <v>12888.50351455798</v>
+        <v>12888.50193928649</v>
       </c>
     </row>
     <row r="902">
@@ -15249,7 +15249,7 @@
         <v>12321.9524511868</v>
       </c>
       <c r="D902" s="3" t="n">
-        <v>13127.91736446822</v>
+        <v>13127.9157719535</v>
       </c>
     </row>
     <row r="903">
@@ -15329,7 +15329,7 @@
         <v>12162.47610647022</v>
       </c>
       <c r="D907" s="3" t="n">
-        <v>12900.46735816442</v>
+        <v>12900.46655321699</v>
       </c>
     </row>
     <row r="908">
@@ -15361,7 +15361,7 @@
         <v>12127.03657211444</v>
       </c>
       <c r="D909" s="3" t="n">
-        <v>12745.37482632069</v>
+        <v>12745.37562797507</v>
       </c>
     </row>
     <row r="910">
@@ -15377,7 +15377,7 @@
         <v>12008.45103787951</v>
       </c>
       <c r="D910" s="3" t="n">
-        <v>12664.0539624136</v>
+        <v>12664.05476596686</v>
       </c>
     </row>
     <row r="911">
@@ -15393,7 +15393,7 @@
         <v>12008.45103787951</v>
       </c>
       <c r="D911" s="3" t="n">
-        <v>12664.0539624136</v>
+        <v>12664.05476596686</v>
       </c>
     </row>
     <row r="912">
@@ -15409,7 +15409,7 @@
         <v>12008.45103787951</v>
       </c>
       <c r="D912" s="3" t="n">
-        <v>12664.0539624136</v>
+        <v>12664.05476596686</v>
       </c>
     </row>
     <row r="913">
@@ -15425,7 +15425,7 @@
         <v>12032.30479060267</v>
       </c>
       <c r="D913" s="3" t="n">
-        <v>12763.80917890861</v>
+        <v>12763.81158638653</v>
       </c>
     </row>
     <row r="914">
@@ -15435,13 +15435,13 @@
         </is>
       </c>
       <c r="B914" s="3" t="n">
-        <v>10103.42</v>
+        <v>10103.43</v>
       </c>
       <c r="C914" s="3" t="n">
         <v>12163.83840554021</v>
       </c>
       <c r="D914" s="3" t="n">
-        <v>12920.36659166479</v>
+        <v>12920.36578885572</v>
       </c>
     </row>
     <row r="915">
@@ -15473,7 +15473,7 @@
         <v>12022.08130804005</v>
       </c>
       <c r="D916" s="3" t="n">
-        <v>12810.0749073758</v>
+        <v>12810.07570674653</v>
       </c>
     </row>
     <row r="917">
@@ -15489,7 +15489,7 @@
         <v>12238.12530177264</v>
       </c>
       <c r="D917" s="3" t="n">
-        <v>12895.59857633805</v>
+        <v>12895.59937349343</v>
       </c>
     </row>
     <row r="918">
@@ -15505,7 +15505,7 @@
         <v>12238.12530177264</v>
       </c>
       <c r="D918" s="3" t="n">
-        <v>12895.59857633805</v>
+        <v>12895.59937349343</v>
       </c>
     </row>
     <row r="919">
@@ -15521,7 +15521,7 @@
         <v>12238.12530177264</v>
       </c>
       <c r="D919" s="3" t="n">
-        <v>12895.59857633805</v>
+        <v>12895.59937349343</v>
       </c>
     </row>
     <row r="920">
@@ -15553,7 +15553,7 @@
         <v>12209.50038253566</v>
       </c>
       <c r="D921" s="3" t="n">
-        <v>12752.79870736289</v>
+        <v>12752.7979091725</v>
       </c>
     </row>
     <row r="922">
@@ -15569,7 +15569,7 @@
         <v>12209.50038253566</v>
       </c>
       <c r="D922" s="3" t="n">
-        <v>12769.95947841479</v>
+        <v>12769.95867654654</v>
       </c>
     </row>
     <row r="923">
@@ -15585,7 +15585,7 @@
         <v>12119.5397675377</v>
       </c>
       <c r="D923" s="3" t="n">
-        <v>12823.27072638516</v>
+        <v>12823.27232189354</v>
       </c>
     </row>
     <row r="924">
@@ -15601,7 +15601,7 @@
         <v>12218.36052610534</v>
       </c>
       <c r="D924" s="3" t="n">
-        <v>12968.29915780449</v>
+        <v>12968.30075160209</v>
       </c>
     </row>
     <row r="925">
@@ -15617,7 +15617,7 @@
         <v>12218.36052610534</v>
       </c>
       <c r="D925" s="3" t="n">
-        <v>12968.29915780449</v>
+        <v>12968.30075160209</v>
       </c>
     </row>
     <row r="926">
@@ -15633,7 +15633,7 @@
         <v>12218.36052610534</v>
       </c>
       <c r="D926" s="3" t="n">
-        <v>12968.29915780449</v>
+        <v>12968.30075160209</v>
       </c>
     </row>
     <row r="927">
@@ -15649,7 +15649,7 @@
         <v>12311.04781908918</v>
       </c>
       <c r="D927" s="3" t="n">
-        <v>13071.70723184147</v>
+        <v>13071.70564175579</v>
       </c>
     </row>
     <row r="928">
@@ -15665,7 +15665,7 @@
         <v>12395.55715796128</v>
       </c>
       <c r="D928" s="3" t="n">
-        <v>13074.72745369843</v>
+        <v>13074.7266593484</v>
       </c>
     </row>
     <row r="929">
@@ -15697,7 +15697,7 @@
         <v>12422.81769828237</v>
       </c>
       <c r="D930" s="3" t="n">
-        <v>13176.53815644364</v>
+        <v>13176.53895231609</v>
       </c>
     </row>
     <row r="931">
@@ -15713,7 +15713,7 @@
         <v>12464.39069822195</v>
       </c>
       <c r="D931" s="3" t="n">
-        <v>13146.72169356259</v>
+        <v>13146.72407271251</v>
       </c>
     </row>
     <row r="932">
@@ -15729,7 +15729,7 @@
         <v>12464.39069822195</v>
       </c>
       <c r="D932" s="3" t="n">
-        <v>13146.72169356259</v>
+        <v>13146.72407271251</v>
       </c>
     </row>
     <row r="933">
@@ -15745,7 +15745,7 @@
         <v>12464.39069822195</v>
       </c>
       <c r="D933" s="3" t="n">
-        <v>13146.72169356259</v>
+        <v>13146.72407271251</v>
       </c>
     </row>
     <row r="934">
@@ -15761,7 +15761,7 @@
         <v>12444.6269624776</v>
       </c>
       <c r="D934" s="3" t="n">
-        <v>13166.49482380654</v>
+        <v>13166.49720621517</v>
       </c>
     </row>
     <row r="935">
@@ -15777,7 +15777,7 @@
         <v>12437.81130743586</v>
       </c>
       <c r="D935" s="3" t="n">
-        <v>13198.55492461691</v>
+        <v>13198.55571705097</v>
       </c>
     </row>
     <row r="936">
@@ -15793,7 +15793,7 @@
         <v>12528.45411189176</v>
       </c>
       <c r="D936" s="3" t="n">
-        <v>13336.03461039299</v>
+        <v>13336.03302860399</v>
       </c>
     </row>
     <row r="937">
@@ -15825,7 +15825,7 @@
         <v>12540.03989352437</v>
       </c>
       <c r="D938" s="3" t="n">
-        <v>13262.43302875722</v>
+        <v>13262.43617683687</v>
       </c>
     </row>
     <row r="939">
@@ -15841,7 +15841,7 @@
         <v>12540.03989352437</v>
       </c>
       <c r="D939" s="3" t="n">
-        <v>13262.43302875722</v>
+        <v>13262.43617683687</v>
       </c>
     </row>
     <row r="940">
@@ -15857,7 +15857,7 @@
         <v>12540.03989352437</v>
       </c>
       <c r="D940" s="3" t="n">
-        <v>13262.43302875722</v>
+        <v>13262.43617683687</v>
       </c>
     </row>
     <row r="941">
@@ -15905,7 +15905,7 @@
         <v>12587.06520951276</v>
       </c>
       <c r="D943" s="3" t="n">
-        <v>13287.38943081385</v>
+        <v>13287.38785494363</v>
       </c>
     </row>
     <row r="944">
@@ -15921,7 +15921,7 @@
         <v>12590.47303703363</v>
       </c>
       <c r="D944" s="3" t="n">
-        <v>13226.84500560119</v>
+        <v>13226.84737594985</v>
       </c>
     </row>
     <row r="945">
@@ -15937,7 +15937,7 @@
         <v>12544.12887058024</v>
       </c>
       <c r="D945" s="3" t="n">
-        <v>13329.78095658473</v>
+        <v>13329.7793745221</v>
       </c>
     </row>
     <row r="946">
@@ -15953,7 +15953,7 @@
         <v>12544.12887058024</v>
       </c>
       <c r="D946" s="3" t="n">
-        <v>13329.78095658473</v>
+        <v>13329.7793745221</v>
       </c>
     </row>
     <row r="947">
@@ -15969,7 +15969,7 @@
         <v>12544.12887058024</v>
       </c>
       <c r="D947" s="3" t="n">
-        <v>13329.78095658473</v>
+        <v>13329.7793745221</v>
       </c>
     </row>
     <row r="948">
@@ -15985,7 +15985,7 @@
         <v>12574.11608888721</v>
       </c>
       <c r="D948" s="3" t="n">
-        <v>13286.83106698484</v>
+        <v>13286.82949001978</v>
       </c>
     </row>
     <row r="949">
@@ -16033,7 +16033,7 @@
         <v>12440.53694549878</v>
       </c>
       <c r="D951" s="3" t="n">
-        <v>13171.05179546592</v>
+        <v>13171.05021181237</v>
       </c>
     </row>
     <row r="952">
@@ -16049,7 +16049,7 @@
         <v>12358.75428461256</v>
       </c>
       <c r="D952" s="3" t="n">
-        <v>13249.81331443652</v>
+        <v>13249.81173569244</v>
       </c>
     </row>
     <row r="953">
@@ -16065,7 +16065,7 @@
         <v>12358.75428461256</v>
       </c>
       <c r="D953" s="3" t="n">
-        <v>13249.81331443652</v>
+        <v>13249.81173569244</v>
       </c>
     </row>
     <row r="954">
@@ -16081,7 +16081,7 @@
         <v>12358.75428461256</v>
       </c>
       <c r="D954" s="3" t="n">
-        <v>13249.81331443652</v>
+        <v>13249.81173569244</v>
       </c>
     </row>
     <row r="955">
@@ -16097,7 +16097,7 @@
         <v>12450.76042806141</v>
       </c>
       <c r="D955" s="3" t="n">
-        <v>13239.06425709997</v>
+        <v>13239.06268092181</v>
       </c>
     </row>
     <row r="956">
@@ -16113,7 +16113,7 @@
         <v>12426.90667533824</v>
       </c>
       <c r="D956" s="3" t="n">
-        <v>13187.8383235277</v>
+        <v>13187.83989185406</v>
       </c>
     </row>
     <row r="957">
@@ -16129,7 +16129,7 @@
         <v>12575.47942788015</v>
       </c>
       <c r="D957" s="3" t="n">
-        <v>13375.86973822802</v>
+        <v>13375.87131023227</v>
       </c>
     </row>
     <row r="958">
@@ -16161,7 +16161,7 @@
         <v>12684.52262908746</v>
       </c>
       <c r="D959" s="3" t="n">
-        <v>13343.95317184069</v>
+        <v>13343.95160164963</v>
       </c>
     </row>
     <row r="960">
@@ -16177,7 +16177,7 @@
         <v>12684.52262908746</v>
       </c>
       <c r="D960" s="3" t="n">
-        <v>13343.95317184069</v>
+        <v>13343.95160164963</v>
       </c>
     </row>
     <row r="961">
@@ -16193,7 +16193,7 @@
         <v>12684.52262908746</v>
       </c>
       <c r="D961" s="3" t="n">
-        <v>13343.95317184069</v>
+        <v>13343.95160164963</v>
       </c>
     </row>
     <row r="962">
@@ -16209,7 +16209,7 @@
         <v>12737.68141065965</v>
       </c>
       <c r="D962" s="3" t="n">
-        <v>13528.67075663909</v>
+        <v>13528.6723436626</v>
       </c>
     </row>
     <row r="963">
@@ -16225,7 +16225,7 @@
         <v>12719.28101390824</v>
       </c>
       <c r="D963" s="3" t="n">
-        <v>13579.67099739108</v>
+        <v>13579.66940821211</v>
       </c>
     </row>
     <row r="964">
@@ -16241,7 +16241,7 @@
         <v>12781.98108858511</v>
       </c>
       <c r="D964" s="3" t="n">
-        <v>13721.71058166884</v>
+        <v>13721.70898894873</v>
       </c>
     </row>
     <row r="965">
@@ -16257,7 +16257,7 @@
         <v>12781.29889912716</v>
       </c>
       <c r="D965" s="3" t="n">
-        <v>13656.74098763679</v>
+        <v>13656.74573361954</v>
       </c>
     </row>
     <row r="966">
@@ -16321,7 +16321,7 @@
         <v>12824.23523805968</v>
       </c>
       <c r="D969" s="3" t="n">
-        <v>13916.64458424788</v>
+        <v>13916.64618264724</v>
       </c>
     </row>
     <row r="970">
@@ -16369,7 +16369,7 @@
         <v>12965.31118602485</v>
       </c>
       <c r="D972" s="3" t="n">
-        <v>13850.21789202292</v>
+        <v>13850.22107414421</v>
       </c>
     </row>
     <row r="973">
@@ -16385,7 +16385,7 @@
         <v>12914.87804251559</v>
       </c>
       <c r="D973" s="3" t="n">
-        <v>13889.94491679181</v>
+        <v>13889.94331902551</v>
       </c>
     </row>
     <row r="974">
@@ -16401,7 +16401,7 @@
         <v>12914.87804251559</v>
       </c>
       <c r="D974" s="3" t="n">
-        <v>13889.94491679181</v>
+        <v>13889.94331902551</v>
       </c>
     </row>
     <row r="975">
@@ -16417,7 +16417,7 @@
         <v>12914.87804251559</v>
       </c>
       <c r="D975" s="3" t="n">
-        <v>13889.94491679181</v>
+        <v>13889.94331902551</v>
       </c>
     </row>
     <row r="976">
@@ -16433,7 +16433,7 @@
         <v>12942.13858283667</v>
       </c>
       <c r="D976" s="3" t="n">
-        <v>13868.95294952591</v>
+        <v>13868.95455008052</v>
       </c>
     </row>
     <row r="977">
@@ -16449,7 +16449,7 @@
         <v>12932.597289732</v>
       </c>
       <c r="D977" s="3" t="n">
-        <v>13864.0344192502</v>
+        <v>13864.03282540126</v>
       </c>
     </row>
     <row r="978">
@@ -16465,7 +16465,7 @@
         <v>12926.4638241482</v>
       </c>
       <c r="D978" s="3" t="n">
-        <v>13911.28516637128</v>
+        <v>13911.28197179656</v>
       </c>
     </row>
     <row r="979">
@@ -16481,7 +16481,7 @@
         <v>12925.7826746132</v>
       </c>
       <c r="D979" s="3" t="n">
-        <v>13971.7116522285</v>
+        <v>13971.71485563017</v>
       </c>
     </row>
     <row r="980">
@@ -16577,7 +16577,7 @@
         <v>12960.54001951103</v>
       </c>
       <c r="D985" s="3" t="n">
-        <v>14012.26015595211</v>
+        <v>14012.26174747455</v>
       </c>
     </row>
     <row r="986">
@@ -16593,7 +16593,7 @@
         <v>12989.84608828301</v>
       </c>
       <c r="D986" s="3" t="n">
-        <v>13953.97532139368</v>
+        <v>13953.97690629609</v>
       </c>
     </row>
     <row r="987">
@@ -16609,7 +16609,7 @@
         <v>12994.61621487387</v>
       </c>
       <c r="D987" s="3" t="n">
-        <v>14011.86940311516</v>
+        <v>14011.87256782238</v>
       </c>
     </row>
     <row r="988">
@@ -16625,7 +16625,7 @@
         <v>12994.61621487387</v>
       </c>
       <c r="D988" s="3" t="n">
-        <v>14011.86940311516</v>
+        <v>14011.87256782238</v>
       </c>
     </row>
     <row r="989">
@@ -16641,7 +16641,7 @@
         <v>12994.61621487387</v>
       </c>
       <c r="D989" s="3" t="n">
-        <v>14011.86940311516</v>
+        <v>14011.87256782238</v>
       </c>
     </row>
     <row r="990">
@@ -16657,7 +16657,7 @@
         <v>13017.78777813909</v>
       </c>
       <c r="D990" s="3" t="n">
-        <v>14008.1702441116</v>
+        <v>14008.17182422415</v>
       </c>
     </row>
     <row r="991">
@@ -16689,7 +16689,7 @@
         <v>13089.34799638564</v>
       </c>
       <c r="D992" s="3" t="n">
-        <v>14175.26128295351</v>
+        <v>14175.26286470834</v>
       </c>
     </row>
     <row r="993">
@@ -16705,7 +16705,7 @@
         <v>13066.17643312042</v>
       </c>
       <c r="D993" s="3" t="n">
-        <v>14029.02038957679</v>
+        <v>14029.02354768097</v>
       </c>
     </row>
     <row r="994">
@@ -16769,7 +16769,7 @@
         <v>13131.60214586022</v>
       </c>
       <c r="D997" s="3" t="n">
-        <v>14088.39659253238</v>
+        <v>14088.39816400623</v>
       </c>
     </row>
     <row r="998">
@@ -16801,7 +16801,7 @@
         <v>13013.69880108322</v>
       </c>
       <c r="D999" s="3" t="n">
-        <v>13951.48537919751</v>
+        <v>13951.48381016979</v>
       </c>
     </row>
     <row r="1000">
@@ -16817,7 +16817,7 @@
         <v>12938.73179523875</v>
       </c>
       <c r="D1000" s="3" t="n">
-        <v>13796.5737751079</v>
+        <v>13796.57221148585</v>
       </c>
     </row>
     <row r="1001">
@@ -16881,7 +16881,7 @@
         <v>12923.05599662732</v>
       </c>
       <c r="D1004" s="3" t="n">
-        <v>13898.36310505228</v>
+        <v>13898.36153554559</v>
       </c>
     </row>
     <row r="1005">
@@ -16913,7 +16913,7 @@
         <v>12819.46511146882</v>
       </c>
       <c r="D1006" s="3" t="n">
-        <v>13622.69005322656</v>
+        <v>13622.68532366558</v>
       </c>
     </row>
     <row r="1007">
@@ -16929,7 +16929,7 @@
         <v>12752.67501981313</v>
       </c>
       <c r="D1007" s="3" t="n">
-        <v>13565.68119585515</v>
+        <v>13565.67803956432</v>
       </c>
     </row>
     <row r="1008">
@@ -16945,7 +16945,7 @@
         <v>12777.89211152924</v>
       </c>
       <c r="D1008" s="3" t="n">
-        <v>13702.73988538622</v>
+        <v>13702.74146182098</v>
       </c>
     </row>
     <row r="1009">
@@ -16961,7 +16961,7 @@
         <v>12777.89211152924</v>
       </c>
       <c r="D1009" s="3" t="n">
-        <v>13702.73988538622</v>
+        <v>13702.74146182098</v>
       </c>
     </row>
     <row r="1010">
@@ -16977,7 +16977,7 @@
         <v>12777.89211152924</v>
       </c>
       <c r="D1010" s="3" t="n">
-        <v>13702.73988538622</v>
+        <v>13702.74146182098</v>
       </c>
     </row>
     <row r="1011">
@@ -16993,7 +16993,7 @@
         <v>12801.74482432945</v>
       </c>
       <c r="D1011" s="3" t="n">
-        <v>13707.67232553361</v>
+        <v>13707.66917338262</v>
       </c>
     </row>
     <row r="1012">
@@ -17009,7 +17009,7 @@
         <v>12811.96830689208</v>
       </c>
       <c r="D1012" s="3" t="n">
-        <v>13681.44512366627</v>
+        <v>13681.44354259566</v>
       </c>
     </row>
     <row r="1013">
@@ -17025,7 +17025,7 @@
         <v>13002.11301945061</v>
       </c>
       <c r="D1013" s="3" t="n">
-        <v>13908.19338197522</v>
+        <v>13908.19496354194</v>
       </c>
     </row>
     <row r="1014">
@@ -17041,7 +17041,7 @@
         <v>12874.66838156895</v>
       </c>
       <c r="D1014" s="3" t="n">
-        <v>13701.3076555334</v>
+        <v>13701.30449469224</v>
       </c>
     </row>
     <row r="1015">
@@ -17057,7 +17057,7 @@
         <v>12358.07313507757</v>
       </c>
       <c r="D1015" s="3" t="n">
-        <v>13491.4702323249</v>
+        <v>13491.47181806554</v>
       </c>
     </row>
     <row r="1016">
@@ -17073,7 +17073,7 @@
         <v>12358.07313507757</v>
       </c>
       <c r="D1016" s="3" t="n">
-        <v>13491.4702323249</v>
+        <v>13491.47181806554</v>
       </c>
     </row>
     <row r="1017">
@@ -17089,7 +17089,7 @@
         <v>12358.07313507757</v>
       </c>
       <c r="D1017" s="3" t="n">
-        <v>13491.4702323249</v>
+        <v>13491.47181806554</v>
       </c>
     </row>
     <row r="1018">
@@ -17105,7 +17105,7 @@
         <v>12080.01125612606</v>
       </c>
       <c r="D1018" s="3" t="n">
-        <v>12950.60588797646</v>
+        <v>12950.60667189161</v>
       </c>
     </row>
     <row r="1019">
@@ -17121,7 +17121,7 @@
         <v>12187.69215826338</v>
       </c>
       <c r="D1019" s="3" t="n">
-        <v>13022.09193866686</v>
+        <v>13022.09037658421</v>
       </c>
     </row>
     <row r="1020">
@@ -17137,7 +17137,7 @@
         <v>12357.39198554258</v>
       </c>
       <c r="D1020" s="3" t="n">
-        <v>12964.37234956764</v>
+        <v>12964.3715667559</v>
       </c>
     </row>
     <row r="1021">
@@ -17153,7 +17153,7 @@
         <v>12357.39198554258</v>
       </c>
       <c r="D1021" s="3" t="n">
-        <v>13261.75544344195</v>
+        <v>13261.75700879185</v>
       </c>
     </row>
     <row r="1022">
@@ -17217,7 +17217,7 @@
         <v>12427.58886479619</v>
       </c>
       <c r="D1025" s="3" t="n">
-        <v>13344.71123329907</v>
+        <v>13344.70966589639</v>
       </c>
     </row>
     <row r="1026">
@@ -17233,7 +17233,7 @@
         <v>12549.58118662904</v>
       </c>
       <c r="D1026" s="3" t="n">
-        <v>13536.3420112268</v>
+        <v>13536.34044704008</v>
       </c>
     </row>
     <row r="1027">
@@ -17249,7 +17249,7 @@
         <v>12580.93174392896</v>
       </c>
       <c r="D1027" s="3" t="n">
-        <v>13504.04923278094</v>
+        <v>13504.05078832888</v>
       </c>
     </row>
     <row r="1028">
@@ -17361,7 +17361,7 @@
         <v>12838.54769767817</v>
       </c>
       <c r="D1034" s="3" t="n">
-        <v>13759.18731640436</v>
+        <v>13759.18885364839</v>
       </c>
     </row>
     <row r="1035">
@@ -17441,7 +17441,7 @@
         <v>12854.90360590165</v>
       </c>
       <c r="D1039" s="3" t="n">
-        <v>13689.53828572057</v>
+        <v>13689.53675672169</v>
       </c>
     </row>
     <row r="1040">
@@ -17473,7 +17473,7 @@
         <v>12858.99258295751</v>
       </c>
       <c r="D1041" s="3" t="n">
-        <v>13640.95348044622</v>
+        <v>13640.95195007891</v>
       </c>
     </row>
     <row r="1042">
@@ -17489,7 +17489,7 @@
         <v>13004.15750797855</v>
       </c>
       <c r="D1042" s="3" t="n">
-        <v>13707.13676114262</v>
+        <v>13707.13522348793</v>
       </c>
     </row>
     <row r="1043">
@@ -17585,7 +17585,7 @@
         <v>12760.85401384782</v>
       </c>
       <c r="D1048" s="3" t="n">
-        <v>13618.61184634016</v>
+        <v>13618.61339458371</v>
       </c>
     </row>
     <row r="1049">
@@ -17601,7 +17601,7 @@
         <v>12672.93684745485</v>
       </c>
       <c r="D1049" s="3" t="n">
-        <v>13546.76223697019</v>
+        <v>13546.76378080034</v>
       </c>
     </row>
     <row r="1050">
@@ -17617,7 +17617,7 @@
         <v>12516.1861408012</v>
       </c>
       <c r="D1050" s="3" t="n">
-        <v>13282.02266145663</v>
+        <v>13282.02112188611</v>
       </c>
     </row>
     <row r="1051">
@@ -17633,7 +17633,7 @@
         <v>12516.1861408012</v>
       </c>
       <c r="D1051" s="3" t="n">
-        <v>13282.02266145663</v>
+        <v>13282.02112188611</v>
       </c>
     </row>
     <row r="1052">
@@ -17649,7 +17649,7 @@
         <v>12516.1861408012</v>
       </c>
       <c r="D1052" s="3" t="n">
-        <v>13282.02266145663</v>
+        <v>13282.02112188611</v>
       </c>
     </row>
     <row r="1053">
@@ -17681,7 +17681,7 @@
         <v>12680.43365203159</v>
       </c>
       <c r="D1054" s="3" t="n">
-        <v>13579.1595618864</v>
+        <v>13579.15801205196</v>
       </c>
     </row>
     <row r="1055">
@@ -17713,7 +17713,7 @@
         <v>12852.85911737371</v>
       </c>
       <c r="D1056" s="3" t="n">
-        <v>13867.46203896403</v>
+        <v>13867.46359254477</v>
       </c>
     </row>
     <row r="1057">
@@ -17729,7 +17729,7 @@
         <v>12946.90974935049</v>
       </c>
       <c r="D1057" s="3" t="n">
-        <v>13855.61864209994</v>
+        <v>13855.62018628927</v>
       </c>
     </row>
     <row r="1058">
@@ -17745,7 +17745,7 @@
         <v>12946.90974935049</v>
       </c>
       <c r="D1058" s="3" t="n">
-        <v>13855.61864209994</v>
+        <v>13855.62018628927</v>
       </c>
     </row>
     <row r="1059">
@@ -17761,7 +17761,7 @@
         <v>12946.90974935049</v>
       </c>
       <c r="D1059" s="3" t="n">
-        <v>13855.61864209994</v>
+        <v>13855.62018628927</v>
       </c>
     </row>
     <row r="1060">
@@ -17825,7 +17825,7 @@
         <v>13083.21453080184</v>
       </c>
       <c r="D1063" s="3" t="n">
-        <v>14029.98031675119</v>
+        <v>14029.98185580851</v>
       </c>
     </row>
     <row r="1064">
@@ -17841,7 +17841,7 @@
         <v>13000.06853092268</v>
       </c>
       <c r="D1064" s="3" t="n">
-        <v>13946.57320677064</v>
+        <v>13946.57473932759</v>
       </c>
     </row>
     <row r="1065">
@@ -17857,7 +17857,7 @@
         <v>13000.06853092268</v>
       </c>
       <c r="D1065" s="3" t="n">
-        <v>13946.57320677064</v>
+        <v>13946.57473932759</v>
       </c>
     </row>
     <row r="1066">
@@ -17873,7 +17873,7 @@
         <v>13000.06853092268</v>
       </c>
       <c r="D1066" s="3" t="n">
-        <v>13946.57320677064</v>
+        <v>13946.57473932759</v>
       </c>
     </row>
     <row r="1067">
@@ -17921,7 +17921,7 @@
         <v>13096.16365142739</v>
       </c>
       <c r="D1069" s="3" t="n">
-        <v>13953.96387376693</v>
+        <v>13953.96234521285</v>
       </c>
     </row>
     <row r="1070">
@@ -17937,7 +17937,7 @@
         <v>13128.87650779729</v>
       </c>
       <c r="D1070" s="3" t="n">
-        <v>14085.01376480642</v>
+        <v>14085.01222798993</v>
       </c>
     </row>
     <row r="1071">
@@ -17953,7 +17953,7 @@
         <v>13175.90182378568</v>
       </c>
       <c r="D1071" s="3" t="n">
-        <v>14006.50455508511</v>
+        <v>14006.50608555525</v>
       </c>
     </row>
     <row r="1072">
@@ -17969,7 +17969,7 @@
         <v>13175.90182378568</v>
       </c>
       <c r="D1072" s="3" t="n">
-        <v>14006.50455508511</v>
+        <v>14006.50608555525</v>
       </c>
     </row>
     <row r="1073">
@@ -17985,7 +17985,7 @@
         <v>13175.90182378568</v>
       </c>
       <c r="D1073" s="3" t="n">
-        <v>14006.50455508511</v>
+        <v>14006.50608555525</v>
       </c>
     </row>
     <row r="1074">
@@ -18001,7 +18001,7 @@
         <v>13135.00997338109</v>
       </c>
       <c r="D1074" s="3" t="n">
-        <v>14071.90359727994</v>
+        <v>14071.90512875918</v>
       </c>
     </row>
     <row r="1075">
@@ -18017,7 +18017,7 @@
         <v>13160.90821463219</v>
       </c>
       <c r="D1075" s="3" t="n">
-        <v>13987.43236267338</v>
+        <v>13987.43389871999</v>
       </c>
     </row>
     <row r="1076">
@@ -18065,7 +18065,7 @@
         <v>13261.09231219277</v>
       </c>
       <c r="D1078" s="3" t="n">
-        <v>14223.71033089712</v>
+        <v>14223.71343111344</v>
       </c>
     </row>
     <row r="1079">
@@ -18081,7 +18081,7 @@
         <v>13261.09231219277</v>
       </c>
       <c r="D1079" s="3" t="n">
-        <v>14223.71033089712</v>
+        <v>14223.71343111344</v>
       </c>
     </row>
     <row r="1080">
@@ -18097,7 +18097,7 @@
         <v>13261.09231219277</v>
       </c>
       <c r="D1080" s="3" t="n">
-        <v>14223.71033089712</v>
+        <v>14223.71343111344</v>
       </c>
     </row>
     <row r="1081">
@@ -18113,7 +18113,7 @@
         <v>13301.98312267441</v>
       </c>
       <c r="D1081" s="3" t="n">
-        <v>14173.51760349503</v>
+        <v>14173.5160447654</v>
       </c>
     </row>
     <row r="1082">
@@ -18177,7 +18177,7 @@
         <v>13471.00180041861</v>
       </c>
       <c r="D1085" s="3" t="n">
-        <v>14521.39795373309</v>
+        <v>14521.39951826191</v>
       </c>
     </row>
     <row r="1086">
@@ -18193,7 +18193,7 @@
         <v>13471.00180041861</v>
       </c>
       <c r="D1086" s="3" t="n">
-        <v>14521.39795373309</v>
+        <v>14521.39951826191</v>
       </c>
     </row>
     <row r="1087">
@@ -18209,7 +18209,7 @@
         <v>13471.00180041861</v>
       </c>
       <c r="D1087" s="3" t="n">
-        <v>14521.39795373309</v>
+        <v>14521.39951826191</v>
       </c>
     </row>
     <row r="1088">
@@ -18273,7 +18273,7 @@
         <v>13662.50985197009</v>
       </c>
       <c r="D1091" s="3" t="n">
-        <v>14686.6771490351</v>
+        <v>14686.67872384467</v>
       </c>
     </row>
     <row r="1092">
@@ -18289,7 +18289,7 @@
         <v>13647.5162428166</v>
       </c>
       <c r="D1092" s="3" t="n">
-        <v>14788.0157083401</v>
+        <v>14788.01254914121</v>
       </c>
     </row>
     <row r="1093">
@@ -18305,7 +18305,7 @@
         <v>13647.5162428166</v>
       </c>
       <c r="D1093" s="3" t="n">
-        <v>14788.0157083401</v>
+        <v>14788.01254914121</v>
       </c>
     </row>
     <row r="1094">
@@ -18321,7 +18321,7 @@
         <v>13647.5162428166</v>
       </c>
       <c r="D1094" s="3" t="n">
-        <v>14788.0157083401</v>
+        <v>14788.01254914121</v>
       </c>
     </row>
     <row r="1095">
@@ -18369,7 +18369,7 @@
         <v>13561.64460487451</v>
       </c>
       <c r="D1097" s="3" t="n">
-        <v>14664.75975726583</v>
+        <v>14664.75817294506</v>
       </c>
     </row>
     <row r="1098">
@@ -18385,7 +18385,7 @@
         <v>13547.33214525602</v>
       </c>
       <c r="D1098" s="3" t="n">
-        <v>14719.32066803376</v>
+        <v>14719.32384160204</v>
       </c>
     </row>
     <row r="1099">
@@ -18449,7 +18449,7 @@
         <v>13584.13501860474</v>
       </c>
       <c r="D1102" s="3" t="n">
-        <v>14737.774556599</v>
+        <v>14737.7713877521</v>
       </c>
     </row>
     <row r="1103">
@@ -18465,7 +18465,7 @@
         <v>13599.12758783527</v>
       </c>
       <c r="D1103" s="3" t="n">
-        <v>14734.04834918864</v>
+        <v>14734.0499306527</v>
       </c>
     </row>
     <row r="1104">
@@ -18481,7 +18481,7 @@
         <v>13533.70187509548</v>
       </c>
       <c r="D1104" s="3" t="n">
-        <v>14684.23459993469</v>
+        <v>14684.23301903513</v>
       </c>
     </row>
     <row r="1105">
@@ -18497,7 +18497,7 @@
         <v>13296.53184654855</v>
       </c>
       <c r="D1105" s="3" t="n">
-        <v>14345.28224698128</v>
+        <v>14345.28067169268</v>
       </c>
     </row>
     <row r="1106">
@@ -18561,7 +18561,7 @@
         <v>13286.30836398593</v>
       </c>
       <c r="D1109" s="3" t="n">
-        <v>14354.50054555624</v>
+        <v>14354.50211862098</v>
       </c>
     </row>
     <row r="1110">
@@ -18577,7 +18577,7 @@
         <v>13356.50524323954</v>
       </c>
       <c r="D1110" s="3" t="n">
-        <v>14528.70637393799</v>
+        <v>14528.70480080478</v>
       </c>
     </row>
     <row r="1111">
@@ -18593,7 +18593,7 @@
         <v>13765.41958759359</v>
       </c>
       <c r="D1111" s="3" t="n">
-        <v>14807.71765101575</v>
+        <v>14807.71608657256</v>
       </c>
     </row>
     <row r="1112">
@@ -18673,7 +18673,7 @@
         <v>14106.86373067992</v>
       </c>
       <c r="D1116" s="3" t="n">
-        <v>15308.52214772308</v>
+        <v>15308.5205512226</v>
       </c>
     </row>
     <row r="1117">
@@ -18689,7 +18689,7 @@
         <v>14055.06724817772</v>
       </c>
       <c r="D1117" s="3" t="n">
-        <v>15333.24638487104</v>
+        <v>15333.24478080953</v>
       </c>
     </row>
     <row r="1118">
@@ -18705,7 +18705,7 @@
         <v>14105.50039168698</v>
       </c>
       <c r="D1118" s="3" t="n">
-        <v>15409.56904251391</v>
+        <v>15409.56743125067</v>
       </c>
     </row>
     <row r="1119">
@@ -18737,7 +18737,7 @@
         <v>13922.17029424724</v>
       </c>
       <c r="D1120" s="3" t="n">
-        <v>15238.73833822617</v>
+        <v>15238.73996274686</v>
       </c>
     </row>
     <row r="1121">
@@ -18753,7 +18753,7 @@
         <v>13922.17029424724</v>
       </c>
       <c r="D1121" s="3" t="n">
-        <v>15238.73833822617</v>
+        <v>15238.73996274686</v>
       </c>
     </row>
     <row r="1122">
@@ -18769,7 +18769,7 @@
         <v>13922.17029424724</v>
       </c>
       <c r="D1122" s="3" t="n">
-        <v>15238.73833822617</v>
+        <v>15238.73996274686</v>
       </c>
     </row>
     <row r="1123">
@@ -18785,7 +18785,7 @@
         <v>13958.29097813801</v>
       </c>
       <c r="D1123" s="3" t="n">
-        <v>15295.85899164873</v>
+        <v>15295.85736769263</v>
       </c>
     </row>
     <row r="1124">
@@ -18801,7 +18801,7 @@
         <v>13941.25288045659</v>
       </c>
       <c r="D1124" s="3" t="n">
-        <v>15263.15524227049</v>
+        <v>15263.15362768868</v>
       </c>
     </row>
     <row r="1125">
@@ -18817,7 +18817,7 @@
         <v>13952.15751255421</v>
       </c>
       <c r="D1125" s="3" t="n">
-        <v>15250.04758997536</v>
+        <v>15250.0492026242</v>
       </c>
     </row>
     <row r="1126">
@@ -18929,7 +18929,7 @@
         <v>14166.83712737091</v>
       </c>
       <c r="D1132" s="3" t="n">
-        <v>15636.76937759427</v>
+        <v>15636.77100813631</v>
       </c>
     </row>
     <row r="1133">
@@ -18945,7 +18945,7 @@
         <v>14234.98951809658</v>
       </c>
       <c r="D1133" s="3" t="n">
-        <v>15531.28626171833</v>
+        <v>15531.287881261</v>
       </c>
     </row>
     <row r="1134">
@@ -19041,7 +19041,7 @@
         <v>14442.17336825949</v>
       </c>
       <c r="D1139" s="3" t="n">
-        <v>15837.70892833968</v>
+        <v>15837.70730084249</v>
       </c>
     </row>
     <row r="1140">
@@ -19057,7 +19057,7 @@
         <v>14429.90539716894</v>
       </c>
       <c r="D1140" s="3" t="n">
-        <v>15806.65899662211</v>
+        <v>15806.66062360613</v>
       </c>
     </row>
     <row r="1141">
@@ -19073,7 +19073,7 @@
         <v>14433.31322468981</v>
       </c>
       <c r="D1141" s="3" t="n">
-        <v>15729.72565690222</v>
+        <v>15729.7272729039</v>
       </c>
     </row>
     <row r="1142">
@@ -19089,7 +19089,7 @@
         <v>14433.31322468981</v>
       </c>
       <c r="D1142" s="3" t="n">
-        <v>15729.72565690222</v>
+        <v>15729.7272729039</v>
       </c>
     </row>
     <row r="1143">
@@ -19105,7 +19105,7 @@
         <v>14433.31322468981</v>
       </c>
       <c r="D1143" s="3" t="n">
-        <v>15729.72565690222</v>
+        <v>15729.7272729039</v>
       </c>
     </row>
     <row r="1144">
@@ -19121,7 +19121,7 @@
         <v>14386.97009815937</v>
       </c>
       <c r="D1144" s="3" t="n">
-        <v>15678.53834702794</v>
+        <v>15678.53996610885</v>
       </c>
     </row>
     <row r="1145">
@@ -19185,7 +19185,7 @@
         <v>14398.55587979198</v>
       </c>
       <c r="D1148" s="3" t="n">
-        <v>15803.0737255272</v>
+        <v>15803.07535873786</v>
       </c>
     </row>
     <row r="1149">
@@ -19201,7 +19201,7 @@
         <v>14398.55587979198</v>
       </c>
       <c r="D1149" s="3" t="n">
-        <v>15803.0737255272</v>
+        <v>15803.07535873786</v>
       </c>
     </row>
     <row r="1150">
@@ -19217,7 +19217,7 @@
         <v>14398.55587979198</v>
       </c>
       <c r="D1150" s="3" t="n">
-        <v>15803.0737255272</v>
+        <v>15803.07535873786</v>
       </c>
     </row>
     <row r="1151">
@@ -19233,7 +19233,7 @@
         <v>14417.63846600133</v>
       </c>
       <c r="D1151" s="3" t="n">
-        <v>15816.19881735925</v>
+        <v>15816.19718974225</v>
       </c>
     </row>
     <row r="1152">
@@ -19249,7 +19249,7 @@
         <v>14378.79110412468</v>
       </c>
       <c r="D1152" s="3" t="n">
-        <v>15740.109463314</v>
+        <v>15740.1062103381</v>
       </c>
     </row>
     <row r="1153">
@@ -19281,7 +19281,7 @@
         <v>14178.42290900352</v>
       </c>
       <c r="D1154" s="3" t="n">
-        <v>15512.76802710257</v>
+        <v>15512.77133259489</v>
       </c>
     </row>
     <row r="1155">
@@ -19345,7 +19345,7 @@
         <v>14172.28944341972</v>
       </c>
       <c r="D1158" s="3" t="n">
-        <v>15667.7297184591</v>
+        <v>15667.72643920783</v>
       </c>
     </row>
     <row r="1159">
@@ -19361,7 +19361,7 @@
         <v>14292.91946618259</v>
       </c>
       <c r="D1159" s="3" t="n">
-        <v>15883.3615949888</v>
+        <v>15883.35995106942</v>
       </c>
     </row>
     <row r="1160">
@@ -19377,7 +19377,7 @@
         <v>14292.91946618259</v>
       </c>
       <c r="D1160" s="3" t="n">
-        <v>15888.31973276248</v>
+        <v>15888.31808832994</v>
       </c>
     </row>
     <row r="1161">
@@ -19409,7 +19409,7 @@
         <v>14242.48632267333</v>
       </c>
       <c r="D1162" s="3" t="n">
-        <v>15691.04167098214</v>
+        <v>15691.04002979988</v>
       </c>
     </row>
     <row r="1163">
@@ -19425,7 +19425,7 @@
         <v>14242.48632267333</v>
       </c>
       <c r="D1163" s="3" t="n">
-        <v>15691.04167098214</v>
+        <v>15691.04002979988</v>
       </c>
     </row>
     <row r="1164">
@@ -19441,7 +19441,7 @@
         <v>14242.48632267333</v>
       </c>
       <c r="D1164" s="3" t="n">
-        <v>15691.04167098214</v>
+        <v>15691.04002979988</v>
       </c>
     </row>
     <row r="1165">
@@ -19457,7 +19457,7 @@
         <v>14166.83712737091</v>
       </c>
       <c r="D1165" s="3" t="n">
-        <v>15502.76584905703</v>
+        <v>15502.76420884986</v>
       </c>
     </row>
     <row r="1166">
@@ -19473,7 +19473,7 @@
         <v>14197.50653513582</v>
       </c>
       <c r="D1166" s="3" t="n">
-        <v>15480.84051062552</v>
+        <v>15480.84379836144</v>
       </c>
     </row>
     <row r="1167">
@@ -19489,7 +19489,7 @@
         <v>14197.50653513582</v>
       </c>
       <c r="D1167" s="3" t="n">
-        <v>15480.84051062552</v>
+        <v>15480.84379836144</v>
       </c>
     </row>
     <row r="1168">
@@ -19505,7 +19505,7 @@
         <v>14352.89390279653</v>
       </c>
       <c r="D1168" s="3" t="n">
-        <v>15523.79620477174</v>
+        <v>15523.79785726115</v>
       </c>
     </row>
     <row r="1169">
@@ -19569,7 +19569,7 @@
         <v>14417.63846600133</v>
       </c>
       <c r="D1172" s="3" t="n">
-        <v>15879.79536727033</v>
+        <v>15879.79204737451</v>
       </c>
     </row>
     <row r="1173">
@@ -19585,7 +19585,7 @@
         <v>14318.81770743369</v>
       </c>
       <c r="D1173" s="3" t="n">
-        <v>15577.80873293955</v>
+        <v>15577.8037919442</v>
       </c>
     </row>
     <row r="1174">
@@ -19601,7 +19601,7 @@
         <v>14322.90668448956</v>
       </c>
       <c r="D1174" s="3" t="n">
-        <v>15662.13729551355</v>
+        <v>15662.13564201476</v>
       </c>
     </row>
     <row r="1175">
@@ -19617,7 +19617,7 @@
         <v>14332.44797759424</v>
       </c>
       <c r="D1175" s="3" t="n">
-        <v>15708.96478536197</v>
+        <v>15708.96312691947</v>
       </c>
     </row>
     <row r="1176">
@@ -19633,7 +19633,7 @@
         <v>14194.77985714994</v>
       </c>
       <c r="D1176" s="3" t="n">
-        <v>15494.81606159123</v>
+        <v>15494.81772278781</v>
       </c>
     </row>
     <row r="1177">
@@ -19649,7 +19649,7 @@
         <v>14194.77985714994</v>
       </c>
       <c r="D1177" s="3" t="n">
-        <v>15494.81606159123</v>
+        <v>15494.81772278781</v>
       </c>
     </row>
     <row r="1178">
@@ -19665,7 +19665,7 @@
         <v>14194.77985714994</v>
       </c>
       <c r="D1178" s="3" t="n">
-        <v>15494.81606159123</v>
+        <v>15494.81772278781</v>
       </c>
     </row>
     <row r="1179">
@@ -19681,7 +19681,7 @@
         <v>14171.60829388472</v>
       </c>
       <c r="D1179" s="3" t="n">
-        <v>15599.38644595257</v>
+        <v>15599.3847761342</v>
       </c>
     </row>
     <row r="1180">
@@ -19697,7 +19697,7 @@
         <v>14152.52570767537</v>
       </c>
       <c r="D1180" s="3" t="n">
-        <v>15589.16791733168</v>
+        <v>15589.16458446914</v>
       </c>
     </row>
     <row r="1181">
@@ -19713,7 +19713,7 @@
         <v>14374.70212706881</v>
       </c>
       <c r="D1181" s="3" t="n">
-        <v>15808.69668373766</v>
+        <v>15808.69336432106</v>
       </c>
     </row>
     <row r="1182">
@@ -19841,7 +19841,7 @@
         <v>14629.5924427551</v>
       </c>
       <c r="D1189" s="3" t="n">
-        <v>16099.86527594268</v>
+        <v>16099.86363270759</v>
       </c>
     </row>
     <row r="1190">
@@ -19857,7 +19857,7 @@
         <v>14565.52902908529</v>
       </c>
       <c r="D1190" s="3" t="n">
-        <v>16043.83940129051</v>
+        <v>16043.84104360183</v>
       </c>
     </row>
     <row r="1191">
@@ -19873,7 +19873,7 @@
         <v>14565.52902908529</v>
       </c>
       <c r="D1191" s="3" t="n">
-        <v>16043.83940129051</v>
+        <v>16043.84104360183</v>
       </c>
     </row>
     <row r="1192">
@@ -19889,7 +19889,7 @@
         <v>14565.52902908529</v>
       </c>
       <c r="D1192" s="3" t="n">
-        <v>16043.83940129051</v>
+        <v>16043.84104360183</v>
       </c>
     </row>
     <row r="1193">
@@ -19905,7 +19905,7 @@
         <v>14326.31451201043</v>
       </c>
       <c r="D1193" s="3" t="n">
-        <v>15738.96752587384</v>
+        <v>15738.9691600939</v>
       </c>
     </row>
     <row r="1194">
@@ -19937,7 +19937,7 @@
         <v>14560.07671303648</v>
       </c>
       <c r="D1195" s="3" t="n">
-        <v>15861.43300769896</v>
+        <v>15861.43464795751</v>
       </c>
     </row>
     <row r="1196">
@@ -20017,7 +20017,7 @@
         <v>14618.00666112249</v>
       </c>
       <c r="D1200" s="3" t="n">
-        <v>16033.62308635742</v>
+        <v>16033.61974781584</v>
       </c>
     </row>
     <row r="1201">
@@ -20033,7 +20033,7 @@
         <v>14612.55434507368</v>
       </c>
       <c r="D1201" s="3" t="n">
-        <v>16016.7878028486</v>
+        <v>16016.79111566218</v>
       </c>
     </row>
     <row r="1202">
@@ -20049,7 +20049,7 @@
         <v>14573.02583366204</v>
       </c>
       <c r="D1202" s="3" t="n">
-        <v>16011.31095479656</v>
+        <v>16011.31425310415</v>
       </c>
     </row>
     <row r="1203">
@@ -20065,7 +20065,7 @@
         <v>14737.95449442742</v>
       </c>
       <c r="D1203" s="3" t="n">
-        <v>16023.62917386408</v>
+        <v>16023.63081857028</v>
       </c>
     </row>
     <row r="1204">
@@ -20081,7 +20081,7 @@
         <v>14710.01176464838</v>
       </c>
       <c r="D1204" s="3" t="n">
-        <v>15900.07800881792</v>
+        <v>15900.07471461571</v>
       </c>
     </row>
     <row r="1205">
@@ -20097,7 +20097,7 @@
         <v>14710.01176464838</v>
       </c>
       <c r="D1205" s="3" t="n">
-        <v>15900.07800881792</v>
+        <v>15900.07471461571</v>
       </c>
     </row>
     <row r="1206">
@@ -20113,7 +20113,7 @@
         <v>14710.01176464838</v>
       </c>
       <c r="D1206" s="3" t="n">
-        <v>15900.07800881792</v>
+        <v>15900.07471461571</v>
       </c>
     </row>
     <row r="1207">
@@ -20129,7 +20129,7 @@
         <v>14791.11327599961</v>
       </c>
       <c r="D1207" s="3" t="n">
-        <v>16123.10409841467</v>
+        <v>16123.10575735337</v>
       </c>
     </row>
     <row r="1208">
@@ -20145,7 +20145,7 @@
         <v>14758.40041962971</v>
       </c>
       <c r="D1208" s="3" t="n">
-        <v>16151.17435672162</v>
+        <v>16151.17601728536</v>
       </c>
     </row>
     <row r="1209">
@@ -20161,7 +20161,7 @@
         <v>14660.94196013206</v>
       </c>
       <c r="D1209" s="3" t="n">
-        <v>16000.6317242188</v>
+        <v>16000.6300738162</v>
       </c>
     </row>
     <row r="1210">
@@ -20273,7 +20273,7 @@
         <v>14832.68627593919</v>
       </c>
       <c r="D1216" s="3" t="n">
-        <v>16124.69271000834</v>
+        <v>16124.69434723909</v>
       </c>
     </row>
     <row r="1217">
@@ -20369,7 +20369,7 @@
         <v>14312.00205239194</v>
       </c>
       <c r="D1222" s="3" t="n">
-        <v>15613.5691022811</v>
+        <v>15613.56746708597</v>
       </c>
     </row>
     <row r="1223">
@@ -20385,7 +20385,7 @@
         <v>14500.78446588049</v>
       </c>
       <c r="D1223" s="3" t="n">
-        <v>15528.29982775518</v>
+        <v>15528.30145319961</v>
       </c>
     </row>
     <row r="1224">
@@ -20401,7 +20401,7 @@
         <v>14526.68166720864</v>
       </c>
       <c r="D1224" s="3" t="n">
-        <v>15331.8971411775</v>
+        <v>15331.89551025908</v>
       </c>
     </row>
     <row r="1225">
@@ -20417,7 +20417,7 @@
         <v>14372.65763854088</v>
       </c>
       <c r="D1225" s="3" t="n">
-        <v>15711.45591513828</v>
+        <v>15711.45426952541</v>
       </c>
     </row>
     <row r="1226">
@@ -20433,7 +20433,7 @@
         <v>14372.65763854088</v>
       </c>
       <c r="D1226" s="3" t="n">
-        <v>15711.45591513828</v>
+        <v>15711.45426952541</v>
       </c>
     </row>
     <row r="1227">
@@ -20449,7 +20449,7 @@
         <v>14372.65763854088</v>
       </c>
       <c r="D1227" s="3" t="n">
-        <v>15711.45591513828</v>
+        <v>15711.45426952541</v>
       </c>
     </row>
     <row r="1228">
@@ -20481,7 +20481,7 @@
         <v>13931.71158735192</v>
       </c>
       <c r="D1229" s="3" t="n">
-        <v>15122.66163583089</v>
+        <v>15122.66000433078</v>
       </c>
     </row>
     <row r="1230">
@@ -20513,7 +20513,7 @@
         <v>13772.91639217034</v>
       </c>
       <c r="D1231" s="3" t="n">
-        <v>14582.84841112622</v>
+        <v>14582.85158045218</v>
       </c>
     </row>
     <row r="1232">
@@ -20529,7 +20529,7 @@
         <v>13517.34492694905</v>
       </c>
       <c r="D1232" s="3" t="n">
-        <v>14674.08131425143</v>
+        <v>14674.07972856213</v>
       </c>
     </row>
     <row r="1233">
@@ -20545,7 +20545,7 @@
         <v>13517.34492694905</v>
       </c>
       <c r="D1233" s="3" t="n">
-        <v>14674.08131425143</v>
+        <v>14674.07972856213</v>
       </c>
     </row>
     <row r="1234">
@@ -20561,7 +20561,7 @@
         <v>13517.34492694905</v>
       </c>
       <c r="D1234" s="3" t="n">
-        <v>14674.08131425143</v>
+        <v>14674.07972856213</v>
       </c>
     </row>
     <row r="1235">
@@ -20577,7 +20577,7 @@
         <v>13416.47967985348</v>
       </c>
       <c r="D1235" s="3" t="n">
-        <v>14187.69732459936</v>
+        <v>14187.69574951599</v>
       </c>
     </row>
     <row r="1236">
@@ -20609,7 +20609,7 @@
         <v>13275.40373188831</v>
       </c>
       <c r="D1237" s="3" t="n">
-        <v>14074.9825522702</v>
+        <v>14074.98098491888</v>
       </c>
     </row>
     <row r="1238">
@@ -20625,7 +20625,7 @@
         <v>13184.07977789742</v>
       </c>
       <c r="D1238" s="3" t="n">
-        <v>13922.97654400486</v>
+        <v>13922.97497263358</v>
       </c>
     </row>
     <row r="1239">
@@ -20641,7 +20641,7 @@
         <v>13332.65253043933</v>
       </c>
       <c r="D1239" s="3" t="n">
-        <v>14250.63022362531</v>
+        <v>14250.63179942717</v>
       </c>
     </row>
     <row r="1240">
@@ -20657,7 +20657,7 @@
         <v>13332.65253043933</v>
       </c>
       <c r="D1240" s="3" t="n">
-        <v>14250.63022362531</v>
+        <v>14250.63179942717</v>
       </c>
     </row>
     <row r="1241">
@@ -20673,7 +20673,7 @@
         <v>13332.65253043933</v>
       </c>
       <c r="D1241" s="3" t="n">
-        <v>14250.63022362531</v>
+        <v>14250.63179942717</v>
       </c>
     </row>
     <row r="1242">
@@ -20689,7 +20689,7 @@
         <v>13391.94477759532</v>
       </c>
       <c r="D1242" s="3" t="n">
-        <v>14326.69367754698</v>
+        <v>14326.69053336765</v>
       </c>
     </row>
     <row r="1243">
@@ -20705,7 +20705,7 @@
         <v>13339.46714555812</v>
       </c>
       <c r="D1243" s="3" t="n">
-        <v>14122.65115810922</v>
+        <v>14122.65272474203</v>
       </c>
     </row>
     <row r="1244">
@@ -20721,7 +20721,7 @@
         <v>13475.77192700947</v>
       </c>
       <c r="D1244" s="3" t="n">
-        <v>14249.96131551245</v>
+        <v>14249.95818806287</v>
       </c>
     </row>
     <row r="1245">
@@ -20737,7 +20737,7 @@
         <v>13519.38941547699</v>
       </c>
       <c r="D1245" s="3" t="n">
-        <v>14244.65787493852</v>
+        <v>14244.65944261483</v>
       </c>
     </row>
     <row r="1246">
@@ -20753,7 +20753,7 @@
         <v>13491.4477256209</v>
       </c>
       <c r="D1246" s="3" t="n">
-        <v>14321.8135086097</v>
+        <v>14321.81508425757</v>
       </c>
     </row>
     <row r="1247">
@@ -20769,7 +20769,7 @@
         <v>13491.4477256209</v>
       </c>
       <c r="D1247" s="3" t="n">
-        <v>14321.8135086097</v>
+        <v>14321.81508425757</v>
       </c>
     </row>
     <row r="1248">
@@ -20785,7 +20785,7 @@
         <v>13491.4477256209</v>
       </c>
       <c r="D1248" s="3" t="n">
-        <v>14321.8135086097</v>
+        <v>14321.81508425757</v>
       </c>
     </row>
     <row r="1249">
@@ -20801,7 +20801,7 @@
         <v>13723.84658765401</v>
       </c>
       <c r="D1249" s="3" t="n">
-        <v>14606.46871081958</v>
+        <v>14606.47028951242</v>
       </c>
     </row>
     <row r="1250">
@@ -20817,7 +20817,7 @@
         <v>13744.9736623913</v>
       </c>
       <c r="D1250" s="3" t="n">
-        <v>14685.21097224319</v>
+        <v>14685.20938884617</v>
       </c>
     </row>
     <row r="1251">
@@ -20833,7 +20833,7 @@
         <v>13678.18461065857</v>
       </c>
       <c r="D1251" s="3" t="n">
-        <v>14531.52616256088</v>
+        <v>14531.52457680325</v>
       </c>
     </row>
     <row r="1252">
@@ -20849,7 +20849,7 @@
         <v>13622.98134055844</v>
       </c>
       <c r="D1252" s="3" t="n">
-        <v>14554.22429762276</v>
+        <v>14554.22270515929</v>
       </c>
     </row>
     <row r="1253">
@@ -20865,7 +20865,7 @@
         <v>13334.01482950931</v>
       </c>
       <c r="D1253" s="3" t="n">
-        <v>14183.30420293267</v>
+        <v>14183.30261915922</v>
       </c>
     </row>
     <row r="1254">
@@ -20881,7 +20881,7 @@
         <v>13334.01482950931</v>
       </c>
       <c r="D1254" s="3" t="n">
-        <v>14183.30420293267</v>
+        <v>14183.30261915922</v>
       </c>
     </row>
     <row r="1255">
@@ -20897,7 +20897,7 @@
         <v>13334.01482950931</v>
       </c>
       <c r="D1255" s="3" t="n">
-        <v>14183.30420293267</v>
+        <v>14183.30261915922</v>
       </c>
     </row>
     <row r="1256">
@@ -20913,7 +20913,7 @@
         <v>13238.60189846255</v>
       </c>
       <c r="D1256" s="3" t="n">
-        <v>14248.28331603907</v>
+        <v>14248.28489645965</v>
       </c>
     </row>
     <row r="1257">
@@ -20961,7 +20961,7 @@
         <v>12747.22270376432</v>
       </c>
       <c r="D1259" s="3" t="n">
-        <v>13564.10353187628</v>
+        <v>13564.10510001445</v>
       </c>
     </row>
     <row r="1260">
@@ -20977,7 +20977,7 @@
         <v>12146.80030785879</v>
       </c>
       <c r="D1260" s="3" t="n">
-        <v>12613.8620565252</v>
+        <v>12613.8605075632</v>
       </c>
     </row>
     <row r="1261">
@@ -21009,7 +21009,7 @@
         <v>12090.91588822367</v>
       </c>
       <c r="D1262" s="3" t="n">
-        <v>13205.29418349236</v>
+        <v>13205.29574542097</v>
       </c>
     </row>
     <row r="1263">
@@ -21025,7 +21025,7 @@
         <v>11968.24137693287</v>
       </c>
       <c r="D1263" s="3" t="n">
-        <v>13075.84405513338</v>
+        <v>13075.84709414316</v>
       </c>
     </row>
     <row r="1264">
@@ -21041,7 +21041,7 @@
         <v>11968.24137693287</v>
       </c>
       <c r="D1264" s="3" t="n">
-        <v>13075.84405513338</v>
+        <v>13075.84709414316</v>
       </c>
     </row>
     <row r="1265">
@@ -21057,7 +21057,7 @@
         <v>11968.24137693287</v>
       </c>
       <c r="D1265" s="3" t="n">
-        <v>13075.84405513338</v>
+        <v>13075.84709414316</v>
       </c>
     </row>
     <row r="1266">
@@ -21073,7 +21073,7 @@
         <v>12313.77345715211</v>
       </c>
       <c r="D1266" s="3" t="n">
-        <v>13103.41170999978</v>
+        <v>13103.41020192202</v>
       </c>
     </row>
     <row r="1267">
@@ -21089,7 +21089,7 @@
         <v>12435.08566937293</v>
       </c>
       <c r="D1267" s="3" t="n">
-        <v>13070.7109281811</v>
+        <v>13070.71243672085</v>
       </c>
     </row>
     <row r="1268">
@@ -21105,7 +21105,7 @@
         <v>12284.46842830308</v>
       </c>
       <c r="D1268" s="3" t="n">
-        <v>12833.36304932174</v>
+        <v>12833.36153450401</v>
       </c>
     </row>
     <row r="1269">
@@ -21185,7 +21185,7 @@
         <v>12167.92738259608</v>
       </c>
       <c r="D1273" s="3" t="n">
-        <v>12431.15419803536</v>
+        <v>12431.15269705668</v>
       </c>
     </row>
     <row r="1274">
@@ -21201,7 +21201,7 @@
         <v>12067.0621355005</v>
       </c>
       <c r="D1274" s="3" t="n">
-        <v>12626.08224112025</v>
+        <v>12626.08521283366</v>
       </c>
     </row>
     <row r="1275">
@@ -21217,7 +21217,7 @@
         <v>12438.49245697085</v>
       </c>
       <c r="D1275" s="3" t="n">
-        <v>13004.18176935586</v>
+        <v>13004.18327635603</v>
       </c>
     </row>
     <row r="1276">
@@ -21249,7 +21249,7 @@
         <v>12595.92535308244</v>
       </c>
       <c r="D1277" s="3" t="n">
-        <v>13349.55267022775</v>
+        <v>13349.55417449083</v>
       </c>
     </row>
     <row r="1278">
@@ -21265,7 +21265,7 @@
         <v>12595.92535308244</v>
       </c>
       <c r="D1278" s="3" t="n">
-        <v>13349.55267022775</v>
+        <v>13349.55417449083</v>
       </c>
     </row>
     <row r="1279">
@@ -21281,7 +21281,7 @@
         <v>12595.92535308244</v>
       </c>
       <c r="D1279" s="3" t="n">
-        <v>13349.55267022775</v>
+        <v>13349.55417449083</v>
       </c>
     </row>
     <row r="1280">
@@ -21313,7 +21313,7 @@
         <v>12674.98133598278</v>
       </c>
       <c r="D1281" s="3" t="n">
-        <v>13394.91017120068</v>
+        <v>13394.90867184708</v>
       </c>
     </row>
     <row r="1282">
@@ -21329,7 +21329,7 @@
         <v>12721.32550243618</v>
       </c>
       <c r="D1282" s="3" t="n">
-        <v>13423.61614988334</v>
+        <v>13423.61765185414</v>
       </c>
     </row>
     <row r="1283">
@@ -21345,7 +21345,7 @@
         <v>12721.32550243618</v>
       </c>
       <c r="D1283" s="3" t="n">
-        <v>13595.57988817319</v>
+        <v>13595.58139868023</v>
       </c>
     </row>
     <row r="1284">
@@ -21361,7 +21361,7 @@
         <v>13032.78138729258</v>
       </c>
       <c r="D1284" s="3" t="n">
-        <v>13832.0851290079</v>
+        <v>13832.08361470331</v>
       </c>
     </row>
     <row r="1285">
@@ -21377,7 +21377,7 @@
         <v>13032.78138729258</v>
       </c>
       <c r="D1285" s="3" t="n">
-        <v>13832.0851290079</v>
+        <v>13832.08361470331</v>
       </c>
     </row>
     <row r="1286">
@@ -21393,7 +21393,7 @@
         <v>13032.78138729258</v>
       </c>
       <c r="D1286" s="3" t="n">
-        <v>13832.0851290079</v>
+        <v>13832.08361470331</v>
       </c>
     </row>
     <row r="1287">
@@ -21425,7 +21425,7 @@
         <v>12988.48274929007</v>
       </c>
       <c r="D1288" s="3" t="n">
-        <v>13617.47676892468</v>
+        <v>13617.47828097113</v>
       </c>
     </row>
     <row r="1289">
@@ -21457,7 +21457,7 @@
         <v>13133.64767431111</v>
       </c>
       <c r="D1290" s="3" t="n">
-        <v>13778.75294108255</v>
+        <v>13778.75445408699</v>
       </c>
     </row>
     <row r="1291">
@@ -21521,7 +21521,7 @@
         <v>13555.51009936776</v>
       </c>
       <c r="D1294" s="3" t="n">
-        <v>14312.89138862116</v>
+        <v>14312.88986530158</v>
       </c>
     </row>
     <row r="1295">
@@ -21537,7 +21537,7 @@
         <v>13645.47175428867</v>
       </c>
       <c r="D1295" s="3" t="n">
-        <v>14581.4977253416</v>
+        <v>14581.49618361563</v>
       </c>
     </row>
     <row r="1296">
@@ -21553,7 +21553,7 @@
         <v>13607.30658186996</v>
       </c>
       <c r="D1296" s="3" t="n">
-        <v>14482.68576699887</v>
+        <v>14482.6842376749</v>
       </c>
     </row>
     <row r="1297">
@@ -21585,7 +21585,7 @@
         <v>13759.28612200979</v>
       </c>
       <c r="D1298" s="3" t="n">
-        <v>14636.26888542088</v>
+        <v>14636.26735707209</v>
       </c>
     </row>
     <row r="1299">
@@ -21601,7 +21601,7 @@
         <v>13759.28612200979</v>
       </c>
       <c r="D1299" s="3" t="n">
-        <v>14636.26888542088</v>
+        <v>14636.26735707209</v>
       </c>
     </row>
     <row r="1300">
@@ -21617,7 +21617,7 @@
         <v>13759.28612200979</v>
       </c>
       <c r="D1300" s="3" t="n">
-        <v>14636.26888542088</v>
+        <v>14636.26735707209</v>
       </c>
     </row>
     <row r="1301">
@@ -21633,7 +21633,7 @@
         <v>13678.86680011651</v>
       </c>
       <c r="D1301" s="3" t="n">
-        <v>14659.00122915197</v>
+        <v>14659.00275820218</v>
       </c>
     </row>
     <row r="1302">
@@ -21665,7 +21665,7 @@
         <v>13607.98773140496</v>
       </c>
       <c r="D1303" s="3" t="n">
-        <v>14235.7775811484</v>
+        <v>14235.77909659915</v>
       </c>
     </row>
     <row r="1304">
@@ -21697,7 +21697,7 @@
         <v>13357.18743269749</v>
       </c>
       <c r="D1305" s="3" t="n">
-        <v>14151.85080020764</v>
+        <v>14151.85231647937</v>
       </c>
     </row>
     <row r="1306">
@@ -21713,7 +21713,7 @@
         <v>13357.18743269749</v>
       </c>
       <c r="D1306" s="3" t="n">
-        <v>14151.85080020764</v>
+        <v>14151.85231647937</v>
       </c>
     </row>
     <row r="1307">
@@ -21729,7 +21729,7 @@
         <v>13357.18743269749</v>
       </c>
       <c r="D1307" s="3" t="n">
-        <v>14151.85080020764</v>
+        <v>14151.85231647937</v>
       </c>
     </row>
     <row r="1308">
@@ -21745,7 +21745,7 @@
         <v>13479.17975453035</v>
       </c>
       <c r="D1308" s="3" t="n">
-        <v>14038.65327233834</v>
+        <v>14038.65477648176</v>
       </c>
     </row>
     <row r="1309">
@@ -21761,7 +21761,7 @@
         <v>13580.04500162592</v>
       </c>
       <c r="D1309" s="3" t="n">
-        <v>14310.80660282375</v>
+        <v>14310.80510075029</v>
       </c>
     </row>
     <row r="1310">
@@ -21777,7 +21777,7 @@
         <v>13597.76528876529</v>
       </c>
       <c r="D1310" s="3" t="n">
-        <v>14292.50349352607</v>
+        <v>14292.49896688087</v>
       </c>
     </row>
     <row r="1311">
@@ -21809,7 +21809,7 @@
         <v>13531.65738656754</v>
       </c>
       <c r="D1312" s="3" t="n">
-        <v>14280.87365923519</v>
+        <v>14280.87215582739</v>
       </c>
     </row>
     <row r="1313">
@@ -21825,7 +21825,7 @@
         <v>13531.65738656754</v>
       </c>
       <c r="D1313" s="3" t="n">
-        <v>14280.87365923519</v>
+        <v>14280.87215582739</v>
       </c>
     </row>
     <row r="1314">
@@ -21841,7 +21841,7 @@
         <v>13531.65738656754</v>
       </c>
       <c r="D1314" s="3" t="n">
-        <v>14280.87365923519</v>
+        <v>14280.87215582739</v>
       </c>
     </row>
     <row r="1315">
@@ -21857,7 +21857,7 @@
         <v>13466.91282336274</v>
       </c>
       <c r="D1315" s="3" t="n">
-        <v>14393.01925429541</v>
+        <v>14393.01774756899</v>
       </c>
     </row>
     <row r="1316">
@@ -21905,7 +21905,7 @@
         <v>13650.24188087953</v>
       </c>
       <c r="D1318" s="3" t="n">
-        <v>14314.61750847117</v>
+        <v>14314.61601081104</v>
       </c>
     </row>
     <row r="1319">
@@ -21985,7 +21985,7 @@
         <v>13700.67502438879</v>
       </c>
       <c r="D1323" s="3" t="n">
-        <v>14549.06581958718</v>
+        <v>14549.0673164604</v>
       </c>
     </row>
     <row r="1324">
@@ -22017,7 +22017,7 @@
         <v>13572.54819704918</v>
       </c>
       <c r="D1325" s="3" t="n">
-        <v>14462.36289393526</v>
+        <v>14462.36140763378</v>
       </c>
     </row>
     <row r="1326">
@@ -22033,7 +22033,7 @@
         <v>13527.56840951168</v>
       </c>
       <c r="D1326" s="3" t="n">
-        <v>14188.58625060916</v>
+        <v>14188.58330130499</v>
       </c>
     </row>
     <row r="1327">
@@ -22049,7 +22049,7 @@
         <v>13527.56840951168</v>
       </c>
       <c r="D1327" s="3" t="n">
-        <v>14188.58625060916</v>
+        <v>14188.58330130499</v>
       </c>
     </row>
     <row r="1328">
@@ -22065,7 +22065,7 @@
         <v>13527.56840951168</v>
       </c>
       <c r="D1328" s="3" t="n">
-        <v>14188.58625060916</v>
+        <v>14188.58330130499</v>
       </c>
     </row>
     <row r="1329">
@@ -22081,7 +22081,7 @@
         <v>13575.95602457005</v>
       </c>
       <c r="D1329" s="3" t="n">
-        <v>14377.57862846982</v>
+        <v>14377.58158889316</v>
       </c>
     </row>
     <row r="1330">
@@ -22113,7 +22113,7 @@
         <v>13539.83534067928</v>
       </c>
       <c r="D1331" s="3" t="n">
-        <v>14344.48230542038</v>
+        <v>14344.48081566343</v>
       </c>
     </row>
     <row r="1332">
@@ -22129,7 +22129,7 @@
         <v>13432.8366279999</v>
       </c>
       <c r="D1332" s="3" t="n">
-        <v>14350.90661575916</v>
+        <v>14350.90512533502</v>
       </c>
     </row>
     <row r="1333">
@@ -22241,7 +22241,7 @@
         <v>13565.73358193038</v>
       </c>
       <c r="D1339" s="3" t="n">
-        <v>14480.76056912209</v>
+        <v>14480.76349735119</v>
       </c>
     </row>
     <row r="1340">
@@ -22305,7 +22305,7 @@
         <v>13650.24188087953</v>
       </c>
       <c r="D1343" s="3" t="n">
-        <v>14567.78769281616</v>
+        <v>14567.78915147383</v>
       </c>
     </row>
     <row r="1344">
@@ -22337,7 +22337,7 @@
         <v>13657.73868545627</v>
       </c>
       <c r="D1345" s="3" t="n">
-        <v>14532.33205071165</v>
+        <v>14532.33060170201</v>
       </c>
     </row>
     <row r="1346">
@@ -22417,7 +22417,7 @@
         <v>13747.01919084219</v>
       </c>
       <c r="D1350" s="3" t="n">
-        <v>14568.26619708029</v>
+        <v>14568.26764913488</v>
       </c>
     </row>
     <row r="1351">
@@ -22433,7 +22433,7 @@
         <v>13744.9736623913</v>
       </c>
       <c r="D1351" s="3" t="n">
-        <v>14615.1781406443</v>
+        <v>14615.17668311574</v>
       </c>
     </row>
     <row r="1352">
@@ -22449,7 +22449,7 @@
         <v>13800.17797241438</v>
       </c>
       <c r="D1352" s="3" t="n">
-        <v>14717.83267559982</v>
+        <v>14717.83121658295</v>
       </c>
     </row>
     <row r="1353">
@@ -22529,7 +22529,7 @@
         <v>13828.11966227046</v>
       </c>
       <c r="D1357" s="3" t="n">
-        <v>14789.07828808488</v>
+        <v>14789.07682376505</v>
       </c>
     </row>
     <row r="1358">
@@ -22577,7 +22577,7 @@
         <v>13976.01126527738</v>
       </c>
       <c r="D1360" s="3" t="n">
-        <v>14924.74870002308</v>
+        <v>14924.74722986998</v>
       </c>
     </row>
     <row r="1361">
@@ -22673,7 +22673,7 @@
         <v>13969.19561023563</v>
       </c>
       <c r="D1366" s="3" t="n">
-        <v>14938.62106754343</v>
+        <v>14938.62252474696</v>
       </c>
     </row>
     <row r="1367">
@@ -22705,7 +22705,7 @@
         <v>14029.85119638456</v>
       </c>
       <c r="D1368" s="3" t="n">
-        <v>14985.02378473369</v>
+        <v>14985.02232963431</v>
       </c>
     </row>
     <row r="1369">
@@ -22721,7 +22721,7 @@
         <v>14029.85119638456</v>
       </c>
       <c r="D1369" s="3" t="n">
-        <v>14985.02378473369</v>
+        <v>14985.02232963431</v>
       </c>
     </row>
     <row r="1370">
@@ -22737,7 +22737,7 @@
         <v>14029.85119638456</v>
       </c>
       <c r="D1370" s="3" t="n">
-        <v>14985.02378473369</v>
+        <v>14985.02232963431</v>
       </c>
     </row>
     <row r="1371">
@@ -22753,7 +22753,7 @@
         <v>14149.1178801545</v>
       </c>
       <c r="D1371" s="3" t="n">
-        <v>14980.38282996263</v>
+        <v>14980.38137494868</v>
       </c>
     </row>
     <row r="1372">
@@ -22769,7 +22769,7 @@
         <v>14207.72897777549</v>
       </c>
       <c r="D1372" s="3" t="n">
-        <v>15147.09242360897</v>
+        <v>15147.09094851213</v>
       </c>
     </row>
     <row r="1373">
@@ -22865,7 +22865,7 @@
         <v>14045.52595507304</v>
       </c>
       <c r="D1378" s="3" t="n">
-        <v>15062.657729485</v>
+        <v>15062.65625310529</v>
       </c>
     </row>
     <row r="1379">
@@ -22897,7 +22897,7 @@
         <v>14042.11812755217</v>
       </c>
       <c r="D1380" s="3" t="n">
-        <v>15110.87965520993</v>
+        <v>15110.87817787218</v>
       </c>
     </row>
     <row r="1381">
@@ -22929,7 +22929,7 @@
         <v>14112.31604672873</v>
       </c>
       <c r="D1382" s="3" t="n">
-        <v>15088.91935278942</v>
+        <v>15088.9208177935</v>
       </c>
     </row>
     <row r="1383">
@@ -22945,7 +22945,7 @@
         <v>14112.31604672873</v>
       </c>
       <c r="D1383" s="3" t="n">
-        <v>15088.91935278942</v>
+        <v>15088.9208177935</v>
       </c>
     </row>
     <row r="1384">
@@ -22961,7 +22961,7 @@
         <v>14112.31604672873</v>
       </c>
       <c r="D1384" s="3" t="n">
-        <v>15088.91935278942</v>
+        <v>15088.9208177935</v>
       </c>
     </row>
     <row r="1385">
@@ -22993,7 +22993,7 @@
         <v>14200.91332273375</v>
       </c>
       <c r="D1386" s="3" t="n">
-        <v>15295.63855862208</v>
+        <v>15295.64003096481</v>
       </c>
     </row>
     <row r="1387">
@@ -23025,7 +23025,7 @@
         <v>14292.91946618259</v>
       </c>
       <c r="D1388" s="3" t="n">
-        <v>15225.66048184468</v>
+        <v>15225.66194231559</v>
       </c>
     </row>
     <row r="1389">
@@ -23201,7 +23201,7 @@
         <v>14312.68320192693</v>
       </c>
       <c r="D1399" s="3" t="n">
-        <v>15171.37780037929</v>
+        <v>15171.37633949786</v>
       </c>
     </row>
     <row r="1400">
@@ -23265,7 +23265,7 @@
         <v>14256.11659283387</v>
       </c>
       <c r="D1403" s="3" t="n">
-        <v>15268.8675618614</v>
+        <v>15268.86609747313</v>
       </c>
     </row>
     <row r="1404">
@@ -23281,7 +23281,7 @@
         <v>14256.11659283387</v>
       </c>
       <c r="D1404" s="3" t="n">
-        <v>15268.8675618614</v>
+        <v>15268.86609747313</v>
       </c>
     </row>
     <row r="1405">
@@ -23297,7 +23297,7 @@
         <v>14256.11659283387</v>
       </c>
       <c r="D1405" s="3" t="n">
-        <v>15268.8675618614</v>
+        <v>15268.86609747313</v>
       </c>
     </row>
     <row r="1406">
@@ -23313,7 +23313,7 @@
         <v>14288.83048912672</v>
       </c>
       <c r="D1406" s="3" t="n">
-        <v>15255.48989995254</v>
+        <v>15255.48843684727</v>
       </c>
     </row>
     <row r="1407">
@@ -23329,7 +23329,7 @@
         <v>14133.44312146602</v>
       </c>
       <c r="D1407" s="3" t="n">
-        <v>15111.28310556381</v>
+        <v>15111.2816454693</v>
       </c>
     </row>
     <row r="1408">
@@ -23345,7 +23345,7 @@
         <v>14226.81156398485</v>
       </c>
       <c r="D1408" s="3" t="n">
-        <v>15297.4868215116</v>
+        <v>15297.48829163035</v>
       </c>
     </row>
     <row r="1409">
@@ -23361,7 +23361,7 @@
         <v>14348.80388581771</v>
       </c>
       <c r="D1409" s="3" t="n">
-        <v>15393.0278649455</v>
+        <v>15393.02639790586</v>
       </c>
     </row>
     <row r="1410">
@@ -23425,7 +23425,7 @@
         <v>14339.26259271303</v>
       </c>
       <c r="D1413" s="3" t="n">
-        <v>15316.89965243755</v>
+        <v>15316.89673156439</v>
       </c>
     </row>
     <row r="1414">
@@ -23537,7 +23537,7 @@
         <v>14534.86066124333</v>
       </c>
       <c r="D1420" s="3" t="n">
-        <v>15584.34434515583</v>
+        <v>15584.34288637849</v>
       </c>
     </row>
     <row r="1421">
@@ -23585,7 +23585,7 @@
         <v>14558.71337404354</v>
       </c>
       <c r="D1423" s="3" t="n">
-        <v>15484.32763077482</v>
+        <v>15484.33052369659</v>
       </c>
     </row>
     <row r="1424">
@@ -23675,13 +23675,13 @@
         </is>
       </c>
       <c r="B1429" s="3" t="n">
-        <v>10373.01</v>
+        <v>10373.02</v>
       </c>
       <c r="C1429" s="3" t="n">
         <v>14599.60522444813</v>
       </c>
       <c r="D1429" s="3" t="n">
-        <v>15515.63964306883</v>
+        <v>15515.64109098367</v>
       </c>
     </row>
     <row r="1430">
@@ -23777,7 +23777,7 @@
         <v>14614.59883360162</v>
       </c>
       <c r="D1435" s="3" t="n">
-        <v>15745.51149373194</v>
+        <v>15745.5129518935</v>
       </c>
     </row>
     <row r="1436">
@@ -23793,7 +23793,7 @@
         <v>14723.64203480893</v>
       </c>
       <c r="D1436" s="3" t="n">
-        <v>15793.23600314831</v>
+        <v>15793.23454553417</v>
       </c>
     </row>
     <row r="1437">
@@ -23985,7 +23985,7 @@
         <v>14823.8261323695</v>
       </c>
       <c r="D1448" s="3" t="n">
-        <v>15845.58149937602</v>
+        <v>15845.58297375432</v>
       </c>
     </row>
     <row r="1449">
@@ -24033,7 +24033,7 @@
         <v>14823.14498283451</v>
       </c>
       <c r="D1451" s="3" t="n">
-        <v>15728.69601126427</v>
+        <v>15728.69307362672</v>
       </c>
     </row>
     <row r="1452">
@@ -24113,7 +24113,7 @@
         <v>14986.02915507196</v>
       </c>
       <c r="D1456" s="3" t="n">
-        <v>15984.85728009529</v>
+        <v>15984.8587491536</v>
       </c>
     </row>
     <row r="1457">
@@ -24209,7 +24209,7 @@
         <v>15178.90054561638</v>
       </c>
       <c r="D1462" s="3" t="n">
-        <v>16334.896265044</v>
+        <v>16334.89773571028</v>
       </c>
     </row>
     <row r="1463">
@@ -24241,7 +24241,7 @@
         <v>15232.05932718857</v>
       </c>
       <c r="D1464" s="3" t="n">
-        <v>16349.364531149</v>
+        <v>16349.36599851372</v>
       </c>
     </row>
     <row r="1465">
@@ -24257,7 +24257,7 @@
         <v>15254.5497409188</v>
       </c>
       <c r="D1465" s="3" t="n">
-        <v>16245.51620505723</v>
+        <v>16245.51767931572</v>
       </c>
     </row>
     <row r="1466">
@@ -24273,7 +24273,7 @@
         <v>15236.83049370238</v>
       </c>
       <c r="D1466" s="3" t="n">
-        <v>16342.3046814251</v>
+        <v>16342.3032032321</v>
       </c>
     </row>
     <row r="1467">
@@ -24289,7 +24289,7 @@
         <v>15236.83049370238</v>
       </c>
       <c r="D1467" s="3" t="n">
-        <v>16342.3046814251</v>
+        <v>16342.3032032321</v>
       </c>
     </row>
     <row r="1468">
@@ -24305,7 +24305,7 @@
         <v>15236.83049370238</v>
       </c>
       <c r="D1468" s="3" t="n">
-        <v>16342.3046814251</v>
+        <v>16342.3032032321</v>
       </c>
     </row>
     <row r="1469">
@@ -24433,7 +24433,7 @@
         <v>15120.97059753037</v>
       </c>
       <c r="D1476" s="3" t="n">
-        <v>16367.88575580007</v>
+        <v>16367.88427394627</v>
       </c>
     </row>
     <row r="1477">
@@ -24449,7 +24449,7 @@
         <v>15176.1738676305</v>
       </c>
       <c r="D1477" s="3" t="n">
-        <v>16386.41721505766</v>
+        <v>16386.41573491455</v>
       </c>
     </row>
     <row r="1478">
@@ -24465,7 +24465,7 @@
         <v>15260.6832065026</v>
       </c>
       <c r="D1478" s="3" t="n">
-        <v>16352.7089448352</v>
+        <v>16352.71042111224</v>
       </c>
     </row>
     <row r="1479">
@@ -24481,7 +24481,7 @@
         <v>15063.72283890231</v>
       </c>
       <c r="D1479" s="3" t="n">
-        <v>16074.83081231741</v>
+        <v>16074.83228799585</v>
       </c>
     </row>
     <row r="1480">
@@ -24497,7 +24497,7 @@
         <v>15020.78649996979</v>
       </c>
       <c r="D1480" s="3" t="n">
-        <v>16017.23914803313</v>
+        <v>16017.23767740106</v>
       </c>
     </row>
     <row r="1481">
@@ -24513,7 +24513,7 @@
         <v>15020.78649996979</v>
       </c>
       <c r="D1481" s="3" t="n">
-        <v>16017.23914803313</v>
+        <v>16017.23767740106</v>
       </c>
     </row>
     <row r="1482">
@@ -24529,7 +24529,7 @@
         <v>15020.78649996979</v>
       </c>
       <c r="D1482" s="3" t="n">
-        <v>16017.23914803313</v>
+        <v>16017.23767740106</v>
       </c>
     </row>
     <row r="1483">
@@ -24545,7 +24545,7 @@
         <v>14959.44976428586</v>
       </c>
       <c r="D1483" s="3" t="n">
-        <v>15890.71917173708</v>
+        <v>15890.71769900087</v>
       </c>
     </row>
     <row r="1484">
@@ -24561,7 +24561,7 @@
         <v>14759.76375862265</v>
       </c>
       <c r="D1484" s="3" t="n">
-        <v>15790.9528962279</v>
+        <v>15790.95142034412</v>
       </c>
     </row>
     <row r="1485">
@@ -24577,7 +24577,7 @@
         <v>14799.97341956929</v>
       </c>
       <c r="D1485" s="3" t="n">
-        <v>15864.81813444945</v>
+        <v>15864.81665736824</v>
       </c>
     </row>
     <row r="1486">
@@ -24769,7 +24769,7 @@
         <v>15125.74176404419</v>
       </c>
       <c r="D1497" s="3" t="n">
-        <v>16258.67461068643</v>
+        <v>16258.6731361883</v>
       </c>
     </row>
     <row r="1498">
@@ -24817,7 +24817,7 @@
         <v>15167.99591351876</v>
       </c>
       <c r="D1500" s="3" t="n">
-        <v>16265.48669679106</v>
+        <v>16265.48523055532</v>
       </c>
     </row>
     <row r="1501">
@@ -24833,7 +24833,7 @@
         <v>15224.56252261182</v>
       </c>
       <c r="D1501" s="3" t="n">
-        <v>16330.03342663562</v>
+        <v>16330.0348958991</v>
       </c>
     </row>
     <row r="1502">
@@ -24849,7 +24849,7 @@
         <v>15224.56252261182</v>
       </c>
       <c r="D1502" s="3" t="n">
-        <v>16330.03342663562</v>
+        <v>16330.0348958991</v>
       </c>
     </row>
     <row r="1503">
@@ -24865,7 +24865,7 @@
         <v>15224.56252261182</v>
       </c>
       <c r="D1503" s="3" t="n">
-        <v>16330.03342663562</v>
+        <v>16330.0348958991</v>
       </c>
     </row>
     <row r="1504">
@@ -25041,7 +25041,7 @@
         <v>15051.45590773471</v>
       </c>
       <c r="D1514" s="3" t="n">
-        <v>15973.90306499083</v>
+        <v>15973.90452180099</v>
       </c>
     </row>
     <row r="1515">
@@ -25105,7 +25105,7 @@
         <v>15152.32115483028</v>
       </c>
       <c r="D1518" s="3" t="n">
-        <v>16266.52020526201</v>
+        <v>16266.5216663316</v>
       </c>
     </row>
     <row r="1519">
@@ -25233,7 +25233,7 @@
         <v>15238.87498223032</v>
       </c>
       <c r="D1526" s="3" t="n">
-        <v>16228.50348212209</v>
+        <v>16228.50493515165</v>
       </c>
     </row>
     <row r="1527">
@@ -25281,7 +25281,7 @@
         <v>15175.4927180955</v>
       </c>
       <c r="D1529" s="3" t="n">
-        <v>16168.57438496863</v>
+        <v>16168.57584076951</v>
       </c>
     </row>
     <row r="1530">
@@ -25297,7 +25297,7 @@
         <v>15175.4927180955</v>
       </c>
       <c r="D1530" s="3" t="n">
-        <v>16168.57438496863</v>
+        <v>16168.57584076951</v>
       </c>
     </row>
     <row r="1531">
@@ -25313,7 +25313,7 @@
         <v>15175.4927180955</v>
       </c>
       <c r="D1531" s="3" t="n">
-        <v>16168.57438496863</v>
+        <v>16168.57584076951</v>
       </c>
     </row>
     <row r="1532">
@@ -25345,7 +25345,7 @@
         <v>15418.79725214918</v>
       </c>
       <c r="D1533" s="3" t="n">
-        <v>16422.69535055001</v>
+        <v>16422.69389033575</v>
       </c>
     </row>
     <row r="1534">
@@ -25441,7 +25441,7 @@
         <v>15559.87216019139</v>
       </c>
       <c r="D1539" s="3" t="n">
-        <v>16631.74607751873</v>
+        <v>16631.74460584311</v>
       </c>
     </row>
     <row r="1540">
@@ -25473,7 +25473,7 @@
         <v>15493.08310845866</v>
       </c>
       <c r="D1541" s="3" t="n">
-        <v>16490.21695028113</v>
+        <v>16490.21841957891</v>
       </c>
     </row>
     <row r="1542">
@@ -25585,7 +25585,7 @@
         <v>15305.66403396305</v>
       </c>
       <c r="D1548" s="3" t="n">
-        <v>16252.61332358635</v>
+        <v>16252.61186497998</v>
       </c>
     </row>
     <row r="1549">
@@ -25601,7 +25601,7 @@
         <v>15403.12145353775</v>
       </c>
       <c r="D1549" s="3" t="n">
-        <v>16414.33509129572</v>
+        <v>16414.33655676165</v>
       </c>
     </row>
     <row r="1550">
@@ -25617,7 +25617,7 @@
         <v>15372.45308569579</v>
       </c>
       <c r="D1550" s="3" t="n">
-        <v>16306.24669892991</v>
+        <v>16306.24524364223</v>
       </c>
     </row>
     <row r="1551">
@@ -25633,7 +25633,7 @@
         <v>15372.45308569579</v>
       </c>
       <c r="D1551" s="3" t="n">
-        <v>16306.24669892991</v>
+        <v>16306.24524364223</v>
       </c>
     </row>
     <row r="1552">
@@ -25649,7 +25649,7 @@
         <v>15372.45308569579</v>
       </c>
       <c r="D1552" s="3" t="n">
-        <v>16306.24669892991</v>
+        <v>16306.24524364223</v>
       </c>
     </row>
     <row r="1553">
@@ -25825,7 +25825,7 @@
         <v>15205.47993640247</v>
       </c>
       <c r="D1563" s="3" t="n">
-        <v>15967.68461566325</v>
+        <v>15967.68606515179</v>
       </c>
     </row>
     <row r="1564">
@@ -25841,7 +25841,7 @@
         <v>15352.00716049349</v>
       </c>
       <c r="D1564" s="3" t="n">
-        <v>16306.86678634965</v>
+        <v>16306.86533393587</v>
       </c>
     </row>
     <row r="1565">
@@ -25857,7 +25857,7 @@
         <v>15352.00716049349</v>
       </c>
       <c r="D1565" s="3" t="n">
-        <v>16306.86678634965</v>
+        <v>16306.86533393587</v>
       </c>
     </row>
     <row r="1566">
@@ -25873,7 +25873,7 @@
         <v>15352.00716049349</v>
       </c>
       <c r="D1566" s="3" t="n">
-        <v>16306.86678634965</v>
+        <v>16306.86533393587</v>
       </c>
     </row>
     <row r="1567">
@@ -25889,7 +25889,7 @@
         <v>15433.79086130267</v>
       </c>
       <c r="D1567" s="3" t="n">
-        <v>16319.10821522394</v>
+        <v>16319.10676869467</v>
       </c>
     </row>
     <row r="1568">
@@ -25937,7 +25937,7 @@
         <v>15313.16083853979</v>
       </c>
       <c r="D1570" s="3" t="n">
-        <v>15953.09234651509</v>
+        <v>15953.09378692014</v>
       </c>
     </row>
     <row r="1571">
@@ -25953,7 +25953,7 @@
         <v>15303.61954543512</v>
       </c>
       <c r="D1571" s="3" t="n">
-        <v>15974.57316987713</v>
+        <v>15974.57172854817</v>
       </c>
     </row>
     <row r="1572">
@@ -25969,7 +25969,7 @@
         <v>15303.61954543512</v>
       </c>
       <c r="D1572" s="3" t="n">
-        <v>15974.57316987713</v>
+        <v>15974.57172854817</v>
       </c>
     </row>
     <row r="1573">
@@ -25985,7 +25985,7 @@
         <v>15303.61954543512</v>
       </c>
       <c r="D1573" s="3" t="n">
-        <v>15974.57316987713</v>
+        <v>15974.57172854817</v>
       </c>
     </row>
     <row r="1574">
@@ -26001,7 +26001,7 @@
         <v>15264.09103402347</v>
       </c>
       <c r="D1574" s="3" t="n">
-        <v>15975.89861410579</v>
+        <v>15975.89717265724</v>
       </c>
     </row>
     <row r="1575">
@@ -26033,7 +26033,7 @@
         <v>15475.36386124225</v>
       </c>
       <c r="D1576" s="3" t="n">
-        <v>16103.4733422314</v>
+        <v>16103.47189888398</v>
       </c>
     </row>
     <row r="1577">
@@ -26145,7 +26145,7 @@
         <v>15572.82128081695</v>
       </c>
       <c r="D1583" s="3" t="n">
-        <v>16370.26799510782</v>
+        <v>16370.2694478467</v>
       </c>
     </row>
     <row r="1584">
@@ -26241,7 +26241,7 @@
         <v>15354.05164902143</v>
       </c>
       <c r="D1589" s="3" t="n">
-        <v>16174.57964648448</v>
+        <v>16174.58110890549</v>
       </c>
     </row>
     <row r="1590">
@@ -26257,7 +26257,7 @@
         <v>15518.98134970976</v>
       </c>
       <c r="D1590" s="3" t="n">
-        <v>16407.9723965789</v>
+        <v>16407.97092344929</v>
       </c>
     </row>
     <row r="1591">
@@ -26289,7 +26289,7 @@
         <v>15435.8353498306</v>
       </c>
       <c r="D1592" s="3" t="n">
-        <v>16108.42259970786</v>
+        <v>16108.42112604801</v>
       </c>
     </row>
     <row r="1593">
@@ -26305,7 +26305,7 @@
         <v>15435.8353498306</v>
       </c>
       <c r="D1593" s="3" t="n">
-        <v>16108.42259970786</v>
+        <v>16108.42112604801</v>
       </c>
     </row>
     <row r="1594">
@@ -26321,7 +26321,7 @@
         <v>15435.8353498306</v>
       </c>
       <c r="D1594" s="3" t="n">
-        <v>16108.42259970786</v>
+        <v>16108.42112604801</v>
       </c>
     </row>
     <row r="1595">
@@ -26337,7 +26337,7 @@
         <v>15189.80517771399</v>
       </c>
       <c r="D1595" s="3" t="n">
-        <v>16369.11993296191</v>
+        <v>16369.12141746717</v>
       </c>
     </row>
     <row r="1596">
@@ -26385,7 +26385,7 @@
         <v>15274.31347666314</v>
       </c>
       <c r="D1598" s="3" t="n">
-        <v>16046.6644567058</v>
+        <v>16046.66297476645</v>
       </c>
     </row>
     <row r="1599">
@@ -29835,13 +29835,13 @@
         </is>
       </c>
       <c r="B1814" s="3" t="n">
-        <v>10685.31</v>
+        <v>10672.58</v>
       </c>
       <c r="C1814" s="3" t="n">
-        <v>18023.5806689554</v>
+        <v>17966.33291032734</v>
       </c>
       <c r="D1814" s="3" t="n">
-        <v>19517.99238949285</v>
+        <v>19328.51800206228</v>
       </c>
     </row>
   </sheetData>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>503.1787</v>
+        <v>503.1786</v>
       </c>
       <c r="F14" t="n">
         <v>444.1</v>
@@ -30535,10 +30535,10 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>508.5686</v>
+        <v>508.5689</v>
       </c>
       <c r="F19" t="n">
-        <v>450.18</v>
+        <v>450.19</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
@@ -31069,7 +31069,7 @@
         <v>13</v>
       </c>
       <c r="E34" t="n">
-        <v>37.5553</v>
+        <v>37.5552</v>
       </c>
       <c r="F34" t="n">
         <v>488.22</v>
@@ -31387,7 +31387,7 @@
         <v>2</v>
       </c>
       <c r="E43" t="n">
-        <v>281.8714</v>
+        <v>281.8713</v>
       </c>
       <c r="F43" t="n">
         <v>522.25</v>
@@ -32205,7 +32205,7 @@
         <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>296.4034</v>
+        <v>296.4033</v>
       </c>
       <c r="F66" t="n">
         <v>281.41</v>
@@ -32455,7 +32455,7 @@
         <v>5</v>
       </c>
       <c r="E73" t="n">
-        <v>79.0334</v>
+        <v>79.0335</v>
       </c>
       <c r="F73" t="n">
         <v>389.11</v>
@@ -32560,7 +32560,7 @@
         <v>5</v>
       </c>
       <c r="E76" t="n">
-        <v>79.4863</v>
+        <v>79.4862</v>
       </c>
       <c r="F76" t="n">
         <v>389.33</v>
@@ -32807,7 +32807,7 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>492.7455</v>
+        <v>492.7454</v>
       </c>
       <c r="F83" t="n">
         <v>486.44</v>
@@ -32878,7 +32878,7 @@
         <v>5</v>
       </c>
       <c r="E85" t="n">
-        <v>80.7533</v>
+        <v>80.75320000000001</v>
       </c>
       <c r="F85" t="n">
         <v>404.24</v>
@@ -33094,7 +33094,7 @@
         <v>22</v>
       </c>
       <c r="E91" t="n">
-        <v>21.4422</v>
+        <v>21.4421</v>
       </c>
       <c r="F91" t="n">
         <v>471.73</v>
@@ -33131,7 +33131,7 @@
         <v>1</v>
       </c>
       <c r="E92" t="n">
-        <v>324.2195</v>
+        <v>324.2196</v>
       </c>
       <c r="F92" t="n">
         <v>337.86</v>
@@ -34264,7 +34264,7 @@
         <v>1</v>
       </c>
       <c r="E124" t="n">
-        <v>237.0889</v>
+        <v>237.0888</v>
       </c>
       <c r="F124" t="n">
         <v>216.14</v>
@@ -34335,7 +34335,7 @@
         <v>6</v>
       </c>
       <c r="E126" t="n">
-        <v>110.5416</v>
+        <v>110.5417</v>
       </c>
       <c r="F126" t="n">
         <v>602.63</v>
@@ -34477,7 +34477,7 @@
         <v>1</v>
       </c>
       <c r="E130" t="n">
-        <v>307.9361</v>
+        <v>307.936</v>
       </c>
       <c r="F130" t="n">
         <v>281.18</v>
@@ -34690,7 +34690,7 @@
         <v>1</v>
       </c>
       <c r="E136" t="n">
-        <v>514.654</v>
+        <v>514.6541</v>
       </c>
       <c r="F136" t="n">
         <v>469.62</v>
@@ -34795,7 +34795,7 @@
         <v>1</v>
       </c>
       <c r="E139" t="n">
-        <v>522.5701</v>
+        <v>522.5700000000001</v>
       </c>
       <c r="F139" t="n">
         <v>480.54</v>
@@ -35187,7 +35187,7 @@
         <v>1</v>
       </c>
       <c r="E150" t="n">
-        <v>549.3198</v>
+        <v>549.3199</v>
       </c>
       <c r="F150" t="n">
         <v>519.9299999999999</v>
@@ -35684,7 +35684,7 @@
         <v>1</v>
       </c>
       <c r="E164" t="n">
-        <v>358.4674</v>
+        <v>358.4675</v>
       </c>
       <c r="F164" t="n">
         <v>335.32</v>
@@ -37175,7 +37175,7 @@
         <v>1</v>
       </c>
       <c r="E206" t="n">
-        <v>838.3390000000001</v>
+        <v>838.3389</v>
       </c>
       <c r="F206" t="n">
         <v>777.76</v>
@@ -37317,7 +37317,7 @@
         <v>1</v>
       </c>
       <c r="E210" t="n">
-        <v>162.0719</v>
+        <v>162.072</v>
       </c>
       <c r="F210" t="n">
         <v>151.38</v>
@@ -37351,7 +37351,7 @@
         <v>1</v>
       </c>
       <c r="E211" t="n">
-        <v>836.5687</v>
+        <v>836.5688</v>
       </c>
       <c r="F211" t="n">
         <v>772.22</v>
@@ -37496,7 +37496,7 @@
         <v>3</v>
       </c>
       <c r="E215" t="n">
-        <v>207.1958</v>
+        <v>207.1957</v>
       </c>
       <c r="F215" t="n">
         <v>570.13</v>
@@ -38416,7 +38416,7 @@
         <v>1</v>
       </c>
       <c r="E241" t="n">
-        <v>331.4656</v>
+        <v>331.4655</v>
       </c>
       <c r="F241" t="n">
         <v>315.83</v>
@@ -39765,7 +39765,7 @@
         <v>2</v>
       </c>
       <c r="E279" t="n">
-        <v>243.4135</v>
+        <v>243.4134</v>
       </c>
       <c r="F279" t="n">
         <v>425.03</v>
@@ -40333,7 +40333,7 @@
         <v>3</v>
       </c>
       <c r="E295" t="n">
-        <v>169.2715</v>
+        <v>169.2714</v>
       </c>
       <c r="F295" t="n">
         <v>436.17</v>
@@ -40404,7 +40404,7 @@
         <v>3</v>
       </c>
       <c r="E297" t="n">
-        <v>167.7402</v>
+        <v>167.7403</v>
       </c>
       <c r="F297" t="n">
         <v>429.52</v>
@@ -40617,7 +40617,7 @@
         <v>3</v>
       </c>
       <c r="E303" t="n">
-        <v>238.1526</v>
+        <v>238.1527</v>
       </c>
       <c r="F303" t="n">
         <v>608.78</v>
@@ -40938,7 +40938,7 @@
         <v>1</v>
       </c>
       <c r="E312" t="n">
-        <v>278.2458</v>
+        <v>278.2457</v>
       </c>
       <c r="F312" t="n">
         <v>240.92</v>
